--- a/RC_Shipping_Tracker.xlsx
+++ b/RC_Shipping_Tracker.xlsx
@@ -15,9 +15,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Shipped'!$A$1:$O$79</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Available'!$A$1:$P$81</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Week'!$A$1:$J$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Shipped'!$A$1:$O$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Available'!$A$1:$P$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Week'!$A$1:$J$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Genre Mix'!$A$1:$H$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Reconciliation'!$A$1:$G$22</definedName>
   </definedNames>
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O79"/>
+  <dimension ref="A1:O89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -5900,8 +5900,674 @@
       <c r="N79" s="2" t="inlineStr"/>
       <c r="O79" s="2" t="inlineStr"/>
     </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Week_8_12_09</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>RC_ELITE_260912_01</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>RC-ELITE-260711-0025</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>elite</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>Life Sciences &amp; Environment</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="I80" s="4" t="inlineStr">
+        <is>
+          <t>needs_review</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>passage fuzzy 0.89</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>exported_rc_sets/RC-ELITE-260711-0025.txt</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>Week_8_12_09/RC_ELITE_260912_01.docx</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr"/>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>passage edited after export</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Week_8_12_09</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>RC_ELITE_260912_02</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>RC-ELITE-260726-0032</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>elite</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>Sociology &amp; Culture</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="I81" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>passage exact</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>exported_rc_sets/RC-ELITE-260726-0032.txt</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>Week_8_12_09/RC_ELITE_260912_02.docx</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr"/>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>Pipeline approved (score 8.6); passed duplicate check, word count 527 (elite band), length-bias clean (0/6 longest); placed into Week_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Week_8_12_09</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>RC_ELITE_260912_03</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>RC-ELITE-260904-0073</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>elite</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>History</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="I82" s="4" t="inlineStr">
+        <is>
+          <t>needs_review</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>passage exact</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>exported_rc_sets/RC-ELITE-260904-0073.txt</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>Week_8_12_09/RC_ELITE_260912_03.docx</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr"/>
+      <c r="O82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Week_8_12_09</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>RC_HARD_260912_01</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>RC-HARD-260726-0021</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>Language &amp; Linguistics</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>passage fuzzy 0.99</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>exported_rc_sets/RC-HARD-260726-0021.txt</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>Week_8_12_09/RC_HARD_260912_01.docx</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr"/>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>passage edited after export</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Week_8_12_09</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>RC_HARD_260912_02</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>RC-HARD-260726-0025</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>Arts, Music &amp; Film</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="I84" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>passage exact</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>exported_rc_sets/RC-HARD-260726-0025.txt</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>Week_8_12_09/RC_HARD_260912_02.docx</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr"/>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>Was needs_review; manually judged 2026-07-26 (family_realization 9, ending_behavior 9, voice_consistency 8, distractor_efficiency 8, explanation_quality 8, avg 8.4) -- approve; db updated to approved/</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Week_8_12_09</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>RC_HARD_260912_03</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>RC-HARD-260822-0060</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>Politics, Law &amp; Policy</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="I85" s="4" t="inlineStr">
+        <is>
+          <t>needs_review</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>passage exact</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>exported_rc_sets/RC-HARD-260822-0060.txt</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>Week_8_12_09/RC_HARD_260912_03.docx</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr"/>
+      <c r="O85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Week_8_12_09</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>RC_MEDIUM_260912_01</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>RC-MEDIUM-260905-0061</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>Medicine &amp; Health</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="I86" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>passage exact</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260905-0061.txt</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>Week_8_12_09/RC_MEDIUM_260912_01.docx</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr"/>
+      <c r="O86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Week_8_12_09</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>RC_MEDIUM_260912_02</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>RC-MEDIUM-260811-0027</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>Economics &amp; Business</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="I87" s="4" t="inlineStr">
+        <is>
+          <t>needs_review</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>passage exact</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>exported_rc_sets/RC-MEDIUM-260811-0027.txt</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>Week_8_12_09/RC_MEDIUM_260912_02.docx</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr"/>
+      <c r="O87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Week_8_12_09</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>RC_MEDIUM_260912_03</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>RC-MEDIUM-260819-0030</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>Philosophy &amp; Ethics</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="I88" s="4" t="inlineStr">
+        <is>
+          <t>needs_review</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>passage exact</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>exported_rc_sets/RC-MEDIUM-260819-0030.txt</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>Week_8_12_09/RC_MEDIUM_260912_03.docx</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Week_8_12_09</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>RC_MEDIUM_260912_04</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>RC-MEDIUM-260907-0065</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="I89" s="4" t="inlineStr">
+        <is>
+          <t>needs_review</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>passage exact</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>exported_rc_sets/RC-MEDIUM-260907-0065.txt</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>Week_8_12_09/RC_MEDIUM_260912_04.docx</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr"/>
+      <c r="O89" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O79"/>
+  <autoFilter ref="A1:O89"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5912,7 +6578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P81"/>
+  <dimension ref="A1:P71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -6230,7 +6896,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260726-0032</t>
+          <t>RC-ELITE-260904-0074</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -6240,7 +6906,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Sociology &amp; Culture</t>
+          <t>Arts, Music &amp; Film</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -6254,55 +6920,47 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>+2 questions</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1</v>
+        <v>0.862</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.658</v>
+        <v>0.505</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>527</v>
+        <v>545</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260726-0032.txt</t>
+          <t>exported_rc_sets/RC-ELITE-260904-0074.txt</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260726-0032.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260904-0074.txt</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260726-0032.txt</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>Pipeline approved (score 8.6); passed duplicate check, word count 527 (elite band), length-bias clean (0/6 longest); placed into Week_5</t>
-        </is>
-      </c>
+          <t>exported_rc_sets/RC-ELITE-260904-0074.txt</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260904-0074</t>
+          <t>RC-ELITE-260822-0057</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -6312,7 +6970,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Arts, Music &amp; Film</t>
+          <t>Sociology &amp; Culture</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -6330,43 +6988,47 @@
       </c>
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.862</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.505</v>
+        <v>0.588</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>545</v>
+        <v>535</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260904-0074.txt</t>
+          <t>exported_rc_sets/RC-ELITE-260822-0057.txt</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260904-0074.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260822-0057.txt</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260904-0074.txt</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/RC-ELITE-260822-0057.txt | exported_rc_sets/post_housevoice_fix/RC-ELITE-260822-0057.txt</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>2 exported variants; preferred one listed first</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260822-0057</t>
+          <t>RC_E_0705_7</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -6376,7 +7038,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Sociology &amp; Culture</t>
+          <t>Philosophy &amp; Ethics</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -6390,51 +7052,53 @@
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>0.9330000000000001</v>
-      </c>
-      <c r="J7" s="2" t="n">
-        <v>0.588</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>+2 questions</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>535</v>
+        <v>573</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260822-0057.txt</t>
+          <t>exported_rc_sets/RC_E_0705_7.txt</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260822-0057.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC_E_0705_7.txt</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260822-0057.txt | exported_rc_sets/post_housevoice_fix/RC-ELITE-260822-0057.txt</t>
+          <t>exported_rc_sets/RC_E_0705_7.txt</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2 exported variants; preferred one listed first</t>
+          <t>legacy/manual export, not in the engine DB</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>RC_E_0705_7</t>
+          <t>RC-ELITE-260711-0023</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -6444,7 +7108,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Philosophy &amp; Ethics</t>
+          <t>Economics &amp; Business</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -6467,54 +7131,58 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8.2</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr"/>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>0.6879999999999999</v>
+      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>573</v>
+        <v>532</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC_E_0705_7.txt</t>
+          <t>exported_rc_sets/RC-ELITE-260711-0023.txt</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC_E_0705_7.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260711-0023.txt</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC_E_0705_7.txt</t>
+          <t>exported_rc_sets/RC-ELITE-260711-0023.txt</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>legacy/manual export, not in the engine DB</t>
+          <t>Was rejected_novelty (verdict not_run_novelty, flagged nearest to RC-ELITE-260706-0005 and RC_E_0706_1); manually judged 2026-07-26 (avg 7.8) -- approve. Manually compared against both flagged neighbo</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260711-0023</t>
+          <t>RC-HARD-260726-0022</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>elite</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Economics &amp; Business</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -6535,50 +7203,48 @@
           <t>+2 questions</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="H9" s="2" t="n">
+        <v>8.6</v>
       </c>
       <c r="I9" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.621</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>532</v>
+        <v>518</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260711-0023.txt</t>
+          <t>exported_rc_sets/RC-HARD-260726-0022.txt</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260711-0023.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260726-0022.txt</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260711-0023.txt</t>
+          <t>exported_rc_sets/RC-HARD-260726-0022.txt</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>Was rejected_novelty (verdict not_run_novelty, flagged nearest to RC-ELITE-260706-0005 and RC_E_0706_1); manually judged 2026-07-26 (avg 7.8) -- approve. Manually compared against both flagged neighbo</t>
+          <t>Pipeline approved (score 8.6); passed duplicate check, word count 518 (18 over hard band, within tolerance), length-bias clean (0/6 longest); placed into Week_5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260726-0021</t>
+          <t>RC-HARD-260726-0024</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -6588,7 +7254,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Language &amp; Linguistics</t>
+          <t>Psychology</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -6616,7 +7282,7 @@
         <v>1</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.545</v>
+        <v>0.623</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
@@ -6624,33 +7290,33 @@
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>556</v>
+        <v>524</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260726-0021.txt</t>
+          <t>exported_rc_sets/RC-HARD-260726-0024.txt</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260726-0021.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260726-0024.txt</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260726-0021.txt</t>
+          <t>exported_rc_sets/RC-HARD-260726-0024.txt</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Was needs_review, user approved 2026-07-26; passed duplicate check, word count 556 (56 over hard band, flagged), length-bias clean (0/6 longest); placed into new Week_5 Hard slot</t>
+          <t>Pipeline approved (score 8.6); passed duplicate check, word count 524 (24 over hard band, flagged), length-bias clean (1/6, Q4, thesis not longest); placed into Week_5 (completed to 5/5)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260726-0022</t>
+          <t>RC-HARD-260811-0046</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -6660,7 +7326,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Economics &amp; Business</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -6674,13 +7340,9 @@
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>+2 questions</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="n">
         <v>8.6</v>
       </c>
@@ -6688,41 +7350,41 @@
         <v>1</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.621</v>
+        <v>0.486</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260726-0022.txt</t>
+          <t>exported_rc_sets/RC-HARD-260811-0046.txt</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260726-0022.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260811-0046.txt</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260726-0022.txt</t>
+          <t>exported_rc_sets/RC-HARD-260811-0046.txt | exported_rc_sets/2026-08-14-exports-260810-260811/260811/RC-HARD-260811-0046.txt</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Pipeline approved (score 8.6); passed duplicate check, word count 518 (18 over hard band, within tolerance), length-bias clean (0/6 longest); placed into Week_5</t>
+          <t>2 exported variants; preferred one listed first</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260726-0024</t>
+          <t>RC-HARD-260726-0015</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -6732,7 +7394,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Psychology</t>
+          <t>Sociology &amp; Culture</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -6754,13 +7416,13 @@
         </is>
       </c>
       <c r="H12" s="2" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I12" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.623</v>
+        <v>0.673</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
@@ -6768,33 +7430,33 @@
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>524</v>
+        <v>501</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260726-0024.txt</t>
+          <t>exported_rc_sets/RC-HARD-260726-0015.txt</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260726-0024.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260726-0015.txt</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260726-0024.txt</t>
+          <t>exported_rc_sets/RC-HARD-260726-0015.txt</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>Pipeline approved (score 8.6); passed duplicate check, word count 524 (24 over hard band, flagged), length-bias clean (1/6, Q4, thesis not longest); placed into Week_5 (completed to 5/5)</t>
+          <t>Was needs_review with verdict "skipped_budget" (judge never ran, not a quality rejection); manually judged 2026-07-26 by same 5-category rubric -- family_realization 8, ending_behavior 9, voice_consis</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260811-0046</t>
+          <t>RC-HARD-260822-0063</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -6804,7 +7466,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Economics &amp; Business</t>
+          <t>Arts, Music &amp; Film</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -6822,35 +7484,35 @@
       </c>
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.486</v>
+        <v>0.539</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>512</v>
+        <v>532</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260811-0046.txt</t>
+          <t>exported_rc_sets/RC-HARD-260822-0063.txt</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260811-0046.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260822-0063.txt</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260811-0046.txt | exported_rc_sets/2026-08-14-exports-260810-260811/260811/RC-HARD-260811-0046.txt</t>
+          <t>exported_rc_sets/RC-HARD-260822-0063.txt | exported_rc_sets/flagged_similar/RC-HARD-260822-0063.txt</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -6862,7 +7524,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260726-0025</t>
+          <t>RC-HARD-260726-0023</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -6872,7 +7534,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Arts, Music &amp; Film</t>
+          <t>Language &amp; Linguistics</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -6894,13 +7556,13 @@
         </is>
       </c>
       <c r="H14" s="2" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="I14" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.581</v>
+        <v>0.652</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
@@ -6908,43 +7570,43 @@
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>548</v>
+        <v>536</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260726-0025.txt</t>
+          <t>exported_rc_sets/RC-HARD-260726-0023.txt</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260726-0025.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260726-0023.txt</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260726-0025.txt</t>
+          <t>exported_rc_sets/RC-HARD-260726-0023.txt</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Was needs_review; manually judged 2026-07-26 (family_realization 9, ending_behavior 9, voice_consistency 8, distractor_efficiency 8, explanation_quality 8, avg 8.4) -- approve; db updated to approved/</t>
+          <t>Pipeline approved (score 8.0); passed duplicate check, word count 536 (36 over hard band, flagged), length-bias clean (1/6, Q5, thesis not longest); placed into Week_5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260726-0015</t>
+          <t>RC-MEDIUM-260904-0056</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>hard</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Sociology &amp; Culture</t>
+          <t>Politics, Law &amp; Policy</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -6958,65 +7620,57 @@
         </is>
       </c>
       <c r="F15" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>+2 questions</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1</v>
+        <v>0.794</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.673</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>501</v>
+        <v>533</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260726-0015.txt</t>
+          <t>exported_rc_sets/RC-MEDIUM-260904-0056.txt</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260726-0015.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-MEDIUM-260904-0056.txt</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260726-0015.txt</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>Was needs_review with verdict "skipped_budget" (judge never ran, not a quality rejection); manually judged 2026-07-26 by same 5-category rubric -- family_realization 8, ending_behavior 9, voice_consis</t>
-        </is>
-      </c>
+          <t>exported_rc_sets/RC-MEDIUM-260904-0056.txt</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260822-0063</t>
+          <t>RC-MEDIUM-260726-0021</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>hard</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Arts, Music &amp; Film</t>
+          <t>Philosophy &amp; Ethics</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -7030,61 +7684,65 @@
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G16" s="2" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>+2 questions</t>
+        </is>
+      </c>
       <c r="H16" s="2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.539</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>532</v>
+        <v>503</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260822-0063.txt</t>
+          <t>exported_rc_sets/RC-MEDIUM-260726-0021.txt</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260822-0063.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-MEDIUM-260726-0021.txt</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260822-0063.txt | exported_rc_sets/flagged_similar/RC-HARD-260822-0063.txt</t>
+          <t>exported_rc_sets/RC-MEDIUM-260726-0021.txt</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2 exported variants; preferred one listed first</t>
+          <t xml:space="preserve">Pipeline approved (score 8.8, verdict approve, verified via judge_json before shipping); passed duplicate check, word count 503 (53 over medium band 400-450, flagged), length-bias clean (0/6 longest, </t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260726-0023</t>
+          <t>RC-ELITE-260905-0075</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>hard</t>
+          <t>elite</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Language &amp; Linguistics</t>
+          <t>Politics, Law &amp; Policy</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -7092,71 +7750,67 @@
           <t>approved</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>+2 questions</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1</v>
+        <v>0.871</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.652</v>
+        <v>0.451</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>536</v>
+        <v>549</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260726-0023.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-ELITE-260905-0075.txt</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260726-0023.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-ELITE-260905-0075.txt</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260726-0023.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-ELITE-260905-0075.txt</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>Pipeline approved (score 8.0); passed duplicate check, word count 536 (36 over hard band, flagged), length-bias clean (1/6, Q5, thesis not longest); placed into Week_5</t>
+          <t>only ever exported into flagged_similar (novelty-flagged)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260904-0056</t>
+          <t>RC-ELITE-260905-0077</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>elite</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Politics, Law &amp; Policy</t>
+          <t>Science &amp; Technology</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -7164,9 +7818,9 @@
           <t>approved</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
@@ -7174,115 +7828,115 @@
       </c>
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0.794</v>
+        <v>0.784</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.545</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-MEDIUM-260904-0056.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-ELITE-260905-0077.txt</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-MEDIUM-260904-0056.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-ELITE-260905-0077.txt</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-MEDIUM-260904-0056.txt</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/flagged_similar/RC-ELITE-260905-0077.txt</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>only ever exported into flagged_similar (novelty-flagged)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260726-0021</t>
+          <t>RC-ELITE-260905-0078</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>elite</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Philosophy &amp; Ethics</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
+          <t>Language &amp; Linguistics</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>needs_review</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
       <c r="F19" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>+2 questions</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>1</v>
+        <v>0.822</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.443</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>503</v>
+        <v>528</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-MEDIUM-260726-0021.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-ELITE-260905-0078.txt</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-MEDIUM-260726-0021.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-ELITE-260905-0078.txt</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-MEDIUM-260726-0021.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-ELITE-260905-0078.txt</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pipeline approved (score 8.8, verdict approve, verified via judge_json before shipping); passed duplicate check, word count 503 (53 over medium band 400-450, flagged), length-bias clean (0/6 longest, </t>
+          <t>only ever exported into flagged_similar (novelty-flagged)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260905-0075</t>
+          <t>RC-ELITE-260810-0035</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -7292,12 +7946,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Politics, Law &amp; Policy</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>approved</t>
+          <t>Life Sciences &amp; Environment</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -7310,47 +7964,47 @@
       </c>
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0.871</v>
+        <v>1</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.451</v>
+        <v>0.652</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>549</v>
+        <v>564</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-ELITE-260905-0075.txt</t>
+          <t>exported_rc_sets/RC-ELITE-260810-0035.txt</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-ELITE-260905-0075.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260810-0035.txt</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-ELITE-260905-0075.txt</t>
+          <t>exported_rc_sets/RC-ELITE-260810-0035.txt | exported_rc_sets/2026-08-14-exports-260810-260811/260810/RC-ELITE-260810-0035.txt</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>only ever exported into flagged_similar (novelty-flagged)</t>
+          <t>2 exported variants; preferred one listed first</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260905-0077</t>
+          <t>RC-ELITE-260821-0050</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -7360,12 +8014,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Science &amp; Technology</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>approved</t>
+          <t>Psychology</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -7381,59 +8035,59 @@
         <v>8.6</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>0.784</v>
+        <v>0.74</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.545</v>
+        <v>0.517</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-ELITE-260905-0077.txt</t>
+          <t>exported_rc_sets/RC-ELITE-260821-0050.txt</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-ELITE-260905-0077.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260821-0050.txt</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-ELITE-260905-0077.txt</t>
+          <t>exported_rc_sets/RC-ELITE-260821-0050.txt | exported_rc_sets/post_housevoice_fix/RC-ELITE-260821-0050.txt | exported_rc_sets/try_2/RC-ELITE-260821-0050.txt</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>only ever exported into flagged_similar (novelty-flagged)</t>
+          <t>3 exported variants; preferred one listed first</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260905-0061</t>
+          <t>RC-ELITE-260822-0060</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>elite</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Medicine &amp; Health</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>approved</t>
+          <t>Arts, Music &amp; Film</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -7446,47 +8100,47 @@
       </c>
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0.836</v>
+        <v>0.895</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.48</v>
+        <v>0.509</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>519</v>
+        <v>564</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260905-0061.txt</t>
+          <t>exported_rc_sets/post_housevoice_fix/RC-ELITE-260822-0060.txt</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-MEDIUM-260905-0061.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\post_housevoice_fix\RC-ELITE-260822-0060.txt</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260905-0061.txt</t>
+          <t>exported_rc_sets/post_housevoice_fix/RC-ELITE-260822-0060.txt | exported_rc_sets/review_shippable/02_likely_length_only/RC-ELITE-260822-0060.txt | exported_rc_sets/flagged_similar/RC-ELITE-260822-0060.txt | exported_rc_sets/try_2/flagged_similar/RC-ELITE-260822-0060.txt</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>only ever exported into flagged_similar (novelty-flagged)</t>
+          <t>4 exported variants; preferred one listed first</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260905-0078</t>
+          <t>RC-ELITE-260811-0038</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -7496,7 +8150,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Language &amp; Linguistics</t>
+          <t>History</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -7514,47 +8168,47 @@
       </c>
       <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>0.822</v>
+        <v>1</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.443</v>
+        <v>0.529</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>528</v>
+        <v>519</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-ELITE-260905-0078.txt</t>
+          <t>exported_rc_sets/RC-ELITE-260811-0038.txt</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-ELITE-260905-0078.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260811-0038.txt</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-ELITE-260905-0078.txt</t>
+          <t>exported_rc_sets/RC-ELITE-260811-0038.txt | exported_rc_sets/2026-08-14-exports-260810-260811/260811/RC-ELITE-260811-0038.txt</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>only ever exported into flagged_similar (novelty-flagged)</t>
+          <t>2 exported variants; preferred one listed first</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260711-0025</t>
+          <t>RC-ELITE-260822-0062</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -7564,7 +8218,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Life Sciences &amp; Environment</t>
+          <t>Philosophy &amp; Ethics</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -7578,51 +8232,51 @@
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>+2 questions</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1</v>
+        <v>0.907</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.663</v>
+        <v>0.616</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>664</v>
+        <v>525</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260711-0025.txt</t>
+          <t>exported_rc_sets/RC-ELITE-260822-0062.txt</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260711-0025.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260822-0062.txt</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260711-0025.txt</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/RC-ELITE-260822-0062.txt | exported_rc_sets/flagged_similar/RC-ELITE-260822-0062.txt</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>2 exported variants; preferred one listed first</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260810-0035</t>
+          <t>RC-ELITE-260907-0082</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -7632,7 +8286,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Life Sciences &amp; Environment</t>
+          <t>Politics, Law &amp; Policy</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -7650,47 +8304,43 @@
       </c>
       <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>1</v>
+        <v>0.884</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.652</v>
+        <v>0.482</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260810-0035.txt</t>
+          <t>exported_rc_sets/RC-ELITE-260907-0082.txt</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260810-0035.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260907-0082.txt</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260810-0035.txt | exported_rc_sets/2026-08-14-exports-260810-260811/260810/RC-ELITE-260810-0035.txt</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>2 exported variants; preferred one listed first</t>
-        </is>
-      </c>
+          <t>exported_rc_sets/RC-ELITE-260907-0082.txt</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260821-0050</t>
+          <t>RC-ELITE-260907-0083</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -7700,7 +8350,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Psychology</t>
+          <t>Medicine &amp; Health</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -7718,47 +8368,43 @@
       </c>
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>0.74</v>
+        <v>0.862</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.517</v>
+        <v>0.44</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>533</v>
+        <v>578</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260821-0050.txt</t>
+          <t>exported_rc_sets/RC-ELITE-260907-0083.txt</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260821-0050.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260907-0083.txt</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260821-0050.txt | exported_rc_sets/post_housevoice_fix/RC-ELITE-260821-0050.txt | exported_rc_sets/try_2/RC-ELITE-260821-0050.txt</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>3 exported variants; preferred one listed first</t>
-        </is>
-      </c>
+          <t>exported_rc_sets/RC-ELITE-260907-0083.txt</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260822-0060</t>
+          <t>RC-ELITE-260905-0076</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -7768,7 +8414,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Arts, Music &amp; Film</t>
+          <t>History</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -7786,47 +8432,43 @@
       </c>
       <c r="G27" s="2" t="inlineStr"/>
       <c r="H27" s="2" t="n">
-        <v>8.6</v>
+        <v>6.8</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>0.895</v>
+        <v>0.862</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.509</v>
+        <v>0.457</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>564</v>
+        <v>536</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/post_housevoice_fix/RC-ELITE-260822-0060.txt</t>
+          <t>exported_rc_sets/RC-ELITE-260905-0076.txt</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\post_housevoice_fix\RC-ELITE-260822-0060.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260905-0076.txt</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/post_housevoice_fix/RC-ELITE-260822-0060.txt | exported_rc_sets/review_shippable/02_likely_length_only/RC-ELITE-260822-0060.txt | exported_rc_sets/flagged_similar/RC-ELITE-260822-0060.txt | exported_rc_sets/try_2/flagged_similar/RC-ELITE-260822-0060.txt</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>4 exported variants; preferred one listed first</t>
-        </is>
-      </c>
+          <t>exported_rc_sets/RC-ELITE-260905-0076.txt</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260904-0073</t>
+          <t>RC-ELITE-260822-0059</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -7836,7 +8478,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>History</t>
+          <t>Politics, Law &amp; Policy</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -7854,53 +8496,57 @@
       </c>
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="n">
-        <v>8.4</v>
+        <v>6</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>0.761</v>
+        <v>0.981</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.555</v>
+        <v>0.622</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>547</v>
+        <v>531</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260904-0073.txt</t>
+          <t>exported_rc_sets/post_housevoice_fix/RC-ELITE-260822-0059.txt</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260904-0073.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\post_housevoice_fix\RC-ELITE-260822-0059.txt</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260904-0073.txt</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/post_housevoice_fix/RC-ELITE-260822-0059.txt | exported_rc_sets/flagged_similar/RC-ELITE-260822-0059.txt | exported_rc_sets/try_2/flagged_similar/RC-ELITE-260822-0059.txt</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>3 exported variants; preferred one listed first</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260811-0038</t>
+          <t>RC-HARD-260811-0035</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>elite</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>History</t>
+          <t>Medicine &amp; Health</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -7918,13 +8564,13 @@
       </c>
       <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I29" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.529</v>
+        <v>0.493</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
@@ -7932,21 +8578,21 @@
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260811-0038.txt</t>
+          <t>exported_rc_sets/RC-HARD-260811-0035.txt</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260811-0038.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260811-0035.txt</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260811-0038.txt | exported_rc_sets/2026-08-14-exports-260810-260811/260811/RC-ELITE-260811-0038.txt</t>
+          <t>exported_rc_sets/RC-HARD-260811-0035.txt | exported_rc_sets/2026-08-14-exports-260810-260811/260811/RC-HARD-260811-0035.txt</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -7958,17 +8604,17 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260822-0062</t>
+          <t>RC-HARD-260901-0073</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>elite</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Philosophy &amp; Ethics</t>
+          <t>Medicine &amp; Health</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -7986,35 +8632,35 @@
       </c>
       <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>0.907</v>
+        <v>0.85</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.616</v>
+        <v>0.499</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>525</v>
+        <v>540</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260822-0062.txt</t>
+          <t>exported_rc_sets/2026-09-01-0901-v2/RC-HARD-260901-0073.txt</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260822-0062.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\2026-09-01-0901-v2\RC-HARD-260901-0073.txt</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260822-0062.txt | exported_rc_sets/flagged_similar/RC-ELITE-260822-0062.txt</t>
+          <t>exported_rc_sets/2026-09-01-0901-v2/RC-HARD-260901-0073.txt | exported_rc_sets/flagged_similar/RC-HARD-260901-0073.txt</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -8026,17 +8672,17 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260907-0082</t>
+          <t>RC-HARD-260811-0037</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>elite</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Politics, Law &amp; Policy</t>
+          <t>Philosophy &amp; Ethics</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -8054,53 +8700,57 @@
       </c>
       <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>0.884</v>
+        <v>1</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.482</v>
+        <v>0.505</v>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>550</v>
+        <v>531</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260907-0082.txt</t>
+          <t>exported_rc_sets/RC-HARD-260811-0037.txt</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260907-0082.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260811-0037.txt</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260907-0082.txt</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/RC-HARD-260811-0037.txt | exported_rc_sets/2026-08-14-exports-260810-260811/260811/RC-HARD-260811-0037.txt</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>2 exported variants; preferred one listed first</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260907-0083</t>
+          <t>RC-HARD-260811-0047</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>elite</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Medicine &amp; Health</t>
+          <t>Literature &amp; Criticism</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -8118,53 +8768,57 @@
       </c>
       <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0.862</v>
+        <v>1</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.44</v>
+        <v>0.538</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>578</v>
+        <v>496</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260907-0083.txt</t>
+          <t>exported_rc_sets/RC-HARD-260811-0047.txt</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260907-0083.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260811-0047.txt</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260907-0083.txt</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/RC-HARD-260811-0047.txt | exported_rc_sets/2026-08-14-exports-260810-260811/260811/RC-HARD-260811-0047.txt</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>2 exported variants; preferred one listed first</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260905-0076</t>
+          <t>RC-HARD-260819-0050</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>elite</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>History</t>
+          <t>Language &amp; Linguistics</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -8182,53 +8836,57 @@
       </c>
       <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>0.862</v>
+        <v>1</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.457</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260905-0076.txt</t>
+          <t>exported_rc_sets/RC-HARD-260819-0050.txt</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260905-0076.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260819-0050.txt</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260905-0076.txt</t>
-        </is>
-      </c>
-      <c r="P33" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/RC-HARD-260819-0050.txt | exported_rc_sets/try_2/RC-HARD-260819-0050.txt</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>2 exported variants; preferred one listed first</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260822-0059</t>
+          <t>RC-HARD-260810-0034</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>elite</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Politics, Law &amp; Policy</t>
+          <t>History</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -8246,47 +8904,47 @@
       </c>
       <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="n">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0.981</v>
+        <v>1</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.622</v>
+        <v>0.543</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>531</v>
+        <v>548</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/post_housevoice_fix/RC-ELITE-260822-0059.txt</t>
+          <t>exported_rc_sets/RC-HARD-260810-0034.txt</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\post_housevoice_fix\RC-ELITE-260822-0059.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260810-0034.txt</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/post_housevoice_fix/RC-ELITE-260822-0059.txt | exported_rc_sets/flagged_similar/RC-ELITE-260822-0059.txt | exported_rc_sets/try_2/flagged_similar/RC-ELITE-260822-0059.txt</t>
+          <t>exported_rc_sets/RC-HARD-260810-0034.txt | exported_rc_sets/2026-08-14-exports-260810-260811/260810/RC-HARD-260810-0034.txt</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>3 exported variants; preferred one listed first</t>
+          <t>2 exported variants; preferred one listed first</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260811-0035</t>
+          <t>RC-HARD-260904-0080</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -8296,7 +8954,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Medicine &amp; Health</t>
+          <t>Literature &amp; Criticism</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -8314,47 +8972,47 @@
       </c>
       <c r="G35" s="2" t="inlineStr"/>
       <c r="H35" s="2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>1</v>
+        <v>0.737</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.493</v>
+        <v>0.581</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>516</v>
+        <v>567</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260811-0035.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-HARD-260904-0080.txt</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260811-0035.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-HARD-260904-0080.txt</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260811-0035.txt | exported_rc_sets/2026-08-14-exports-260810-260811/260811/RC-HARD-260811-0035.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-HARD-260904-0080.txt</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2 exported variants; preferred one listed first</t>
+          <t>only ever exported into flagged_similar (novelty-flagged)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260901-0073</t>
+          <t>RC-HARD-260905-0082</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -8364,7 +9022,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Medicine &amp; Health</t>
+          <t>Anthropology &amp; Archaeology</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -8382,47 +9040,43 @@
       </c>
       <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="I36" s="2" t="n">
         <v>0.85</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.499</v>
+        <v>0.533</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>540</v>
+        <v>549</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/2026-09-01-0901-v2/RC-HARD-260901-0073.txt</t>
+          <t>exported_rc_sets/RC-HARD-260905-0082.txt</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\2026-09-01-0901-v2\RC-HARD-260901-0073.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260905-0082.txt</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/2026-09-01-0901-v2/RC-HARD-260901-0073.txt | exported_rc_sets/flagged_similar/RC-HARD-260901-0073.txt</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>2 exported variants; preferred one listed first</t>
-        </is>
-      </c>
+          <t>exported_rc_sets/RC-HARD-260905-0082.txt</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260811-0037</t>
+          <t>RC-HARD-260907-0087</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -8432,7 +9086,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Philosophy &amp; Ethics</t>
+          <t>Arts, Music &amp; Film</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -8450,47 +9104,47 @@
       </c>
       <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>1</v>
+        <v>0.831</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.505</v>
+        <v>0.534</v>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>531</v>
+        <v>561</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260811-0037.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-HARD-260907-0087.txt</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260811-0037.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-HARD-260907-0087.txt</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260811-0037.txt | exported_rc_sets/2026-08-14-exports-260810-260811/260811/RC-HARD-260811-0037.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-HARD-260907-0087.txt</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2 exported variants; preferred one listed first</t>
+          <t>only ever exported into flagged_similar (novelty-flagged)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260811-0047</t>
+          <t>RC-HARD-260822-0061</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -8500,7 +9154,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Literature &amp; Criticism</t>
+          <t>Politics, Law &amp; Policy</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -8518,47 +9172,47 @@
       </c>
       <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>1</v>
+        <v>0.857</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.538</v>
+        <v>0.524</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>496</v>
+        <v>503</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260811-0047.txt</t>
+          <t>exported_rc_sets/post_housevoice_fix/RC-HARD-260822-0061.txt</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260811-0047.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\post_housevoice_fix\RC-HARD-260822-0061.txt</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260811-0047.txt | exported_rc_sets/2026-08-14-exports-260810-260811/260811/RC-HARD-260811-0047.txt</t>
+          <t>exported_rc_sets/post_housevoice_fix/RC-HARD-260822-0061.txt | exported_rc_sets/review_shippable/01_shippable_as_is/RC-HARD-260822-0061.txt | exported_rc_sets/flagged_similar/RC-HARD-260822-0061.txt | exported_rc_sets/try_2/flagged_similar/RC-HARD-260822-0061.txt</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2 exported variants; preferred one listed first</t>
+          <t>4 exported variants; preferred one listed first</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260819-0050</t>
+          <t>RC-HARD-260901-0077</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -8568,7 +9222,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Language &amp; Linguistics</t>
+          <t>Sociology &amp; Culture</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -8586,47 +9240,43 @@
       </c>
       <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="2" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>1</v>
+        <v>0.79</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.531</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>533</v>
+        <v>551</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260819-0050.txt</t>
+          <t>exported_rc_sets/RC-HARD-260901-0077.txt</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260819-0050.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260901-0077.txt</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260819-0050.txt | exported_rc_sets/try_2/RC-HARD-260819-0050.txt</t>
-        </is>
-      </c>
-      <c r="P39" s="2" t="inlineStr">
-        <is>
-          <t>2 exported variants; preferred one listed first</t>
-        </is>
-      </c>
+          <t>exported_rc_sets/RC-HARD-260901-0077.txt</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260810-0034</t>
+          <t>RC-HARD-260905-0081</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -8636,7 +9286,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>History</t>
+          <t>Politics, Law &amp; Policy</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -8654,47 +9304,47 @@
       </c>
       <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>1</v>
+        <v>0.862</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.543</v>
+        <v>0.524</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260810-0034.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-HARD-260905-0081.txt</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260810-0034.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-HARD-260905-0081.txt</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260810-0034.txt | exported_rc_sets/2026-08-14-exports-260810-260811/260810/RC-HARD-260810-0034.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-HARD-260905-0081.txt</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2 exported variants; preferred one listed first</t>
+          <t>only ever exported into flagged_similar (novelty-flagged)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260904-0080</t>
+          <t>RC-HARD-260901-0074</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -8704,7 +9354,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Literature &amp; Criticism</t>
+          <t>Medicine &amp; Health</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -8722,47 +9372,47 @@
       </c>
       <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="2" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>0.737</v>
+        <v>0.86</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.581</v>
+        <v>0.529</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>567</v>
+        <v>545</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-HARD-260904-0080.txt</t>
+          <t>exported_rc_sets/2026-09-01-0901-v2/RC-HARD-260901-0074.txt</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-HARD-260904-0080.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\2026-09-01-0901-v2\RC-HARD-260901-0074.txt</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-HARD-260904-0080.txt</t>
+          <t>exported_rc_sets/2026-09-01-0901-v2/RC-HARD-260901-0074.txt | exported_rc_sets/RC-HARD-260901-0074.txt</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>only ever exported into flagged_similar (novelty-flagged)</t>
+          <t>2 exported variants; preferred one listed first</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260905-0082</t>
+          <t>RC-HARD-260822-0062</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -8772,7 +9422,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Anthropology &amp; Archaeology</t>
+          <t>Philosophy &amp; Ethics</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -8790,43 +9440,47 @@
       </c>
       <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>0.85</v>
+        <v>0.843</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.533</v>
+        <v>0.6</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>549</v>
+        <v>452</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260905-0082.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-HARD-260822-0062.txt</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260905-0082.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-HARD-260822-0062.txt</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260905-0082.txt</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/flagged_similar/RC-HARD-260822-0062.txt</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>only ever exported into flagged_similar (novelty-flagged)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260907-0087</t>
+          <t>RC-HARD-260907-0086</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -8836,7 +9490,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Arts, Music &amp; Film</t>
+          <t>Science &amp; Technology</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -8854,13 +9508,13 @@
       </c>
       <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>0.831</v>
+        <v>0.847</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.534</v>
+        <v>0.578</v>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
@@ -8868,33 +9522,29 @@
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>561</v>
+        <v>550</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-HARD-260907-0087.txt</t>
+          <t>exported_rc_sets/RC-HARD-260907-0086.txt</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-HARD-260907-0087.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260907-0086.txt</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-HARD-260907-0087.txt</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>only ever exported into flagged_similar (novelty-flagged)</t>
-        </is>
-      </c>
+          <t>exported_rc_sets/RC-HARD-260907-0086.txt</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260822-0060</t>
+          <t>RC-HARD-260905-0084</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -8904,7 +9554,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Politics, Law &amp; Policy</t>
+          <t>Life Sciences &amp; Environment</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -8922,47 +9572,47 @@
       </c>
       <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="2" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.839</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.591</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>486</v>
+        <v>523</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260822-0060.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-HARD-260905-0084.txt</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260822-0060.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-HARD-260905-0084.txt</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260822-0060.txt | exported_rc_sets/post_housevoice_fix/RC-HARD-260822-0060.txt | exported_rc_sets/flagged_similar/RC-HARD-260822-0060.txt | exported_rc_sets/try_2/flagged_similar/RC-HARD-260822-0060.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-HARD-260905-0084.txt</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>4 exported variants; preferred one listed first</t>
+          <t>only ever exported into flagged_similar (novelty-flagged)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260822-0061</t>
+          <t>RC-HARD-260905-0085</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -8972,7 +9622,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Politics, Law &amp; Policy</t>
+          <t>Economics &amp; Business</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -8990,47 +9640,43 @@
       </c>
       <c r="G45" s="2" t="inlineStr"/>
       <c r="H45" s="2" t="n">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>0.857</v>
+        <v>0.766</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.524</v>
+        <v>0.539</v>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>503</v>
+        <v>521</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/post_housevoice_fix/RC-HARD-260822-0061.txt</t>
+          <t>exported_rc_sets/RC-HARD-260905-0085.txt</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\post_housevoice_fix\RC-HARD-260822-0061.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260905-0085.txt</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/post_housevoice_fix/RC-HARD-260822-0061.txt | exported_rc_sets/review_shippable/01_shippable_as_is/RC-HARD-260822-0061.txt | exported_rc_sets/flagged_similar/RC-HARD-260822-0061.txt | exported_rc_sets/try_2/flagged_similar/RC-HARD-260822-0061.txt</t>
-        </is>
-      </c>
-      <c r="P45" s="2" t="inlineStr">
-        <is>
-          <t>4 exported variants; preferred one listed first</t>
-        </is>
-      </c>
+          <t>exported_rc_sets/RC-HARD-260905-0085.txt</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260901-0077</t>
+          <t>RC-HARD-260904-0079</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -9040,7 +9686,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Sociology &amp; Culture</t>
+          <t>History</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -9058,53 +9704,57 @@
       </c>
       <c r="G46" s="2" t="inlineStr"/>
       <c r="H46" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>0.79</v>
+        <v>0.806</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.531</v>
+        <v>0.514</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>551</v>
+        <v>566</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260901-0077.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-HARD-260904-0079.txt</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260901-0077.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-HARD-260904-0079.txt</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260901-0077.txt</t>
-        </is>
-      </c>
-      <c r="P46" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/flagged_similar/RC-HARD-260904-0079.txt</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>only ever exported into flagged_similar (novelty-flagged)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260905-0081</t>
+          <t>RC-MEDIUM-260904-0057</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>hard</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Politics, Law &amp; Policy</t>
+          <t>Science &amp; Technology</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -9122,35 +9772,35 @@
       </c>
       <c r="G47" s="2" t="inlineStr"/>
       <c r="H47" s="2" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>0.862</v>
+        <v>0.537</v>
       </c>
       <c r="J47" s="2" t="n">
         <v>0.524</v>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-HARD-260905-0081.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260904-0057.txt</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-HARD-260905-0081.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-MEDIUM-260904-0057.txt</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-HARD-260905-0081.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260904-0057.txt</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -9162,17 +9812,17 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260901-0074</t>
+          <t>RC-MEDIUM-260904-0058</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>hard</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Medicine &amp; Health</t>
+          <t>Politics, Law &amp; Policy</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -9190,57 +9840,57 @@
       </c>
       <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>0.86</v>
+        <v>0.89</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.529</v>
+        <v>0.585</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/2026-09-01-0901-v2/RC-HARD-260901-0074.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260904-0058.txt</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\2026-09-01-0901-v2\RC-HARD-260901-0074.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-MEDIUM-260904-0058.txt</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/2026-09-01-0901-v2/RC-HARD-260901-0074.txt | exported_rc_sets/RC-HARD-260901-0074.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260904-0058.txt</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>2 exported variants; preferred one listed first</t>
+          <t>only ever exported into flagged_similar (novelty-flagged)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260822-0062</t>
+          <t>RC-MEDIUM-260810-0024</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>hard</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Philosophy &amp; Ethics</t>
+          <t>Medicine &amp; Health</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -9258,57 +9908,57 @@
       </c>
       <c r="G49" s="2" t="inlineStr"/>
       <c r="H49" s="2" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>0.843</v>
+        <v>1</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.6</v>
+        <v>0.653</v>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L49" s="2" t="n">
-        <v>452</v>
+        <v>535</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-HARD-260822-0062.txt</t>
+          <t>exported_rc_sets/2026-08-14-exports-260810-260811/260810/RC-MEDIUM-260810-0024.txt</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-HARD-260822-0062.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\2026-08-14-exports-260810-260811\260810\RC-MEDIUM-260810-0024.txt</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-HARD-260822-0062.txt</t>
+          <t>exported_rc_sets/2026-08-14-exports-260810-260811/260810/RC-MEDIUM-260810-0024.txt | exported_rc_sets/2026-08-14-medium-8q/RC-MEDIUM-260810-0024.txt | exported_rc_sets/RC-MEDIUM-260810-0024.txt</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>only ever exported into flagged_similar (novelty-flagged)</t>
+          <t>3 exported variants; preferred one listed first</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260907-0086</t>
+          <t>RC-MEDIUM-260811-0025</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>hard</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Science &amp; Technology</t>
+          <t>Philosophy &amp; Ethics</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -9326,53 +9976,57 @@
       </c>
       <c r="G50" s="2" t="inlineStr"/>
       <c r="H50" s="2" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>0.847</v>
+        <v>1</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.578</v>
+        <v>0.544</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>550</v>
+        <v>506</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260907-0086.txt</t>
+          <t>exported_rc_sets/RC-MEDIUM-260811-0025.txt</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260907-0086.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-MEDIUM-260811-0025.txt</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260907-0086.txt</t>
-        </is>
-      </c>
-      <c r="P50" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/RC-MEDIUM-260811-0025.txt | exported_rc_sets/2026-08-14-exports-260810-260811/260811/RC-MEDIUM-260811-0025.txt</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>2 exported variants; preferred one listed first</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260905-0084</t>
+          <t>RC-MEDIUM-260901-0055</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>hard</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Life Sciences &amp; Environment</t>
+          <t>Literature &amp; Criticism</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -9390,35 +10044,35 @@
       </c>
       <c r="G51" s="2" t="inlineStr"/>
       <c r="H51" s="2" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>0.839</v>
+        <v>0.871</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.523</v>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
-        <v>523</v>
+        <v>551</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-HARD-260905-0084.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260901-0055.txt</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-HARD-260905-0084.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-MEDIUM-260901-0055.txt</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-HARD-260905-0084.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260901-0055.txt</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -9430,17 +10084,17 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260905-0085</t>
+          <t>RC-MEDIUM-260905-0063</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>hard</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Economics &amp; Business</t>
+          <t>Politics, Law &amp; Policy</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -9458,13 +10112,13 @@
       </c>
       <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="2" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>0.766</v>
+        <v>0.875</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.539</v>
+        <v>0.508</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
@@ -9472,39 +10126,43 @@
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>521</v>
+        <v>474</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260905-0085.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260905-0063.txt</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260905-0085.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-MEDIUM-260905-0063.txt</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260905-0085.txt</t>
-        </is>
-      </c>
-      <c r="P52" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260905-0063.txt</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>only ever exported into flagged_similar (novelty-flagged)</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260904-0079</t>
+          <t>RC-MEDIUM-260822-0040</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>hard</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>History</t>
+          <t>Philosophy &amp; Ethics</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -9522,35 +10180,35 @@
       </c>
       <c r="G53" s="2" t="inlineStr"/>
       <c r="H53" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>0.806</v>
+        <v>0.845</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.514</v>
+        <v>0.593</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
-        <v>566</v>
+        <v>401</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-HARD-260904-0079.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260822-0040.txt</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-HARD-260904-0079.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-MEDIUM-260822-0040.txt</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-HARD-260904-0079.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260822-0040.txt</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -9562,7 +10220,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260904-0057</t>
+          <t>RC-MEDIUM-260822-0038</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -9572,7 +10230,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Science &amp; Technology</t>
+          <t>Politics, Law &amp; Policy</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -9590,47 +10248,47 @@
       </c>
       <c r="G54" s="2" t="inlineStr"/>
       <c r="H54" s="2" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>0.537</v>
+        <v>0.95</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.524</v>
+        <v>0.633</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>550</v>
+        <v>479</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260904-0057.txt</t>
+          <t>exported_rc_sets/post_housevoice_fix/RC-MEDIUM-260822-0038.txt</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-MEDIUM-260904-0057.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\post_housevoice_fix\RC-MEDIUM-260822-0038.txt</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260904-0057.txt</t>
+          <t>exported_rc_sets/post_housevoice_fix/RC-MEDIUM-260822-0038.txt | exported_rc_sets/review_shippable/02_likely_length_only/RC-MEDIUM-260822-0038.txt | exported_rc_sets/flagged_similar/RC-MEDIUM-260822-0038.txt | exported_rc_sets/try_2/flagged_similar/RC-MEDIUM-260822-0038.txt</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>only ever exported into flagged_similar (novelty-flagged)</t>
+          <t>4 exported variants; preferred one listed first</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260904-0058</t>
+          <t>RC-MEDIUM-260901-0054</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -9640,7 +10298,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Politics, Law &amp; Policy</t>
+          <t>Arts, Music &amp; Film</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -9658,47 +10316,43 @@
       </c>
       <c r="G55" s="2" t="inlineStr"/>
       <c r="H55" s="2" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>0.89</v>
+        <v>0.884</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.585</v>
+        <v>0.45</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
-        <v>544</v>
+        <v>525</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260904-0058.txt</t>
+          <t>exported_rc_sets/RC-MEDIUM-260901-0054.txt</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-MEDIUM-260904-0058.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-MEDIUM-260901-0054.txt</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260904-0058.txt</t>
-        </is>
-      </c>
-      <c r="P55" s="2" t="inlineStr">
-        <is>
-          <t>only ever exported into flagged_similar (novelty-flagged)</t>
-        </is>
-      </c>
+          <t>exported_rc_sets/RC-MEDIUM-260901-0054.txt</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260810-0024</t>
+          <t>RC-MEDIUM-260904-0060</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -9708,7 +10362,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Medicine &amp; Health</t>
+          <t>History</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -9726,62 +10380,62 @@
       </c>
       <c r="G56" s="2" t="inlineStr"/>
       <c r="H56" s="2" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>1</v>
+        <v>0.847</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.653</v>
+        <v>0.536</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>535</v>
+        <v>557</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/2026-08-14-exports-260810-260811/260810/RC-MEDIUM-260810-0024.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260904-0060.txt</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\2026-08-14-exports-260810-260811\260810\RC-MEDIUM-260810-0024.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-MEDIUM-260904-0060.txt</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/2026-08-14-exports-260810-260811/260810/RC-MEDIUM-260810-0024.txt | exported_rc_sets/2026-08-14-medium-8q/RC-MEDIUM-260810-0024.txt | exported_rc_sets/RC-MEDIUM-260810-0024.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260904-0060.txt</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>3 exported variants; preferred one listed first</t>
+          <t>only ever exported into flagged_similar (novelty-flagged)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260811-0025</t>
+          <t>RC-ELITE-260822-0056</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>elite</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Philosophy &amp; Ethics</t>
-        </is>
-      </c>
-      <c r="D57" s="4" t="inlineStr">
-        <is>
-          <t>needs_review</t>
+          <t>Anthropology &amp; Archaeology</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>solver_dispute</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -9793,63 +10447,65 @@
         <v>8</v>
       </c>
       <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="n">
-        <v>8.6</v>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.544</v>
+        <v>0.531</v>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
-        <v>506</v>
+        <v>548</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-MEDIUM-260811-0025.txt</t>
+          <t>exported_rc_sets/RC-ELITE-260822-0056.txt</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-MEDIUM-260811-0025.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260822-0056.txt</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-MEDIUM-260811-0025.txt | exported_rc_sets/2026-08-14-exports-260810-260811/260811/RC-MEDIUM-260811-0025.txt</t>
+          <t>exported_rc_sets/RC-ELITE-260822-0056.txt | exported_rc_sets/post_housevoice_fix/RC-ELITE-260822-0056.txt | exported_rc_sets/try_2/RC-ELITE-260822-0056.txt</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>2 exported variants; preferred one listed first</t>
+          <t>3 exported variants; preferred one listed first</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260811-0027</t>
+          <t>RC-ELITE-260905-0080</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>elite</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Economics &amp; Business</t>
-        </is>
-      </c>
-      <c r="D58" s="4" t="inlineStr">
-        <is>
-          <t>needs_review</t>
+          <t>Literature &amp; Criticism</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>solver_dispute</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -9861,63 +10517,61 @@
         <v>8</v>
       </c>
       <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="n">
-        <v>8.6</v>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>1</v>
+        <v>0.804</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.5</v>
+        <v>0.542</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>489</v>
+        <v>519</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-MEDIUM-260811-0027.txt</t>
+          <t>exported_rc_sets/RC-ELITE-260905-0080.txt</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-MEDIUM-260811-0027.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260905-0080.txt</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-MEDIUM-260811-0027.txt | exported_rc_sets/2026-08-14-exports-260810-260811/260811/RC-MEDIUM-260811-0027.txt</t>
-        </is>
-      </c>
-      <c r="P58" s="2" t="inlineStr">
-        <is>
-          <t>2 exported variants; preferred one listed first</t>
-        </is>
-      </c>
+          <t>exported_rc_sets/RC-ELITE-260905-0080.txt</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260819-0030</t>
+          <t>RC-HARD-260901-0076</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Philosophy &amp; Ethics</t>
-        </is>
-      </c>
-      <c r="D59" s="4" t="inlineStr">
-        <is>
-          <t>needs_review</t>
+          <t>Literature &amp; Criticism</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>solver_dispute</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -9929,63 +10583,61 @@
         <v>8</v>
       </c>
       <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="n">
-        <v>8.6</v>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.468</v>
+        <v>0.549</v>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>517</v>
+        <v>539</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-MEDIUM-260819-0030.txt</t>
+          <t>exported_rc_sets/RC-HARD-260901-0076.txt</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-MEDIUM-260819-0030.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260901-0076.txt</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-MEDIUM-260819-0030.txt | exported_rc_sets/try_2/RC-MEDIUM-260819-0030.txt</t>
-        </is>
-      </c>
-      <c r="P59" s="2" t="inlineStr">
-        <is>
-          <t>2 exported variants; preferred one listed first</t>
-        </is>
-      </c>
+          <t>exported_rc_sets/RC-HARD-260901-0076.txt</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260901-0055</t>
+          <t>RC-HARD-260904-0078</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Literature &amp; Criticism</t>
-        </is>
-      </c>
-      <c r="D60" s="4" t="inlineStr">
-        <is>
-          <t>needs_review</t>
+          <t>Psychology</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>solver_dispute</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -9997,36 +10649,38 @@
         <v>8</v>
       </c>
       <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="n">
-        <v>8.6</v>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>0.871</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.523</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>551</v>
+        <v>544</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260901-0055.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-HARD-260904-0078.txt</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-MEDIUM-260901-0055.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-HARD-260904-0078.txt</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260901-0055.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-HARD-260904-0078.txt</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -10038,7 +10692,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260905-0063</t>
+          <t>RC-MEDIUM-260810-0022</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -10048,12 +10702,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Politics, Law &amp; Policy</t>
-        </is>
-      </c>
-      <c r="D61" s="4" t="inlineStr">
-        <is>
-          <t>needs_review</t>
+          <t>Medicine &amp; Health</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>solver_dispute</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -10065,48 +10719,50 @@
         <v>8</v>
       </c>
       <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="n">
-        <v>8.199999999999999</v>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.508</v>
+        <v>0.647</v>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>474</v>
+        <v>553</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260905-0063.txt</t>
+          <t>exported_rc_sets/2026-08-14-exports-260810-260811/260810/RC-MEDIUM-260810-0022.txt</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-MEDIUM-260905-0063.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\2026-08-14-exports-260810-260811\260810\RC-MEDIUM-260810-0022.txt</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260905-0063.txt</t>
+          <t>exported_rc_sets/2026-08-14-exports-260810-260811/260810/RC-MEDIUM-260810-0022.txt | exported_rc_sets/2026-08-14-medium-8q/RC-MEDIUM-260810-0022.txt | exported_rc_sets/RC-MEDIUM-260810-0022.txt</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>only ever exported into flagged_similar (novelty-flagged)</t>
+          <t>3 exported variants; preferred one listed first</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260822-0040</t>
+          <t>RC-MEDIUM-260822-0035</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -10116,12 +10772,12 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Philosophy &amp; Ethics</t>
-        </is>
-      </c>
-      <c r="D62" s="4" t="inlineStr">
-        <is>
-          <t>needs_review</t>
+          <t>Politics, Law &amp; Policy</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>solver_dispute</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -10133,14 +10789,16 @@
         <v>8</v>
       </c>
       <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="n">
-        <v>8</v>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>0.845</v>
+        <v>0.9</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.593</v>
+        <v>0.59</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
@@ -10148,33 +10806,33 @@
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>401</v>
+        <v>540</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260822-0040.txt</t>
+          <t>exported_rc_sets/RC-MEDIUM-260822-0035.txt</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-MEDIUM-260822-0040.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-MEDIUM-260822-0035.txt</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260822-0040.txt</t>
+          <t>exported_rc_sets/RC-MEDIUM-260822-0035.txt | exported_rc_sets/post_housevoice_fix/RC-MEDIUM-260822-0035.txt</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>only ever exported into flagged_similar (novelty-flagged)</t>
+          <t>2 exported variants; preferred one listed first</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260822-0038</t>
+          <t>RC-MEDIUM-260905-0062</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -10184,12 +10842,12 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Politics, Law &amp; Policy</t>
-        </is>
-      </c>
-      <c r="D63" s="4" t="inlineStr">
-        <is>
-          <t>needs_review</t>
+          <t>Economics &amp; Business</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>solver_dispute</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -10201,48 +10859,50 @@
         <v>8</v>
       </c>
       <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="n">
-        <v>7.8</v>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>0.95</v>
+        <v>0.79</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.633</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>479</v>
+        <v>566</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/post_housevoice_fix/RC-MEDIUM-260822-0038.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260905-0062.txt</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\post_housevoice_fix\RC-MEDIUM-260822-0038.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-MEDIUM-260905-0062.txt</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/post_housevoice_fix/RC-MEDIUM-260822-0038.txt | exported_rc_sets/review_shippable/02_likely_length_only/RC-MEDIUM-260822-0038.txt | exported_rc_sets/flagged_similar/RC-MEDIUM-260822-0038.txt | exported_rc_sets/try_2/flagged_similar/RC-MEDIUM-260822-0038.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260905-0062.txt</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>4 exported variants; preferred one listed first</t>
+          <t>only ever exported into flagged_similar (novelty-flagged)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260901-0054</t>
+          <t>RC-MEDIUM-260907-0066</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -10252,12 +10912,12 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Arts, Music &amp; Film</t>
-        </is>
-      </c>
-      <c r="D64" s="4" t="inlineStr">
-        <is>
-          <t>needs_review</t>
+          <t>Politics, Law &amp; Policy</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>solver_dispute</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -10269,36 +10929,38 @@
         <v>8</v>
       </c>
       <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="n">
-        <v>7.8</v>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>0.884</v>
+        <v>0.785</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.45</v>
+        <v>0.528</v>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>525</v>
+        <v>543</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-MEDIUM-260901-0054.txt</t>
+          <t>exported_rc_sets/RC-MEDIUM-260907-0066.txt</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-MEDIUM-260901-0054.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-MEDIUM-260907-0066.txt</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-MEDIUM-260901-0054.txt</t>
+          <t>exported_rc_sets/RC-MEDIUM-260907-0066.txt</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr"/>
@@ -10306,22 +10968,22 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260904-0060</t>
+          <t>RC-ELITE-260726-0030</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>elite</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="D65" s="4" t="inlineStr">
-        <is>
-          <t>needs_review</t>
+          <t>Anthropology &amp; Archaeology</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>rejected_novelty</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -10330,51 +10992,53 @@
         </is>
       </c>
       <c r="F65" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="n">
-        <v>7.8</v>
+        <v>6</v>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>+2 questions</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>0.847</v>
+        <v>1</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.536</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>557</v>
+        <v>500</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260904-0060.txt</t>
+          <t>exported_rc_sets/RC-ELITE-260726-0030.txt</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-MEDIUM-260904-0060.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260726-0030.txt</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260904-0060.txt</t>
-        </is>
-      </c>
-      <c r="P65" s="2" t="inlineStr">
-        <is>
-          <t>only ever exported into flagged_similar (novelty-flagged)</t>
-        </is>
-      </c>
+          <t>exported_rc_sets/RC-ELITE-260726-0030.txt</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260907-0065</t>
+          <t>RC-MEDIUM-260904-0059</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -10384,12 +11048,12 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Education</t>
-        </is>
-      </c>
-      <c r="D66" s="4" t="inlineStr">
-        <is>
-          <t>needs_review</t>
+          <t>Science &amp; Technology</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>rejected_novelty</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -10401,59 +11065,65 @@
         <v>8</v>
       </c>
       <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="n">
-        <v>7.6</v>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.525</v>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>504</v>
+        <v>568</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-MEDIUM-260907-0065.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260904-0059.txt</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-MEDIUM-260907-0065.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-MEDIUM-260904-0059.txt</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-MEDIUM-260907-0065.txt</t>
-        </is>
-      </c>
-      <c r="P66" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260904-0059.txt</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>only ever exported into flagged_similar (novelty-flagged)</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260822-0056</t>
+          <t>RC-MANUAL-260708-10</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>elite</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Anthropology &amp; Archaeology</t>
-        </is>
-      </c>
-      <c r="D67" s="5" t="inlineStr">
-        <is>
-          <t>solver_dispute</t>
+          <t>Science &amp; Technology</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>unrated</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -10462,53 +11132,45 @@
         </is>
       </c>
       <c r="F67" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I67" s="2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J67" s="2" t="n">
-        <v>0.531</v>
-      </c>
-      <c r="K67" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>+2 questions</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr"/>
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="n">
-        <v>548</v>
+        <v>384</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260822-0056.txt</t>
+          <t>exported_rc_sets/RC-MANUAL-260708-10_medium.txt</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260822-0056.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-MANUAL-260708-10_medium.txt</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260822-0056.txt | exported_rc_sets/post_housevoice_fix/RC-ELITE-260822-0056.txt | exported_rc_sets/try_2/RC-ELITE-260822-0056.txt</t>
+          <t>exported_rc_sets/RC-MANUAL-260708-10_medium.txt</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>3 exported variants; preferred one listed first</t>
+          <t xml:space="preserve">legacy/manual export, not in the engine DB; Source: manual generator (evolutionary metaphors for technology); word count 384 (medium band); tier assigned via word count + complexity read 2026-07-12; user-vetted before shipping; placed into new </t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260905-0080</t>
+          <t>RC_E_0705_2</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -10518,12 +11180,12 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Literature &amp; Criticism</t>
+          <t>Sociology &amp; Culture</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>solver_dispute</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -10532,64 +11194,68 @@
         </is>
       </c>
       <c r="F68" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G68" s="2" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>+2 questions</t>
+        </is>
+      </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I68" s="2" t="n">
-        <v>0.804</v>
-      </c>
-      <c r="J68" s="2" t="n">
-        <v>0.542</v>
-      </c>
+          <t>8.8</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>519</v>
+        <v>580</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260905-0080.txt</t>
+          <t>exported_rc_sets/RC_E_0705_2.txt</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260905-0080.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC_E_0705_2.txt</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260905-0080.txt</t>
-        </is>
-      </c>
-      <c r="P68" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/RC_E_0705_2.txt</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>BLOCKED - you marked this not-sent: length-bias FAILED: correct answer longest in 4/6 questions, incl. thesis Q1 -- needs content fix before shipping; legacy/manual export, not in the engine DB</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260901-0076</t>
+          <t>RC_E_0705_5</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>hard</t>
+          <t>elite</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Literature &amp; Criticism</t>
+          <t>Language &amp; Linguistics</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>solver_dispute</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -10598,49 +11264,53 @@
         </is>
       </c>
       <c r="F69" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G69" s="2" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>+2 questions</t>
+        </is>
+      </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I69" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J69" s="2" t="n">
-        <v>0.549</v>
-      </c>
+          <t>8.8</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>539</v>
+        <v>589</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260901-0076.txt</t>
+          <t>exported_rc_sets/RC_E_0705_5.txt</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260901-0076.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC_E_0705_5.txt</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260901-0076.txt</t>
-        </is>
-      </c>
-      <c r="P69" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/RC_E_0705_5.txt</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>BLOCKED - you marked this not-sent: length-bias FAILED: correct answer longest in 5/6 questions, incl. thesis Q1 -- needs content fix before shipping; legacy/manual export, not in the engine DB</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260904-0078</t>
+          <t>rc_hard_0004</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -10650,12 +11320,12 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Psychology</t>
+          <t>Anthropology &amp; Archaeology</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>solver_dispute</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -10664,58 +11334,58 @@
         </is>
       </c>
       <c r="F70" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G70" s="2" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>+2 questions</t>
+        </is>
+      </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="J70" s="2" t="n">
-        <v>0.5629999999999999</v>
-      </c>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>544</v>
+        <v>485</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-HARD-260904-0078.txt</t>
+          <t>exported_rc_sets/rc_hard_0004.txt</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-HARD-260904-0078.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\rc_hard_0004.txt</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-HARD-260904-0078.txt</t>
+          <t>exported_rc_sets/rc_hard_0004.txt</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>only ever exported into flagged_similar (novelty-flagged)</t>
+          <t>BLOCKED - you marked this not-sent: length-bias FAILED: correct answer longest in 6/6 questions (all), incl. thesis Q1 -- needs content fix before shipping; legacy/manual export, not in the engine DB</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260810-0022</t>
+          <t>RC_H_0705_3</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -10725,7 +11395,7 @@
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>solver_dispute</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -10734,739 +11404,51 @@
         </is>
       </c>
       <c r="F71" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G71" s="2" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>+2 questions</t>
+        </is>
+      </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I71" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J71" s="2" t="n">
-        <v>0.647</v>
-      </c>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="L71" s="2" t="n">
-        <v>553</v>
+        <v>515</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/2026-08-14-exports-260810-260811/260810/RC-MEDIUM-260810-0022.txt</t>
+          <t>exported_rc_sets/RC_H_0705_3.txt</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\2026-08-14-exports-260810-260811\260810\RC-MEDIUM-260810-0022.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC_H_0705_3.txt</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/2026-08-14-exports-260810-260811/260810/RC-MEDIUM-260810-0022.txt | exported_rc_sets/2026-08-14-medium-8q/RC-MEDIUM-260810-0022.txt | exported_rc_sets/RC-MEDIUM-260810-0022.txt</t>
+          <t>exported_rc_sets/RC_H_0705_3.txt</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>3 exported variants; preferred one listed first</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>RC-MEDIUM-260822-0035</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>Politics, Law &amp; Policy</t>
-        </is>
-      </c>
-      <c r="D72" s="5" t="inlineStr">
-        <is>
-          <t>solver_dispute</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J72" s="2" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="K72" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="L72" s="2" t="n">
-        <v>540</v>
-      </c>
-      <c r="M72" s="2" t="inlineStr">
-        <is>
-          <t>exported_rc_sets/RC-MEDIUM-260822-0035.txt</t>
-        </is>
-      </c>
-      <c r="N72" s="2" t="inlineStr">
-        <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-MEDIUM-260822-0035.txt</t>
-        </is>
-      </c>
-      <c r="O72" s="2" t="inlineStr">
-        <is>
-          <t>exported_rc_sets/RC-MEDIUM-260822-0035.txt | exported_rc_sets/post_housevoice_fix/RC-MEDIUM-260822-0035.txt</t>
-        </is>
-      </c>
-      <c r="P72" s="2" t="inlineStr">
-        <is>
-          <t>2 exported variants; preferred one listed first</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>RC-MEDIUM-260905-0062</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>Economics &amp; Business</t>
-        </is>
-      </c>
-      <c r="D73" s="5" t="inlineStr">
-        <is>
-          <t>solver_dispute</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I73" s="2" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="J73" s="2" t="n">
-        <v>0.5610000000000001</v>
-      </c>
-      <c r="K73" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="n">
-        <v>566</v>
-      </c>
-      <c r="M73" s="2" t="inlineStr">
-        <is>
-          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260905-0062.txt</t>
-        </is>
-      </c>
-      <c r="N73" s="2" t="inlineStr">
-        <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-MEDIUM-260905-0062.txt</t>
-        </is>
-      </c>
-      <c r="O73" s="2" t="inlineStr">
-        <is>
-          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260905-0062.txt</t>
-        </is>
-      </c>
-      <c r="P73" s="2" t="inlineStr">
-        <is>
-          <t>only ever exported into flagged_similar (novelty-flagged)</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>RC-MEDIUM-260907-0066</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>Politics, Law &amp; Policy</t>
-        </is>
-      </c>
-      <c r="D74" s="5" t="inlineStr">
-        <is>
-          <t>solver_dispute</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I74" s="2" t="n">
-        <v>0.785</v>
-      </c>
-      <c r="J74" s="2" t="n">
-        <v>0.528</v>
-      </c>
-      <c r="K74" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="L74" s="2" t="n">
-        <v>543</v>
-      </c>
-      <c r="M74" s="2" t="inlineStr">
-        <is>
-          <t>exported_rc_sets/RC-MEDIUM-260907-0066.txt</t>
-        </is>
-      </c>
-      <c r="N74" s="2" t="inlineStr">
-        <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-MEDIUM-260907-0066.txt</t>
-        </is>
-      </c>
-      <c r="O74" s="2" t="inlineStr">
-        <is>
-          <t>exported_rc_sets/RC-MEDIUM-260907-0066.txt</t>
-        </is>
-      </c>
-      <c r="P74" s="2" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>RC-ELITE-260726-0030</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>elite</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>Anthropology &amp; Archaeology</t>
-        </is>
-      </c>
-      <c r="D75" s="6" t="inlineStr">
-        <is>
-          <t>rejected_novelty</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G75" s="2" t="inlineStr">
-        <is>
-          <t>+2 questions</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I75" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J75" s="2" t="n">
-        <v>0.6870000000000001</v>
-      </c>
-      <c r="K75" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="n">
-        <v>500</v>
-      </c>
-      <c r="M75" s="2" t="inlineStr">
-        <is>
-          <t>exported_rc_sets/RC-ELITE-260726-0030.txt</t>
-        </is>
-      </c>
-      <c r="N75" s="2" t="inlineStr">
-        <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260726-0030.txt</t>
-        </is>
-      </c>
-      <c r="O75" s="2" t="inlineStr">
-        <is>
-          <t>exported_rc_sets/RC-ELITE-260726-0030.txt</t>
-        </is>
-      </c>
-      <c r="P75" s="2" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>RC-MEDIUM-260904-0059</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>Science &amp; Technology</t>
-        </is>
-      </c>
-      <c r="D76" s="6" t="inlineStr">
-        <is>
-          <t>rejected_novelty</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I76" s="2" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="J76" s="2" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="K76" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="L76" s="2" t="n">
-        <v>568</v>
-      </c>
-      <c r="M76" s="2" t="inlineStr">
-        <is>
-          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260904-0059.txt</t>
-        </is>
-      </c>
-      <c r="N76" s="2" t="inlineStr">
-        <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-MEDIUM-260904-0059.txt</t>
-        </is>
-      </c>
-      <c r="O76" s="2" t="inlineStr">
-        <is>
-          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260904-0059.txt</t>
-        </is>
-      </c>
-      <c r="P76" s="2" t="inlineStr">
-        <is>
-          <t>only ever exported into flagged_similar (novelty-flagged)</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>RC-MANUAL-260708-10</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>Science &amp; Technology</t>
-        </is>
-      </c>
-      <c r="D77" s="6" t="inlineStr">
-        <is>
-          <t>unrated</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t>+2 questions</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr"/>
-      <c r="I77" s="2" t="inlineStr"/>
-      <c r="J77" s="2" t="inlineStr"/>
-      <c r="K77" s="2" t="inlineStr"/>
-      <c r="L77" s="2" t="n">
-        <v>384</v>
-      </c>
-      <c r="M77" s="2" t="inlineStr">
-        <is>
-          <t>exported_rc_sets/RC-MANUAL-260708-10_medium.txt</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="inlineStr">
-        <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-MANUAL-260708-10_medium.txt</t>
-        </is>
-      </c>
-      <c r="O77" s="2" t="inlineStr">
-        <is>
-          <t>exported_rc_sets/RC-MANUAL-260708-10_medium.txt</t>
-        </is>
-      </c>
-      <c r="P77" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">legacy/manual export, not in the engine DB; Source: manual generator (evolutionary metaphors for technology); word count 384 (medium band); tier assigned via word count + complexity read 2026-07-12; user-vetted before shipping; placed into new </t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>RC_E_0705_2</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>elite</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>Sociology &amp; Culture</t>
-        </is>
-      </c>
-      <c r="D78" s="5" t="inlineStr">
-        <is>
-          <t>blocked</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t>+2 questions</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>8.8</t>
-        </is>
-      </c>
-      <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="inlineStr"/>
-      <c r="K78" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="L78" s="2" t="n">
-        <v>580</v>
-      </c>
-      <c r="M78" s="2" t="inlineStr">
-        <is>
-          <t>exported_rc_sets/RC_E_0705_2.txt</t>
-        </is>
-      </c>
-      <c r="N78" s="2" t="inlineStr">
-        <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC_E_0705_2.txt</t>
-        </is>
-      </c>
-      <c r="O78" s="2" t="inlineStr">
-        <is>
-          <t>exported_rc_sets/RC_E_0705_2.txt</t>
-        </is>
-      </c>
-      <c r="P78" s="2" t="inlineStr">
-        <is>
-          <t>BLOCKED - you marked this not-sent: length-bias FAILED: correct answer longest in 4/6 questions, incl. thesis Q1 -- needs content fix before shipping; legacy/manual export, not in the engine DB</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>RC_E_0705_5</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>elite</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>Language &amp; Linguistics</t>
-        </is>
-      </c>
-      <c r="D79" s="5" t="inlineStr">
-        <is>
-          <t>blocked</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G79" s="2" t="inlineStr">
-        <is>
-          <t>+2 questions</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>8.8</t>
-        </is>
-      </c>
-      <c r="I79" s="2" t="inlineStr"/>
-      <c r="J79" s="2" t="inlineStr"/>
-      <c r="K79" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="L79" s="2" t="n">
-        <v>589</v>
-      </c>
-      <c r="M79" s="2" t="inlineStr">
-        <is>
-          <t>exported_rc_sets/RC_E_0705_5.txt</t>
-        </is>
-      </c>
-      <c r="N79" s="2" t="inlineStr">
-        <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC_E_0705_5.txt</t>
-        </is>
-      </c>
-      <c r="O79" s="2" t="inlineStr">
-        <is>
-          <t>exported_rc_sets/RC_E_0705_5.txt</t>
-        </is>
-      </c>
-      <c r="P79" s="2" t="inlineStr">
-        <is>
           <t>BLOCKED - you marked this not-sent: length-bias FAILED: correct answer longest in 5/6 questions, incl. thesis Q1 -- needs content fix before shipping; legacy/manual export, not in the engine DB</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>rc_hard_0004</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>Anthropology &amp; Archaeology</t>
-        </is>
-      </c>
-      <c r="D80" s="5" t="inlineStr">
-        <is>
-          <t>blocked</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G80" s="2" t="inlineStr">
-        <is>
-          <t>+2 questions</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>8.4</t>
-        </is>
-      </c>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr"/>
-      <c r="K80" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-04</t>
-        </is>
-      </c>
-      <c r="L80" s="2" t="n">
-        <v>485</v>
-      </c>
-      <c r="M80" s="2" t="inlineStr">
-        <is>
-          <t>exported_rc_sets/rc_hard_0004.txt</t>
-        </is>
-      </c>
-      <c r="N80" s="2" t="inlineStr">
-        <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\rc_hard_0004.txt</t>
-        </is>
-      </c>
-      <c r="O80" s="2" t="inlineStr">
-        <is>
-          <t>exported_rc_sets/rc_hard_0004.txt</t>
-        </is>
-      </c>
-      <c r="P80" s="2" t="inlineStr">
-        <is>
-          <t>BLOCKED - you marked this not-sent: length-bias FAILED: correct answer longest in 6/6 questions (all), incl. thesis Q1 -- needs content fix before shipping; legacy/manual export, not in the engine DB</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>RC_H_0705_3</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>Medicine &amp; Health</t>
-        </is>
-      </c>
-      <c r="D81" s="5" t="inlineStr">
-        <is>
-          <t>blocked</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G81" s="2" t="inlineStr">
-        <is>
-          <t>+2 questions</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>8.2</t>
-        </is>
-      </c>
-      <c r="I81" s="2" t="inlineStr"/>
-      <c r="J81" s="2" t="inlineStr"/>
-      <c r="K81" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="n">
-        <v>515</v>
-      </c>
-      <c r="M81" s="2" t="inlineStr">
-        <is>
-          <t>exported_rc_sets/RC_H_0705_3.txt</t>
-        </is>
-      </c>
-      <c r="N81" s="2" t="inlineStr">
-        <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC_H_0705_3.txt</t>
-        </is>
-      </c>
-      <c r="O81" s="2" t="inlineStr">
-        <is>
-          <t>exported_rc_sets/RC_H_0705_3.txt</t>
-        </is>
-      </c>
-      <c r="P81" s="2" t="inlineStr">
-        <is>
-          <t>BLOCKED - you marked this not-sent: length-bias FAILED: correct answer longest in 5/6 questions, incl. thesis Q1 -- needs content fix before shipping; legacy/manual export, not in the engine DB</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:P81"/>
+  <autoFilter ref="A1:P71"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11477,7 +11459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -11810,8 +11792,46 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Week_8_12_09</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>renamed (RC_TIER_YYMMDD_NN)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J8"/>
+  <autoFilter ref="A1:J9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11884,10 +11904,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>3</v>
@@ -11899,94 +11919,94 @@
         <v>2</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>19.2</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Science &amp; Technology</t>
+          <t>Politics, Law &amp; Policy</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>10.3</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Anthropology &amp; Archaeology</t>
+          <t>Science &amp; Technology</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Politics, Law &amp; Policy</t>
+          <t>Anthropology &amp; Archaeology</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -11996,25 +12016,25 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>2</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>7.7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -12024,25 +12044,25 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>7.7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -12052,16 +12072,16 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" s="2" t="n">
         <v>5</v>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>6</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>2</v>
@@ -12070,17 +12090,17 @@
         <v>1</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Psychology</t>
+          <t>Sociology &amp; Culture</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>4</v>
@@ -12098,119 +12118,119 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Sociology &amp; Culture</t>
+          <t>Economics &amp; Business</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>5</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Economics &amp; Business</t>
+          <t>Life Sciences &amp; Environment</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Life Sciences &amp; Environment</t>
+          <t>Medicine &amp; Health</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G12" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="H12" s="2" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Medicine &amp; Health</t>
+          <t>Psychology</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C13" s="2" t="n">
-        <v>8</v>
-      </c>
       <c r="D13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>3</v>
-      </c>
       <c r="H13" s="2" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="14">
@@ -12220,10 +12240,10 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>2</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>1</v>
@@ -12235,10 +12255,10 @@
         <v>1</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="15">
@@ -12266,7 +12286,7 @@
         <v>1</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="16">
@@ -12276,22 +12296,22 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="D16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="G16" s="2" t="n">
         <v>18</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>22</v>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
     </row>
@@ -12674,7 +12694,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>no file in the live week folder; returned to the available bench</t>
+          <t>no file in the live week folder; the set itself shipped under another id</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12711,7 +12731,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>no file in the live week folder; returned to the available bench</t>
+          <t>no file in the live week folder; the set itself shipped under another id</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -13007,7 +13027,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>no file in the live week folder; returned to the available bench</t>
+          <t>no file in the live week folder; the set itself shipped under another id</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -13093,7 +13113,7 @@
         </is>
       </c>
       <c r="B4" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -13103,7 +13123,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6">
@@ -13113,7 +13133,7 @@
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7">
@@ -13123,7 +13143,7 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -13146,7 +13166,7 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11">
@@ -13156,7 +13176,7 @@
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12">
@@ -13166,7 +13186,7 @@
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
@@ -13176,7 +13196,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -13186,7 +13206,7 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
@@ -13239,7 +13259,7 @@
         </is>
       </c>
       <c r="B20" s="9" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21">
@@ -13249,7 +13269,7 @@
         </is>
       </c>
       <c r="B21" s="9" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
@@ -13259,7 +13279,7 @@
         </is>
       </c>
       <c r="B22" s="9" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23">
@@ -13272,7 +13292,7 @@
         </is>
       </c>
       <c r="B24" s="9" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25">
@@ -13282,7 +13302,7 @@
         </is>
       </c>
       <c r="B25" s="9" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26">
@@ -13292,7 +13312,7 @@
         </is>
       </c>
       <c r="B26" s="9" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27">
@@ -13305,7 +13325,7 @@
         </is>
       </c>
       <c r="B28" s="9" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="29">
@@ -13315,7 +13335,7 @@
         </is>
       </c>
       <c r="B29" s="9" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="30">

--- a/RC_Shipping_Tracker.xlsx
+++ b/RC_Shipping_Tracker.xlsx
@@ -11,15 +11,17 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Available" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By Week" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Genre Mix" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reconciliation" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Folder vs Sent" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reconciliation" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Shipped'!$A$1:$O$89</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Available'!$A$1:$P$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Shipped'!$A$1:$P$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Available'!$A$1:$P$70</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Week'!$A$1:$J$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Genre Mix'!$A$1:$H$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Reconciliation'!$A$1:$G$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Folder vs Sent'!$A$1:$E$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Reconciliation'!$A$1:$G$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -485,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O89"/>
+  <dimension ref="A1:P92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -499,10 +501,11 @@
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="7" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="44" customWidth="1" min="12" max="12"/>
-    <col width="60" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="46" customWidth="1" min="15" max="15"/>
+    <col width="34" customWidth="1" min="12" max="12"/>
+    <col width="44" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="46" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -563,20 +566,25 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>Delivery</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>Export_File</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Delivered_Files</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Old_Tracker_ID</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -636,20 +644,25 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
+          <t>emailed</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
           <t>exported_rc_sets/RC-ELITE-260706-0006.txt</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>Week_1_25_07/Elite/Text/RC_ELITE_260725_01.txt | Week_1_25_07/Elite/word/RC_ELITE_260725_01.docx</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>RC-ELITE-260706-0006</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>Length-bias fixed; local file corrected 2026-07-08 (was stale pre-fix wording) | ship-format renamed to RC_ELITE_260725_01</t>
         </is>
@@ -709,20 +722,25 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
+          <t>emailed</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
           <t>exported_rc_sets/RC-ELITE-260707-0015.txt</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>Week_1_25_07/Elite/Text/RC_ELITE_260725_02.txt | Week_1_25_07/Elite/word/RC_ELITE_260725_02.docx</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>RC-ELITE-260707-0015</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>Length-bias fixed; local file corrected 2026-07-08 (was stale pre-fix wording) | ship-format renamed to RC_ELITE_260725_02</t>
         </is>
@@ -776,20 +794,25 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>emailed</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
           <t>exported_rc_sets/RC-MANUAL-260707-1_elite.txt</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>Week_1_25_07/Elite/Text/RC_ELITE_260725_03.txt | Week_1_25_07/Elite/word/RC_ELITE_260725_03.docx</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>RC-MANUAL-260707-1</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>Source: manual generator (institutional disclosure/legibility asymmetry); word count 523 (elite band); tier assigned via word count + complexity read 2026-07-12; user-vetted before shipping; placed in</t>
         </is>
@@ -849,20 +872,25 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
+          <t>emailed</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
           <t>exported_rc_sets/RC_E_0706_1.txt</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>Week_1_25_07/Elite/Text/RC_ELITE_260725_04.txt | Week_1_25_07/Elite/word/RC_ELITE_260725_04.docx</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>RC_E_0706_1</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>ship-format renamed to RC_ELITE_260725_04</t>
         </is>
@@ -916,20 +944,25 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
+          <t>emailed</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
           <t>exported_rc_sets/RC-MANUAL-260708-5_elite.txt</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>Week_1_25_07/Elite/Text/RC_ELITE_260725_05.txt | Week_1_25_07/Elite/word/RC_ELITE_260725_05.docx</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>RC-MANUAL-260708-5</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>Source: manual generator (Persian hal / Sanskrit rasa untranslatability); word count 500 (elite band); tier assigned via word count + complexity read 2026-07-12; user-vetted before shipping; placed in</t>
         </is>
@@ -989,20 +1022,25 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
+          <t>emailed</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
           <t>exported_rc_sets/RC-HARD-260706-0002.txt</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>Week_1_25_07/Hard/Text/RC_HARD_260725_01.txt | Week_1_25_07/Hard/word/RC_HARD_260725_01.docx</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>RC-HARD-260706-0002</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>Length-bias fixed; local file corrected 2026-07-08 (was stale pre-fix wording) | ship-format renamed to RC_HARD_260725_01</t>
         </is>
@@ -1056,20 +1094,25 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
+          <t>emailed</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
           <t>exported_rc_sets/RC-MANUAL-260708-8_hard.txt</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>Week_1_25_07/Hard/Text/RC_HARD_260725_02.txt | Week_1_25_07/Hard/word/RC_HARD_260725_02.docx</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>RC-MANUAL-260708-8</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>Source: manual generator (word-retrieval psycholinguistics, ~600ms); word count 455 (hard band); tier assigned via word count + complexity read 2026-07-12; user-vetted before shipping; placed into Wee</t>
         </is>
@@ -1131,20 +1174,25 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
+          <t>emailed</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
           <t>exported_rc_sets/RC_H_0705_1.txt</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>Week_1_25_07/Hard/Text/RC_HARD_260725_03.txt | Week_1_25_07/Hard/word/RC_HARD_260725_03.docx</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>RC_H_0705_1</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>ship-format renamed to RC_HARD_260725_03 | FLAGGED 2026-07-08: thesis-longest bias -- correct answer to Central Thesis (Q1) is the strictly-longest option; not caught before original ship. Already shi</t>
         </is>
@@ -1206,20 +1254,25 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
+          <t>emailed</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
           <t>exported_rc_sets/RC_H_0705_2.txt</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>Week_1_25_07/Hard/Text/RC_HARD_260725_04.txt | Week_1_25_07/Hard/word/RC_HARD_260725_04.docx</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>RC_H_0705_2</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>ship-format renamed to RC_HARD_260725_04 | FLAGGED 2026-07-08: thesis-longest bias -- correct answer to Central Thesis (Q1) is the strictly-longest option; not caught before original ship. Already shi</t>
         </is>
@@ -1273,20 +1326,25 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
+          <t>emailed</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
           <t>exported_rc_sets/RC-MANUAL-260708-11_hard.txt</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>Week_1_25_07/Hard/Text/RC_HARD_260725_05.txt | Week_1_25_07/Hard/word/RC_HARD_260725_05.docx</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>RC-MANUAL-260708-11</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>Source: manual generator (tacit vs codified expertise); word count 482 (hard band); tier assigned via word count + complexity read 2026-07-12; user-vetted before shipping; placed into Week_1 as part o</t>
         </is>
@@ -1346,20 +1404,25 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
+          <t>emailed</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
           <t>exported_rc_sets/RC-MEDIUM-260707-0003.txt</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>Week_1_25_07/Medium/Text/RC_MEDIUM_260725_01.txt | Week_1_25_07/Medium/word/RC_MEDIUM_260725_01.docx</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>RC-MEDIUM-260707-0003</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>ship-format renamed to RC_MEDIUM_260725_01</t>
         </is>
@@ -1413,20 +1476,25 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
+          <t>emailed</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
           <t>exported_rc_sets/RC-MANUAL-260708-4_medium.txt</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>Week_1_25_07/Medium/Text/RC_MEDIUM_260725_02.txt | Week_1_25_07/Medium/word/RC_MEDIUM_260725_02.docx</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>RC-MANUAL-260708-4</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>Source: manual generator ("amateurish" as verdict / etymology of contempt); word count 444 (medium band); tier assigned via word count + complexity read 2026-07-12; user-vetted before shipping; placed</t>
         </is>
@@ -1486,20 +1554,25 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
+          <t>emailed</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
           <t>exported_rc_sets/RC-ELITE-260706-0005.txt</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>Week_2_01_08/Elite/Text/RC_ELITE_260801_01.txt | Week_2_01_08/Elite/word/RC_ELITE_260801_01.docx</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>RC-ELITE-260706-0005</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>Manually approved &amp; shipped despite needs_review flag (reason not traceable in db) | ship-format renamed to RC_ELITE_260801_01</t>
         </is>
@@ -1553,20 +1626,25 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
+          <t>emailed</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
           <t>exported_rc_sets/RC-MANUAL-260708-3.txt</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>Week_2_01_08/Elite/Text/RC_ELITE_260801_02.txt | Week_2_01_08/Elite/word/RC_ELITE_260801_02.docx</t>
         </is>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>RC-ELITE-260708-0003</t>
         </is>
       </c>
-      <c r="O15" s="2" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr">
         <is>
           <t>old tracker filed this as RC-ELITE-260708-0003</t>
         </is>
@@ -1620,20 +1698,25 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
+          <t>emailed</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
           <t>exported_rc_sets/RC-MANUAL-260708-6.txt</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>Week_2_01_08/Elite/Text/RC_ELITE_260801_03.txt | Week_2_01_08/Elite/word/RC_ELITE_260801_03.docx</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>RC-ELITE-260708-0006</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>old tracker filed this as RC-ELITE-260708-0006</t>
         </is>
@@ -1687,20 +1770,25 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
+          <t>emailed</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
           <t>exported_rc_sets/RC-MANUAL-260708-9.txt</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>Week_2_01_08/Elite/Text/RC_ELITE_260801_04.txt | Week_2_01_08/Elite/word/RC_ELITE_260801_04.docx</t>
         </is>
       </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>RC-ELITE-260708-0009</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>old tracker filed this as RC-ELITE-260708-0009</t>
         </is>
@@ -1754,20 +1842,25 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
+          <t>emailed</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
           <t>exported_rc_sets/RC-MANUAL-260708-12.txt</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>Week_2_01_08/Elite/Text/RC_ELITE_260801_05.txt | Week_2_01_08/Elite/word/RC_ELITE_260801_05.docx</t>
         </is>
       </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>RC-ELITE-260708-0012</t>
         </is>
       </c>
-      <c r="O18" s="2" t="inlineStr">
+      <c r="P18" s="2" t="inlineStr">
         <is>
           <t>old tracker filed this as RC-ELITE-260708-0012</t>
         </is>
@@ -1827,20 +1920,25 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
+          <t>emailed</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
           <t>exported_rc_sets/RC-HARD-260706-0003.txt</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>Week_2_01_08/Hard/Text/RC_HARD_260801_01.txt | Week_2_01_08/Hard/word/RC_HARD_260801_01.docx</t>
         </is>
       </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>RC-HARD-260706-0003</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>passage edited after export</t>
         </is>
@@ -1894,20 +1992,25 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
+          <t>emailed</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
           <t>exported_rc_sets/RC-MANUAL-260708-2.txt</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>Week_2_01_08/Hard/Text/RC_HARD_260801_02.txt | Week_2_01_08/Hard/word/RC_HARD_260801_02.docx</t>
         </is>
       </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>RC-HARD-260708-0002</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>old tracker filed this as RC-HARD-260708-0002</t>
         </is>
@@ -1961,20 +2064,25 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
+          <t>emailed</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
           <t>manual_rc_sets/used/RC-MANUAL-260708-14_hard.txt</t>
         </is>
       </c>
-      <c r="M21" s="2" t="inlineStr">
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>Week_2_01_08/Hard/Text/RC_HARD_260801_03.txt | Week_2_01_08/Hard/word/RC_HARD_260801_03.docx</t>
         </is>
       </c>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>RC-MANUAL-260708-14</t>
         </is>
       </c>
-      <c r="O21" s="2" t="inlineStr">
+      <c r="P21" s="2" t="inlineStr">
         <is>
           <t>Source: manual generator (self-invented topic, AVOID list honored vs prior elite/medium blueprints, posture rotated to resolution_qualified); passed duplicate check, word count 500 (hard/elite boundar</t>
         </is>
@@ -2028,20 +2136,25 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
+          <t>emailed</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
           <t>exported_rc_sets/RC-MANUAL-260711-1_hard.txt</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>Week_2_01_08/Hard/Text/RC_HARD_260801_04.txt | Week_2_01_08/Hard/word/RC_HARD_260801_04.docx</t>
         </is>
       </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>RC-MANUAL-260711-1</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
         <is>
           <t>Source: manual generator (gift-giving disavowal); passed duplicate check, word count 499, length-bias clean (0/6 longest)</t>
         </is>
@@ -2095,20 +2208,25 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
+          <t>emailed</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
           <t>exported_rc_sets/RC-MANUAL-260711-2_hard.txt</t>
         </is>
       </c>
-      <c r="M23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>Week_2_01_08/Hard/Text/RC_HARD_260801_05.txt | Week_2_01_08/Hard/word/RC_HARD_260801_05.docx</t>
         </is>
       </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>RC-MANUAL-260711-2</t>
         </is>
       </c>
-      <c r="O23" s="2" t="inlineStr">
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>Source: manual generator (queue vs needs-based allocation); passed duplicate check, word count 496, length-bias clean (0/6 longest)</t>
         </is>
@@ -2162,20 +2280,25 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
+          <t>emailed</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
           <t>exported_rc_sets/RC-MANUAL-260708-1.txt</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr">
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>Week_2_01_08/Medium/Text/RC_MEDIUM_260801_01.txt | Week_2_01_08/Medium/word/RC_MEDIUM_260801_01.docx</t>
         </is>
       </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>RC-MEDIUM-260708-0001</t>
         </is>
       </c>
-      <c r="O24" s="2" t="inlineStr">
+      <c r="P24" s="2" t="inlineStr">
         <is>
           <t>old tracker filed this as RC-MEDIUM-260708-0001</t>
         </is>
@@ -2229,20 +2352,25 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
+          <t>emailed</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
           <t>exported_rc_sets/RC-MANUAL-260711-3_medium.txt</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr">
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>Week_2_01_08/Medium/Text/RC_MEDIUM_260801_02.txt | Week_2_01_08/Medium/word/RC_MEDIUM_260801_02.docx</t>
         </is>
       </c>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>RC-MANUAL-260711-3</t>
         </is>
       </c>
-      <c r="O25" s="2" t="inlineStr">
+      <c r="P25" s="2" t="inlineStr">
         <is>
           <t>Source: manual generator (ruin preservation as composition); passed duplicate check, word count 417, length-bias clean (0/6 longest)</t>
         </is>
@@ -2302,20 +2430,25 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
+          <t>emailed</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
           <t>exported_rc_sets/RC-ELITE-260706-0010.txt</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>Week_3_08_08/Elite/Text/RC_ELITE_260808_01.txt | Week_3_08_08/Elite/word/RC_ELITE_260808_01.docx</t>
         </is>
       </c>
-      <c r="N26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>RC-ELITE-260706-0010</t>
         </is>
       </c>
-      <c r="O26" s="2" t="inlineStr">
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>Moved from Week_2_01_08 due to elite quota overflow | ship-format renamed to RC_ELITE_260808_01 | Re-verified 2026-07-11: duplicate clean, word count 490, length-bias clean (2/6, thesis not longest) -</t>
         </is>
@@ -2369,20 +2502,25 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
+          <t>emailed</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
           <t>exported_rc_sets/RC-MANUAL-260708-13_elite.txt</t>
         </is>
       </c>
-      <c r="M27" s="2" t="inlineStr">
+      <c r="N27" s="2" t="inlineStr">
         <is>
           <t>Week_3_08_08/Elite/Text/RC_ELITE_260808_02.txt | Week_3_08_08/Elite/word/RC_ELITE_260808_02.docx</t>
         </is>
       </c>
-      <c r="N27" s="2" t="inlineStr">
+      <c r="O27" s="2" t="inlineStr">
         <is>
           <t>RC-MANUAL-260708-13</t>
         </is>
       </c>
-      <c r="O27" s="2" t="inlineStr">
+      <c r="P27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Source: manual generator (audit culture / measurement critique); word count 522 (elite band); previously flagged failing length-bias, re-verified 2026-07-12: 1/6 longest (Q5), thesis (Q1) not longest </t>
         </is>
@@ -2436,20 +2574,25 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
+          <t>emailed</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
           <t>exported_rc_sets/RC-MANUAL-260708-15_elite.txt</t>
         </is>
       </c>
-      <c r="M28" s="2" t="inlineStr">
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>Week_3_08_08/Elite/Text/RC_ELITE_260808_03.txt | Week_3_08_08/Elite/word/RC_ELITE_260808_03.docx</t>
         </is>
       </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>RC-MANUAL-260708-15</t>
         </is>
       </c>
-      <c r="O28" s="2" t="inlineStr">
+      <c r="P28" s="2" t="inlineStr">
         <is>
           <t>Source: manual generator (calibrated confidence in expertise); word count 520 (elite band); tier assigned via word count + complexity read 2026-07-12; user-vetted before shipping; placed into Week_3 a</t>
         </is>
@@ -2503,20 +2646,25 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
+          <t>emailed</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
           <t>exported_rc_sets/RC_ELITE_APPROVED.txt</t>
         </is>
       </c>
-      <c r="M29" s="2" t="inlineStr">
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>Week_3_08_08/Elite/Text/RC_ELITE_260808_04.txt | Week_3_08_08/Elite/word/RC_ELITE_260808_04.docx</t>
         </is>
       </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>RC_ELITE_260708_0001</t>
         </is>
       </c>
-      <c r="O29" s="2" t="inlineStr">
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>old tracker filed this as RC_ELITE_260708_0001</t>
         </is>
@@ -2576,20 +2724,25 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
+          <t>emailed</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
           <t>exported_rc_sets/RC-ELITE-260712-0029.txt</t>
         </is>
       </c>
-      <c r="M30" s="2" t="inlineStr">
+      <c r="N30" s="2" t="inlineStr">
         <is>
           <t>Week_3_08_08/Elite/Text/RC_ELITE_260808_05.txt | Week_3_08_08/Elite/word/RC_ELITE_260808_05.docx</t>
         </is>
       </c>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>RC-ELITE-260712-0029</t>
         </is>
       </c>
-      <c r="O30" s="2" t="inlineStr">
+      <c r="P30" s="2" t="inlineStr">
         <is>
           <t>Pipeline approved (score 8.8); passed duplicate check, word count 563 (13 over elite band, within tolerance), length-bias clean (1/6, thesis not longest)</t>
         </is>
@@ -2649,20 +2802,25 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
+          <t>emailed</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
           <t>exported_rc_sets/RC-HARD-260712-0010.txt</t>
         </is>
       </c>
-      <c r="M31" s="2" t="inlineStr">
+      <c r="N31" s="2" t="inlineStr">
         <is>
           <t>Week_3_08_08/Hard/Text/RC_HARD_260808_01.txt | Week_3_08_08/Hard/word/RC_HARD_260808_01.docx</t>
         </is>
       </c>
-      <c r="N31" s="2" t="inlineStr">
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t>RC-HARD-260712-0010</t>
         </is>
       </c>
-      <c r="O31" s="2" t="inlineStr">
+      <c r="P31" s="2" t="inlineStr">
         <is>
           <t>Pipeline approved (score 8.8); passed duplicate check, word count 500, length-bias clean (0/6 longest)</t>
         </is>
@@ -2722,20 +2880,25 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
+          <t>emailed</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
           <t>exported_rc_sets/RC-HARD-260712-0013.txt</t>
         </is>
       </c>
-      <c r="M32" s="2" t="inlineStr">
+      <c r="N32" s="2" t="inlineStr">
         <is>
           <t>Week_3_08_08/Hard/Text/RC_HARD_260808_02.txt | Week_3_08_08/Hard/word/RC_HARD_260808_02.docx</t>
         </is>
       </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>RC-HARD-260712-0013</t>
         </is>
       </c>
-      <c r="O32" s="2" t="inlineStr">
+      <c r="P32" s="2" t="inlineStr">
         <is>
           <t>Pipeline approved (score 8.8); passed duplicate check, word count 471, length-bias clean (1/6, thesis not longest)</t>
         </is>
@@ -2795,20 +2958,25 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
+          <t>emailed</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
           <t>exported_rc_sets/RC-HARD-260712-0009.txt</t>
         </is>
       </c>
-      <c r="M33" s="2" t="inlineStr">
+      <c r="N33" s="2" t="inlineStr">
         <is>
           <t>Week_3_08_08/Hard/Text/RC_HARD_260808_03.txt | Week_3_08_08/Hard/word/RC_HARD_260808_03.docx</t>
         </is>
       </c>
-      <c r="N33" s="2" t="inlineStr">
+      <c r="O33" s="2" t="inlineStr">
         <is>
           <t>RC-HARD-260712-0009</t>
         </is>
       </c>
-      <c r="O33" s="2" t="inlineStr">
+      <c r="P33" s="2" t="inlineStr">
         <is>
           <t>Was needs_review, user approved 2026-07-12; passed duplicate check, word count 475 (hard band), length-bias clean (1/6, thesis not longest); NOTE: source .txt in exported_rc_sets was found truncated o</t>
         </is>
@@ -2862,20 +3030,25 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
+          <t>emailed</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
           <t>exported_rc_sets/RC-MANUAL-260711-5_hard.txt</t>
         </is>
       </c>
-      <c r="M34" s="2" t="inlineStr">
+      <c r="N34" s="2" t="inlineStr">
         <is>
           <t>Week_3_08_08/Hard/Text/RC_HARD_260808_04.txt | Week_3_08_08/Hard/word/RC_HARD_260808_04.docx</t>
         </is>
       </c>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="O34" s="2" t="inlineStr">
         <is>
           <t>RC-MANUAL-260711-5</t>
         </is>
       </c>
-      <c r="O34" s="2" t="inlineStr">
+      <c r="P34" s="2" t="inlineStr">
         <is>
           <t>Source: manual generator (boredom as modern word); word count 490 (hard band); user-vetted before shipping; placed into Week_3 open slot as part of manual/pipeline mixing plan</t>
         </is>
@@ -2929,20 +3102,25 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
+          <t>emailed</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
           <t>exported_rc_sets/RC-MANUAL-260711-6_hard.txt</t>
         </is>
       </c>
-      <c r="M35" s="2" t="inlineStr">
+      <c r="N35" s="2" t="inlineStr">
         <is>
           <t>Week_3_08_08/Hard/Text/RC_HARD_260808_05.txt | Week_3_08_08/Hard/word/RC_HARD_260808_05.docx</t>
         </is>
       </c>
-      <c r="N35" s="2" t="inlineStr">
+      <c r="O35" s="2" t="inlineStr">
         <is>
           <t>RC-MANUAL-260711-6</t>
         </is>
       </c>
-      <c r="O35" s="2" t="inlineStr">
+      <c r="P35" s="2" t="inlineStr">
         <is>
           <t>Source: manual generator (proverbs / contradiction); word count 480 (hard band); user-vetted before shipping; placed into Week_3 open slot as part of manual/pipeline mixing plan</t>
         </is>
@@ -2996,20 +3174,25 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
+          <t>emailed</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
           <t>exported_rc_sets/RC-MANUAL-260711-4_medium.txt</t>
         </is>
       </c>
-      <c r="M36" s="2" t="inlineStr">
+      <c r="N36" s="2" t="inlineStr">
         <is>
           <t>Week_3_08_08/Medium/Text/RC_MEDIUM_260808_01.txt | Week_3_08_08/Medium/word/RC_MEDIUM_260808_01.docx</t>
         </is>
       </c>
-      <c r="N36" s="2" t="inlineStr">
+      <c r="O36" s="2" t="inlineStr">
         <is>
           <t>RC-MANUAL-260711-4</t>
         </is>
       </c>
-      <c r="O36" s="2" t="inlineStr">
+      <c r="P36" s="2" t="inlineStr">
         <is>
           <t>Source: manual generator (reversibility and deliberation); passed duplicate check, word count 454 (4 over medium band, within tolerance), length-bias clean (0/6 longest); moved to Week_3 as Week_2 med</t>
         </is>
@@ -3069,20 +3252,25 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
+          <t>emailed</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
           <t>exported_rc_sets/RC-MEDIUM-260712-0020.txt</t>
         </is>
       </c>
-      <c r="M37" s="2" t="inlineStr">
+      <c r="N37" s="2" t="inlineStr">
         <is>
           <t>Week_3_08_08/Medium/Text/RC_MEDIUM_260808_02.txt | Week_3_08_08/Medium/word/RC_MEDIUM_260808_02.docx</t>
         </is>
       </c>
-      <c r="N37" s="2" t="inlineStr">
+      <c r="O37" s="2" t="inlineStr">
         <is>
           <t>RC-MEDIUM-260712-0020</t>
         </is>
       </c>
-      <c r="O37" s="2" t="inlineStr">
+      <c r="P37" s="2" t="inlineStr">
         <is>
           <t>Pipeline approved (score 8.4); passed duplicate check, word count 371 (29 under medium band, flagged), length-bias clean (1/6, thesis Q5 not longest)</t>
         </is>
@@ -3142,20 +3330,25 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
+          <t>staged, never emailed</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
           <t>exported_rc_sets/RC-ELITE-260712-0028.txt</t>
         </is>
       </c>
-      <c r="M38" s="2" t="inlineStr">
+      <c r="N38" s="2" t="inlineStr">
         <is>
           <t>Week_4_15_08/Elite/Text/RC_ELITE_260815_01.txt | Week_4_15_08/Elite/word/RC_ELITE_260815_01.docx</t>
         </is>
       </c>
-      <c r="N38" s="2" t="inlineStr">
+      <c r="O38" s="2" t="inlineStr">
         <is>
           <t>RC-ELITE-260712-0028</t>
         </is>
       </c>
-      <c r="O38" s="2" t="inlineStr">
+      <c r="P38" s="2" t="inlineStr">
         <is>
           <t>Was needs_review, user approved 2026-07-12; passed duplicate check, word count 514 (elite band), length-bias clean (0/6 longest); Week_1-3 elite quota all full (5/5 each), new Week_4_15_08 folder crea</t>
         </is>
@@ -3209,20 +3402,25 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
+          <t>staged, never emailed</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
           <t>exported_rc_sets/RC-MANUAL-260708-16_elite.txt</t>
         </is>
       </c>
-      <c r="M39" s="2" t="inlineStr">
+      <c r="N39" s="2" t="inlineStr">
         <is>
           <t>Week_4_15_08/Elite/Text/RC_ELITE_260815_02.txt | Week_4_15_08/Elite/word/RC_ELITE_260815_02.docx</t>
         </is>
       </c>
-      <c r="N39" s="2" t="inlineStr">
+      <c r="O39" s="2" t="inlineStr">
         <is>
           <t>RC-MANUAL-260708-16</t>
         </is>
       </c>
-      <c r="O39" s="2" t="inlineStr">
+      <c r="P39" s="2" t="inlineStr">
         <is>
           <t>Source: manual generator (epoch-naming / historicism); word count 553 (elite band); previously flagged failing length-bias (Q1 &amp; Q5 longest), re-verified 2026-07-12 post-fix: 1/6 longest (Q5 only), th</t>
         </is>
@@ -3284,20 +3482,25 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
+          <t>emailed</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
           <t>exported_rc_sets/RC_E_0705_4.txt</t>
         </is>
       </c>
-      <c r="M40" s="2" t="inlineStr">
+      <c r="N40" s="2" t="inlineStr">
         <is>
           <t>Week_4_15_08/Elite/Text/RC_ELITE_260815_03.txt | Week_4_15_08/Elite/word/RC_ELITE_260815_03.docx</t>
         </is>
       </c>
-      <c r="N40" s="2" t="inlineStr">
+      <c r="O40" s="2" t="inlineStr">
         <is>
           <t>RC_E_0705_4</t>
         </is>
       </c>
-      <c r="O40" s="2" t="inlineStr">
+      <c r="P40" s="2" t="inlineStr">
         <is>
           <t>ship-format renamed to RC_ELITE_260725_03 | FLAGGED 2026-07-08: thesis-longest bias -- correct answer to Central Thesis (Q1) is the strictly-longest option; not caught before original ship. Already sh</t>
         </is>
@@ -3359,20 +3562,25 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
+          <t>emailed</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
           <t>exported_rc_sets/rc_elite_0005.txt</t>
         </is>
       </c>
-      <c r="M41" s="2" t="inlineStr">
+      <c r="N41" s="2" t="inlineStr">
         <is>
           <t>Week_4_15_08/Elite/Text/RC_ELITE_260815_04.txt | Week_4_15_08/Elite/word/RC_ELITE_260815_04.docx</t>
         </is>
       </c>
-      <c r="N41" s="2" t="inlineStr">
+      <c r="O41" s="2" t="inlineStr">
         <is>
           <t>rc_elite_0005</t>
         </is>
       </c>
-      <c r="O41" s="2" t="inlineStr">
+      <c r="P41" s="2" t="inlineStr">
         <is>
           <t>passage edited after export</t>
         </is>
@@ -3434,20 +3642,25 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
+          <t>emailed</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
           <t>exported_rc_sets/RC_E_0705_6.txt</t>
         </is>
       </c>
-      <c r="M42" s="2" t="inlineStr">
+      <c r="N42" s="2" t="inlineStr">
         <is>
           <t>Week_4_15_08/Elite/Text/RC_ELITE_260815_05.txt | Week_4_15_08/Elite/word/RC_ELITE_260815_05.docx</t>
         </is>
       </c>
-      <c r="N42" s="2" t="inlineStr">
+      <c r="O42" s="2" t="inlineStr">
         <is>
           <t>RC_ELITE_260705_0003</t>
         </is>
       </c>
-      <c r="O42" s="2" t="inlineStr">
+      <c r="P42" s="2" t="inlineStr">
         <is>
           <t>old tracker filed this as RC_ELITE_260705_0003</t>
         </is>
@@ -3501,20 +3714,25 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
+          <t>emailed</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
           <t>exported_rc_sets/RC-MANUAL-260711-7_hard.txt</t>
         </is>
       </c>
-      <c r="M43" s="2" t="inlineStr">
+      <c r="N43" s="2" t="inlineStr">
         <is>
           <t>Week_4_15_08/Hard/Text/RC_HARD_260815_01.txt | Week_4_15_08/Hard/word/RC_HARD_260815_01.docx</t>
         </is>
       </c>
-      <c r="N43" s="2" t="inlineStr">
+      <c r="O43" s="2" t="inlineStr">
         <is>
           <t>RC-MANUAL-260711-7</t>
         </is>
       </c>
-      <c r="O43" s="2" t="inlineStr">
+      <c r="P43" s="2" t="inlineStr">
         <is>
           <t>Source: manual generator (technical standards lock-in); word count 473 (hard band); user-vetted before shipping; placed into new Week_4 as part of manual/pipeline mixing plan</t>
         </is>
@@ -3568,20 +3786,25 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
+          <t>staged, never emailed</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
           <t>exported_rc_sets/RC-MANUAL-260711-8_hard.txt</t>
         </is>
       </c>
-      <c r="M44" s="2" t="inlineStr">
+      <c r="N44" s="2" t="inlineStr">
         <is>
           <t>Week_4_15_08/Hard/Text/RC_HARD_260815_02.txt | Week_4_15_08/Hard/word/RC_HARD_260815_02.docx</t>
         </is>
       </c>
-      <c r="N44" s="2" t="inlineStr">
+      <c r="O44" s="2" t="inlineStr">
         <is>
           <t>RC-MANUAL-260711-8</t>
         </is>
       </c>
-      <c r="O44" s="2" t="inlineStr">
+      <c r="P44" s="2" t="inlineStr">
         <is>
           <t>Source: manual generator (posthumous obligation / wills); word count 479 (hard band); user-vetted before shipping; placed into new Week_4 as part of manual/pipeline mixing plan</t>
         </is>
@@ -3635,20 +3858,25 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
+          <t>emailed</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
           <t>exported_rc_sets/RC_MEDIUM_005_MN.txt</t>
         </is>
       </c>
-      <c r="M45" s="2" t="inlineStr">
+      <c r="N45" s="2" t="inlineStr">
         <is>
           <t>Week_4_15_08/Hard/Text/RC_HARD_260815_03.txt | Week_4_15_08/Hard/word/RC_HARD_260815_03.docx</t>
         </is>
       </c>
-      <c r="N45" s="2" t="inlineStr">
+      <c r="O45" s="2" t="inlineStr">
         <is>
           <t>RC_HARD_005_MN</t>
         </is>
       </c>
-      <c r="O45" s="2" t="inlineStr">
+      <c r="P45" s="2" t="inlineStr">
         <is>
           <t>old tracker filed this as RC_HARD_005_MN</t>
         </is>
@@ -3710,20 +3938,25 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
+          <t>emailed</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
           <t>exported_rc_sets/RC_H_0705_4.txt</t>
         </is>
       </c>
-      <c r="M46" s="2" t="inlineStr">
+      <c r="N46" s="2" t="inlineStr">
         <is>
           <t>Week_4_15_08/Hard/Text/RC_HARD_260815_04.txt | Week_4_15_08/Hard/word/RC_HARD_260815_04.docx</t>
         </is>
       </c>
-      <c r="N46" s="2" t="inlineStr">
+      <c r="O46" s="2" t="inlineStr">
         <is>
           <t>RC_H_0705_4</t>
         </is>
       </c>
-      <c r="O46" s="2" t="inlineStr">
+      <c r="P46" s="2" t="inlineStr">
         <is>
           <t>passage edited after export</t>
         </is>
@@ -3783,20 +4016,25 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
+          <t>staged, never emailed</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
           <t>exported_rc_sets/RC-HARD-260726-0019.txt</t>
         </is>
       </c>
-      <c r="M47" s="2" t="inlineStr">
+      <c r="N47" s="2" t="inlineStr">
         <is>
           <t>Week_4_15_08/Hard/Text/RC_HARD_260815_05.txt | Week_4_15_08/Hard/word/RC_HARD_260815_05.docx</t>
         </is>
       </c>
-      <c r="N47" s="2" t="inlineStr">
+      <c r="O47" s="2" t="inlineStr">
         <is>
           <t>RC-HARD-260726-0019</t>
         </is>
       </c>
-      <c r="O47" s="2" t="inlineStr">
+      <c r="P47" s="2" t="inlineStr">
         <is>
           <t>Was needs_review, user approved 2026-07-26; passed duplicate check, word count 545 (45 over hard band, flagged), length-bias clean (2/6 longest -- Q2,Q6 -- thesis Q1 not longest); placed into Week_4 (</t>
         </is>
@@ -3815,7 +4053,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>RC_MEDIUM_260815_01</t>
+          <t>RC_MEDIUM_260811_0025</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
@@ -3823,7 +4061,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>RC-MANUAL-260708-7</t>
+          <t>RC-MEDIUM-260811-0025</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -3833,39 +4071,42 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Economics &amp; Business</t>
+          <t>Philosophy &amp; Ethics</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr"/>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>needs_review</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>8.6</v>
+      </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>passage exact</t>
+          <t>passage fuzzy 1.00</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-MANUAL-260708-7_medium.txt</t>
+          <t>emailed, never filed in the folder</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>Week_4_15_08/Medium/Text/RC_MEDIUM_260815_01.txt | Week_4_15_08/Medium/word/RC_MEDIUM_260815_01.docx</t>
-        </is>
-      </c>
-      <c r="N48" s="2" t="inlineStr">
-        <is>
-          <t>RC-MANUAL-260708-7</t>
-        </is>
-      </c>
-      <c r="O48" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Source: manual generator (two Adam Smiths / inheritance dispute); word count 429 (medium band); tier assigned via word count + complexity read 2026-07-12; user-vetted before shipping; placed into new </t>
+          <t>exported_rc_sets/RC-MEDIUM-260811-0025.txt</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr"/>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>passage edited after export</t>
         </is>
       </c>
     </row>
@@ -3882,7 +4123,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>RC_MEDIUM_260815_02</t>
+          <t>RC_MEDIUM_260811_0027</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
@@ -3890,7 +4131,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>rc_medium_0003</t>
+          <t>RC-MEDIUM-260811-0027</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -3900,64 +4141,59 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Anthropology &amp; Archaeology</t>
+          <t>Economics &amp; Business</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>Legacy</t>
-        </is>
-      </c>
-      <c r="I49" s="3" t="inlineStr">
-        <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>8.6</t>
-        </is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>needs_review</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="n">
+        <v>8.6</v>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>passage exact</t>
+          <t>passage fuzzy 0.99</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/rc_medium_0003.txt</t>
+          <t>emailed, never filed in the folder</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>Week_4_15_08/Medium/Text/RC_MEDIUM_260815_02.txt | Week_4_15_08/Medium/word/RC_MEDIUM_260815_02.docx</t>
-        </is>
-      </c>
-      <c r="N49" s="2" t="inlineStr">
-        <is>
-          <t>rc_medium_0003</t>
-        </is>
-      </c>
-      <c r="O49" s="2" t="inlineStr">
-        <is>
-          <t>ship-format renamed to RC_MEDIUM_260725_02 | FLAGGED 2026-07-08: thesis-longest bias -- correct answer to Central Thesis (Q1) is the strictly-longest option; not caught before original ship. Already s</t>
+          <t>exported_rc_sets/RC-MEDIUM-260811-0027.txt</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr"/>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>passage edited after export</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Week_5_22_08</t>
+          <t>Week_4_15_08</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260821-0048</t>
+          <t>RC_MEDIUM_260815_01</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
@@ -3965,12 +4201,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260821-0048</t>
+          <t>RC-MANUAL-260708-7</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>elite</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -3980,17 +4216,11 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-      <c r="I50" s="4" t="inlineStr">
-        <is>
-          <t>needs_review</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="n">
-        <v>8.6</v>
-      </c>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr">
         <is>
           <t>passage exact</t>
@@ -3998,96 +4228,100 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/post_housevoice_fix/2026-08-22-selected-10/v2/RC-ELITE-260821-0048.txt</t>
+          <t>emailed</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>Week_5_22_08/RC-ELITE-260821-0048.docx</t>
-        </is>
-      </c>
-      <c r="N50" s="2" t="inlineStr"/>
-      <c r="O50" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/RC-MANUAL-260708-7_medium.txt</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>Week_4_15_08/Medium/Text/RC_MEDIUM_260815_01.txt | Week_4_15_08/Medium/word/RC_MEDIUM_260815_01.docx</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>RC-MANUAL-260708-7</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Source: manual generator (two Adam Smiths / inheritance dispute); word count 429 (medium band); tier assigned via word count + complexity read 2026-07-12; user-vetted before shipping; placed into new </t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Week_5_22_08</t>
+          <t>Week_4_15_08</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260821-0053</t>
+          <t>RC_MEDIUM_260815_02</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>RC-ELITE-260821-0053</t>
-        </is>
-      </c>
+      <c r="E51" s="2" t="inlineStr"/>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>elite</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Arts, Music &amp; Film</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-      <c r="I51" s="3" t="inlineStr">
-        <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="n">
-        <v>8.800000000000001</v>
-      </c>
+          <t>Philosophy &amp; Ethics</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>passage exact</t>
+          <t>UNMATCHED</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/post_housevoice_fix/2026-08-22-selected-10/v2/RC-ELITE-260821-0053.txt</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t>Week_5_22_08/RC-ELITE-260821-0053.docx</t>
-        </is>
-      </c>
+          <t>emailed, never filed in the folder</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
       <c r="N51" s="2" t="inlineStr"/>
-      <c r="O51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>rc_medium_0003</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>old tracker filed this as rc_medium_0003</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Week_5_22_08</t>
+          <t>Week_4_15_08</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260822-0061</t>
+          <t>RC_MEDIUM_260815_02 [staged]</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
@@ -4095,31 +4329,33 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260822-0061</t>
+          <t>rc_medium_0003</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>elite</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Politics, Law &amp; Policy</t>
+          <t>Anthropology &amp; Archaeology</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-      <c r="I52" s="4" t="inlineStr">
-        <is>
-          <t>needs_review</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="n">
-        <v>7.6</v>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>8.6</t>
+        </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
@@ -4128,16 +4364,25 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/post_housevoice_fix/2026-08-22-selected-10/v2/RC-ELITE-260822-0061.txt</t>
+          <t>staged, never emailed</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>Week_5_22_08/RC-ELITE-260822-0061.docx</t>
-        </is>
-      </c>
-      <c r="N52" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/rc_medium_0003.txt</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>Week_4_15_08/Medium/Text/RC_MEDIUM_260815_02.txt | Week_4_15_08/Medium/word/RC_MEDIUM_260815_02.docx</t>
+        </is>
+      </c>
       <c r="O52" s="2" t="inlineStr"/>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>ship-format renamed to RC_MEDIUM_260725_02 | FLAGGED 2026-07-08: thesis-longest bias -- correct answer to Central Thesis (Q1) is the strictly-longest option; not caught before original ship. Already s</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -4152,7 +4397,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260821-0052</t>
+          <t>RC-ELITE-260821-0048</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
@@ -4160,17 +4405,17 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260821-0052</t>
+          <t>RC-ELITE-260821-0048</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>hard</t>
+          <t>elite</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Science &amp; Technology</t>
+          <t>Economics &amp; Business</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4178,9 +4423,9 @@
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="I53" s="3" t="inlineStr">
-        <is>
-          <t>approved</t>
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
@@ -4193,16 +4438,21 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/post_housevoice_fix/2026-08-22-selected-10/v2/RC-HARD-260821-0052.txt</t>
+          <t>emailed</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>Week_5_22_08/RC-HARD-260821-0052.docx</t>
-        </is>
-      </c>
-      <c r="N53" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/post_housevoice_fix/2026-08-22-selected-10/v2/RC-ELITE-260821-0048.txt</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>Week_5_22_08/RC-ELITE-260821-0048.docx</t>
+        </is>
+      </c>
       <c r="O53" s="2" t="inlineStr"/>
+      <c r="P53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -4217,7 +4467,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260821-0056</t>
+          <t>RC-ELITE-260821-0053</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
@@ -4225,17 +4475,17 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260821-0056</t>
+          <t>RC-ELITE-260821-0053</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>hard</t>
+          <t>elite</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>History</t>
+          <t>Arts, Music &amp; Film</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4243,13 +4493,13 @@
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="I54" s="4" t="inlineStr">
-        <is>
-          <t>needs_review</t>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
@@ -4258,16 +4508,21 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/post_housevoice_fix/2026-08-22-selected-10/v2/RC-HARD-260821-0056.txt</t>
+          <t>emailed</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>Week_5_22_08/RC-HARD-260821-0056.docx</t>
-        </is>
-      </c>
-      <c r="N54" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/post_housevoice_fix/2026-08-22-selected-10/v2/RC-ELITE-260821-0053.txt</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>Week_5_22_08/RC-ELITE-260821-0053.docx</t>
+        </is>
+      </c>
       <c r="O54" s="2" t="inlineStr"/>
+      <c r="P54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -4282,7 +4537,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260822-0059</t>
+          <t>RC-ELITE-260822-0061</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
@@ -4290,17 +4545,17 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260822-0059</t>
+          <t>RC-ELITE-260822-0061</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>hard</t>
+          <t>elite</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Economics &amp; Business</t>
+          <t>Politics, Law &amp; Policy</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4308,13 +4563,13 @@
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="I55" s="3" t="inlineStr">
-        <is>
-          <t>approved</t>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
@@ -4323,16 +4578,21 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/post_housevoice_fix/2026-08-22-selected-10/v2/RC-HARD-260822-0059.txt</t>
+          <t>emailed</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>Week_5_22_08/RC-HARD-260822-0059.docx</t>
-        </is>
-      </c>
-      <c r="N55" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/post_housevoice_fix/2026-08-22-selected-10/v2/RC-ELITE-260822-0061.txt</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>Week_5_22_08/RC-ELITE-260822-0061.docx</t>
+        </is>
+      </c>
       <c r="O55" s="2" t="inlineStr"/>
+      <c r="P55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -4347,7 +4607,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260822-0033</t>
+          <t>RC-HARD-260821-0052</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
@@ -4355,17 +4615,17 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260822-0033</t>
+          <t>RC-HARD-260821-0052</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Philosophy &amp; Ethics</t>
+          <t>Science &amp; Technology</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4373,9 +4633,9 @@
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="I56" s="4" t="inlineStr">
-        <is>
-          <t>needs_review</t>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
@@ -4388,16 +4648,21 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/post_housevoice_fix/2026-08-22-selected-10/v2/RC-MEDIUM-260822-0033.txt</t>
+          <t>emailed</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>Week_5_22_08/RC-MEDIUM-260822-0033.docx</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/post_housevoice_fix/2026-08-22-selected-10/v2/RC-HARD-260821-0052.txt</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>Week_5_22_08/RC-HARD-260821-0052.docx</t>
+        </is>
+      </c>
       <c r="O56" s="2" t="inlineStr"/>
+      <c r="P56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -4412,7 +4677,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260822-0034</t>
+          <t>RC-HARD-260821-0056</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
@@ -4420,17 +4685,17 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260822-0034</t>
+          <t>RC-HARD-260821-0056</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Language &amp; Linguistics</t>
+          <t>History</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4438,15 +4703,13 @@
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="I57" s="5" t="inlineStr">
-        <is>
-          <t>solver_dispute</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="I57" s="4" t="inlineStr">
+        <is>
+          <t>needs_review</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="n">
+        <v>8.6</v>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
@@ -4455,16 +4718,21 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/post_housevoice_fix/2026-08-22-selected-10/v2/RC-MEDIUM-260822-0034.txt</t>
+          <t>emailed</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>Week_5_22_08/RC-MEDIUM-260822-0034.docx</t>
-        </is>
-      </c>
-      <c r="N57" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/post_housevoice_fix/2026-08-22-selected-10/v2/RC-HARD-260821-0056.txt</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>Week_5_22_08/RC-HARD-260821-0056.docx</t>
+        </is>
+      </c>
       <c r="O57" s="2" t="inlineStr"/>
+      <c r="P57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -4479,7 +4747,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260822-0037</t>
+          <t>RC-HARD-260822-0059</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
@@ -4487,17 +4755,17 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260822-0037</t>
+          <t>RC-HARD-260822-0059</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Philosophy &amp; Ethics</t>
+          <t>Economics &amp; Business</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4505,13 +4773,13 @@
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="I58" s="4" t="inlineStr">
-        <is>
-          <t>needs_review</t>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
@@ -4520,16 +4788,21 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/post_housevoice_fix/2026-08-22-selected-10/v2/RC-MEDIUM-260822-0037.txt</t>
+          <t>emailed</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>Week_5_22_08/RC-MEDIUM-260822-0037.docx</t>
-        </is>
-      </c>
-      <c r="N58" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/post_housevoice_fix/2026-08-22-selected-10/v2/RC-HARD-260822-0059.txt</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>Week_5_22_08/RC-HARD-260822-0059.docx</t>
+        </is>
+      </c>
       <c r="O58" s="2" t="inlineStr"/>
+      <c r="P58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -4544,7 +4817,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260822-0039</t>
+          <t>RC-MEDIUM-260822-0033</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
@@ -4552,7 +4825,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260822-0039</t>
+          <t>RC-MEDIUM-260822-0033</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -4562,7 +4835,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Sociology &amp; Culture</t>
+          <t>Philosophy &amp; Ethics</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4576,7 +4849,7 @@
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
@@ -4585,31 +4858,36 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/post_housevoice_fix/2026-08-22-selected-10/v2/RC-MEDIUM-260822-0039.txt</t>
+          <t>emailed</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>Week_5_22_08/RC-MEDIUM-260822-0039.docx</t>
-        </is>
-      </c>
-      <c r="N59" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/post_housevoice_fix/2026-08-22-selected-10/v2/RC-MEDIUM-260822-0033.txt</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>Week_5_22_08/RC-MEDIUM-260822-0033.docx</t>
+        </is>
+      </c>
       <c r="O59" s="2" t="inlineStr"/>
+      <c r="P59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Week_6_29_08</t>
+          <t>Week_5_22_08</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260824-0065</t>
+          <t>RC-MEDIUM-260822-0034</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
@@ -4617,17 +4895,17 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260824-0065</t>
+          <t>RC-MEDIUM-260822-0034</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>elite</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Psychology</t>
+          <t>Language &amp; Linguistics</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4635,13 +4913,15 @@
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="I60" s="4" t="inlineStr">
-        <is>
-          <t>needs_review</t>
-        </is>
-      </c>
-      <c r="J60" s="2" t="n">
-        <v>6.8</v>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>solver_dispute</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
@@ -4650,31 +4930,36 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/2026-08-29-post-0823-v2/RC-ELITE-260824-0065.txt</t>
+          <t>emailed</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>Week_6_29_08/docx/RC-ELITE-260824-0065.docx</t>
-        </is>
-      </c>
-      <c r="N60" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/post_housevoice_fix/2026-08-22-selected-10/v2/RC-MEDIUM-260822-0034.txt</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>Week_5_22_08/RC-MEDIUM-260822-0034.docx</t>
+        </is>
+      </c>
       <c r="O60" s="2" t="inlineStr"/>
+      <c r="P60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Week_6_29_08</t>
+          <t>Week_5_22_08</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260824-0067</t>
+          <t>RC-MEDIUM-260822-0037</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
@@ -4682,17 +4967,17 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260824-0067</t>
+          <t>RC-MEDIUM-260822-0037</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>elite</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Psychology</t>
+          <t>Philosophy &amp; Ethics</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -4700,13 +4985,13 @@
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="I61" s="3" t="inlineStr">
-        <is>
-          <t>approved</t>
+      <c r="I61" s="4" t="inlineStr">
+        <is>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
@@ -4715,31 +5000,36 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/2026-08-29-post-0823-v2/RC-ELITE-260824-0067.txt</t>
+          <t>emailed</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>Week_6_29_08/docx/RC-ELITE-260824-0067.docx</t>
-        </is>
-      </c>
-      <c r="N61" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/post_housevoice_fix/2026-08-22-selected-10/v2/RC-MEDIUM-260822-0037.txt</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>Week_5_22_08/RC-MEDIUM-260822-0037.docx</t>
+        </is>
+      </c>
       <c r="O61" s="2" t="inlineStr"/>
+      <c r="P61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Week_6_29_08</t>
+          <t>Week_5_22_08</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260829-0069</t>
+          <t>RC-MEDIUM-260822-0039</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
@@ -4747,17 +5037,17 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260829-0069</t>
+          <t>RC-MEDIUM-260822-0039</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>elite</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Science &amp; Technology</t>
+          <t>Sociology &amp; Culture</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -4771,7 +5061,7 @@
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
@@ -4780,16 +5070,21 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/2026-08-29-0829-v2/RC-ELITE-260829-0069.txt</t>
+          <t>emailed</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>Week_6_29_08/docx/RC-ELITE-260829-0069.docx</t>
-        </is>
-      </c>
-      <c r="N62" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/post_housevoice_fix/2026-08-22-selected-10/v2/RC-MEDIUM-260822-0039.txt</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>Week_5_22_08/RC-MEDIUM-260822-0039.docx</t>
+        </is>
+      </c>
       <c r="O62" s="2" t="inlineStr"/>
+      <c r="P62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -4804,7 +5099,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260824-0066</t>
+          <t>RC-ELITE-260824-0065</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
@@ -4812,17 +5107,17 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260824-0066</t>
+          <t>RC-ELITE-260824-0065</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>hard</t>
+          <t>elite</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Politics, Law &amp; Policy</t>
+          <t>Psychology</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -4830,13 +5125,13 @@
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="I63" s="3" t="inlineStr">
-        <is>
-          <t>approved</t>
+      <c r="I63" s="4" t="inlineStr">
+        <is>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>9</v>
+        <v>6.8</v>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
@@ -4845,16 +5140,21 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/2026-08-29-post-0823-v2/RC-HARD-260824-0066.txt</t>
+          <t>emailed</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>Week_6_29_08/docx/RC-HARD-260824-0066.docx</t>
-        </is>
-      </c>
-      <c r="N63" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/2026-08-29-post-0823-v2/RC-ELITE-260824-0065.txt</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>Week_6_29_08/docx/RC-ELITE-260824-0065.docx</t>
+        </is>
+      </c>
       <c r="O63" s="2" t="inlineStr"/>
+      <c r="P63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -4869,7 +5169,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260828-0067</t>
+          <t>RC-ELITE-260824-0067</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
@@ -4877,17 +5177,17 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260828-0067</t>
+          <t>RC-ELITE-260824-0067</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>hard</t>
+          <t>elite</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Sociology &amp; Culture</t>
+          <t>Psychology</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -4895,9 +5195,9 @@
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="I64" s="4" t="inlineStr">
-        <is>
-          <t>needs_review</t>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
@@ -4910,16 +5210,21 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/2026-08-29-post-0823-v2/RC-HARD-260828-0067.txt</t>
+          <t>emailed</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>Week_6_29_08/docx/RC-HARD-260828-0067.docx</t>
-        </is>
-      </c>
-      <c r="N64" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/2026-08-29-post-0823-v2/RC-ELITE-260824-0067.txt</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>Week_6_29_08/docx/RC-ELITE-260824-0067.docx</t>
+        </is>
+      </c>
       <c r="O64" s="2" t="inlineStr"/>
+      <c r="P64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -4934,7 +5239,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260829-0068</t>
+          <t>RC-ELITE-260829-0069</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
@@ -4942,17 +5247,17 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260829-0068</t>
+          <t>RC-ELITE-260829-0069</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>hard</t>
+          <t>elite</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Anthropology &amp; Archaeology</t>
+          <t>Science &amp; Technology</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -4966,7 +5271,7 @@
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
@@ -4975,16 +5280,21 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/2026-08-29-0829-v2/RC-HARD-260829-0068.txt</t>
+          <t>emailed</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>Week_6_29_08/docx/RC-HARD-260829-0068.docx</t>
-        </is>
-      </c>
-      <c r="N65" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/2026-08-29-0829-v2/RC-ELITE-260829-0069.txt</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>Week_6_29_08/docx/RC-ELITE-260829-0069.docx</t>
+        </is>
+      </c>
       <c r="O65" s="2" t="inlineStr"/>
+      <c r="P65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -4999,7 +5309,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260825-0046</t>
+          <t>RC-HARD-260824-0066</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
@@ -5007,17 +5317,17 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260825-0046</t>
+          <t>RC-HARD-260824-0066</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Arts, Music &amp; Film</t>
+          <t>Politics, Law &amp; Policy</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -5025,13 +5335,13 @@
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="I66" s="4" t="inlineStr">
-        <is>
-          <t>needs_review</t>
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
@@ -5040,16 +5350,21 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/2026-08-29-post-0823-v2/RC-MEDIUM-260825-0046.txt</t>
+          <t>emailed</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>Week_6_29_08/docx/RC-MEDIUM-260825-0046.docx</t>
-        </is>
-      </c>
-      <c r="N66" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/2026-08-29-post-0823-v2/RC-HARD-260824-0066.txt</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>Week_6_29_08/docx/RC-HARD-260824-0066.docx</t>
+        </is>
+      </c>
       <c r="O66" s="2" t="inlineStr"/>
+      <c r="P66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -5064,7 +5379,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260828-0047</t>
+          <t>RC-HARD-260828-0067</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
@@ -5072,17 +5387,17 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260828-0047</t>
+          <t>RC-HARD-260828-0067</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Philosophy &amp; Ethics</t>
+          <t>Sociology &amp; Culture</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5090,13 +5405,13 @@
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="I67" s="3" t="inlineStr">
-        <is>
-          <t>approved</t>
+      <c r="I67" s="4" t="inlineStr">
+        <is>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
@@ -5105,16 +5420,21 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/2026-08-29-post-0823-v2/RC-MEDIUM-260828-0047.txt</t>
+          <t>emailed</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>Week_6_29_08/docx/RC-MEDIUM-260828-0047.docx</t>
-        </is>
-      </c>
-      <c r="N67" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/2026-08-29-post-0823-v2/RC-HARD-260828-0067.txt</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>Week_6_29_08/docx/RC-HARD-260828-0067.docx</t>
+        </is>
+      </c>
       <c r="O67" s="2" t="inlineStr"/>
+      <c r="P67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -5129,7 +5449,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260829-0048</t>
+          <t>RC-HARD-260829-0068</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
@@ -5137,17 +5457,17 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260829-0048</t>
+          <t>RC-HARD-260829-0068</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>History</t>
+          <t>Anthropology &amp; Archaeology</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -5161,7 +5481,7 @@
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
@@ -5170,16 +5490,21 @@
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/2026-08-29-0829-v2/RC-MEDIUM-260829-0048.txt</t>
+          <t>emailed</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>Week_6_29_08/docx/RC-MEDIUM-260829-0048.docx</t>
-        </is>
-      </c>
-      <c r="N68" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/2026-08-29-0829-v2/RC-HARD-260829-0068.txt</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>Week_6_29_08/docx/RC-HARD-260829-0068.docx</t>
+        </is>
+      </c>
       <c r="O68" s="2" t="inlineStr"/>
+      <c r="P68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -5194,7 +5519,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260829-0049</t>
+          <t>RC-MEDIUM-260825-0046</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
@@ -5202,7 +5527,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260829-0049</t>
+          <t>RC-MEDIUM-260825-0046</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -5212,7 +5537,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Politics, Law &amp; Policy</t>
+          <t>Arts, Music &amp; Film</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5226,7 +5551,7 @@
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
@@ -5235,31 +5560,36 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/2026-08-29-0829-v2/RC-MEDIUM-260829-0049.txt</t>
+          <t>emailed</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>Week_6_29_08/docx/RC-MEDIUM-260829-0049.docx</t>
-        </is>
-      </c>
-      <c r="N69" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/2026-08-29-post-0823-v2/RC-MEDIUM-260825-0046.txt</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>Week_6_29_08/docx/RC-MEDIUM-260825-0046.docx</t>
+        </is>
+      </c>
       <c r="O69" s="2" t="inlineStr"/>
+      <c r="P69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Week_7_05_09</t>
+          <t>Week_6_29_08</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260825-0068</t>
+          <t>RC-MEDIUM-260828-0047</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
@@ -5267,17 +5597,17 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260825-0068</t>
+          <t>RC-MEDIUM-260828-0047</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>elite</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Literature &amp; Criticism</t>
+          <t>Philosophy &amp; Ethics</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -5285,15 +5615,13 @@
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="I70" s="5" t="inlineStr">
-        <is>
-          <t>solver_dispute</t>
-        </is>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
@@ -5302,31 +5630,36 @@
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/2026-08-29-post-0823-v2/RC-ELITE-260825-0068.txt</t>
+          <t>emailed</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>Week_7_05_09/RC-ELITE-260825-0068.docx</t>
-        </is>
-      </c>
-      <c r="N70" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/2026-08-29-post-0823-v2/RC-MEDIUM-260828-0047.txt</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>Week_6_29_08/docx/RC-MEDIUM-260828-0047.docx</t>
+        </is>
+      </c>
       <c r="O70" s="2" t="inlineStr"/>
+      <c r="P70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Week_7_05_09</t>
+          <t>Week_6_29_08</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260901-0071</t>
+          <t>RC-MEDIUM-260829-0048</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
@@ -5334,17 +5667,17 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260901-0071</t>
+          <t>RC-MEDIUM-260829-0048</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>elite</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Arts, Music &amp; Film</t>
+          <t>History</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5352,13 +5685,13 @@
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="I71" s="3" t="inlineStr">
-        <is>
-          <t>approved</t>
+      <c r="I71" s="4" t="inlineStr">
+        <is>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
@@ -5367,31 +5700,36 @@
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/2026-09-01-0901b-v2/RC-ELITE-260901-0071.txt</t>
+          <t>emailed</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>Week_7_05_09/RC-ELITE-260901-0071.docx</t>
-        </is>
-      </c>
-      <c r="N71" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/2026-08-29-0829-v2/RC-MEDIUM-260829-0048.txt</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>Week_6_29_08/docx/RC-MEDIUM-260829-0048.docx</t>
+        </is>
+      </c>
       <c r="O71" s="2" t="inlineStr"/>
+      <c r="P71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Week_7_05_09</t>
+          <t>Week_6_29_08</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260901-0072</t>
+          <t>RC-MEDIUM-260829-0049</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
@@ -5399,12 +5737,12 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260901-0072</t>
+          <t>RC-MEDIUM-260829-0049</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>elite</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -5423,7 +5761,7 @@
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
@@ -5432,16 +5770,21 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/2026-09-01-0901b-v2/RC-ELITE-260901-0072.txt</t>
+          <t>emailed</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>Week_7_05_09/RC-ELITE-260901-0072.docx</t>
-        </is>
-      </c>
-      <c r="N72" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/2026-08-29-0829-v2/RC-MEDIUM-260829-0049.txt</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>Week_6_29_08/docx/RC-MEDIUM-260829-0049.docx</t>
+        </is>
+      </c>
       <c r="O72" s="2" t="inlineStr"/>
+      <c r="P72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -5456,7 +5799,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260824-0064</t>
+          <t>RC-ELITE-260825-0068</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
@@ -5464,17 +5807,17 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260824-0064</t>
+          <t>RC-ELITE-260825-0068</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>hard</t>
+          <t>elite</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Politics, Law &amp; Policy</t>
+          <t>Literature &amp; Criticism</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -5482,13 +5825,15 @@
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="I73" s="4" t="inlineStr">
-        <is>
-          <t>needs_review</t>
-        </is>
-      </c>
-      <c r="J73" s="2" t="n">
-        <v>8.4</v>
+      <c r="I73" s="5" t="inlineStr">
+        <is>
+          <t>solver_dispute</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
@@ -5497,16 +5842,21 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/2026-08-29-post-0823-v2/RC-HARD-260824-0064.txt</t>
+          <t>emailed</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>Week_7_05_09/RC-HARD-260824-0064.docx</t>
-        </is>
-      </c>
-      <c r="N73" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/2026-08-29-post-0823-v2/RC-ELITE-260825-0068.txt</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>Week_7_05_09/RC-ELITE-260825-0068.docx</t>
+        </is>
+      </c>
       <c r="O73" s="2" t="inlineStr"/>
+      <c r="P73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -5521,7 +5871,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260829-0069</t>
+          <t>RC-ELITE-260901-0071</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
@@ -5529,17 +5879,17 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260829-0069</t>
+          <t>RC-ELITE-260901-0071</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>hard</t>
+          <t>elite</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Medicine &amp; Health</t>
+          <t>Arts, Music &amp; Film</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -5547,13 +5897,13 @@
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="I74" s="4" t="inlineStr">
-        <is>
-          <t>needs_review</t>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
@@ -5562,16 +5912,21 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/2026-08-29-0829-v2/RC-HARD-260829-0069.txt</t>
+          <t>emailed</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>Week_7_05_09/RC-HARD-260829-0069.docx</t>
-        </is>
-      </c>
-      <c r="N74" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/2026-09-01-0901b-v2/RC-ELITE-260901-0071.txt</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>Week_7_05_09/RC-ELITE-260901-0071.docx</t>
+        </is>
+      </c>
       <c r="O74" s="2" t="inlineStr"/>
+      <c r="P74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -5586,7 +5941,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260901-0075</t>
+          <t>RC-ELITE-260901-0072</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
@@ -5594,17 +5949,17 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260901-0075</t>
+          <t>RC-ELITE-260901-0072</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>hard</t>
+          <t>elite</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Science &amp; Technology</t>
+          <t>Politics, Law &amp; Policy</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -5612,13 +5967,13 @@
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="I75" s="3" t="inlineStr">
-        <is>
-          <t>approved</t>
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
@@ -5627,16 +5982,21 @@
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/2026-09-01-0901-v2/RC-HARD-260901-0075.txt</t>
+          <t>emailed</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>Week_7_05_09/RC-HARD-260901-0075.docx</t>
-        </is>
-      </c>
-      <c r="N75" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/2026-09-01-0901b-v2/RC-ELITE-260901-0072.txt</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>Week_7_05_09/RC-ELITE-260901-0072.docx</t>
+        </is>
+      </c>
       <c r="O75" s="2" t="inlineStr"/>
+      <c r="P75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -5651,7 +6011,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260824-0044</t>
+          <t>RC-HARD-260824-0064</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
@@ -5659,12 +6019,12 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260824-0044</t>
+          <t>RC-HARD-260824-0064</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -5683,7 +6043,7 @@
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
@@ -5692,16 +6052,21 @@
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/2026-08-29-post-0823-v2/RC-MEDIUM-260824-0044.txt</t>
+          <t>emailed</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>Week_7_05_09/RC-MEDIUM-260824-0044.docx</t>
-        </is>
-      </c>
-      <c r="N76" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/2026-08-29-post-0823-v2/RC-HARD-260824-0064.txt</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>Week_7_05_09/RC-HARD-260824-0064.docx</t>
+        </is>
+      </c>
       <c r="O76" s="2" t="inlineStr"/>
+      <c r="P76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -5716,7 +6081,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260901-0050</t>
+          <t>RC-HARD-260829-0069</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
@@ -5724,17 +6089,17 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260901-0050</t>
+          <t>RC-HARD-260829-0069</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>History</t>
+          <t>Medicine &amp; Health</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -5742,15 +6107,13 @@
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="I77" s="5" t="inlineStr">
-        <is>
-          <t>solver_dispute</t>
-        </is>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="I77" s="4" t="inlineStr">
+        <is>
+          <t>needs_review</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="n">
+        <v>7</v>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
@@ -5759,16 +6122,21 @@
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/2026-09-01-0901-v2/RC-MEDIUM-260901-0050.txt</t>
+          <t>emailed</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>Week_7_05_09/RC-MEDIUM-260901-0050.docx</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/2026-08-29-0829-v2/RC-HARD-260829-0069.txt</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>Week_7_05_09/RC-HARD-260829-0069.docx</t>
+        </is>
+      </c>
       <c r="O77" s="2" t="inlineStr"/>
+      <c r="P77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -5783,7 +6151,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260901-0051</t>
+          <t>RC-HARD-260901-0075</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
@@ -5791,17 +6159,17 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260901-0051</t>
+          <t>RC-HARD-260901-0075</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Life Sciences &amp; Environment</t>
+          <t>Science &amp; Technology</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -5809,9 +6177,9 @@
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="I78" s="4" t="inlineStr">
-        <is>
-          <t>needs_review</t>
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
@@ -5824,16 +6192,21 @@
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/2026-09-01-0901-v2/RC-MEDIUM-260901-0051.txt</t>
+          <t>emailed</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>Week_7_05_09/RC-MEDIUM-260901-0051.docx</t>
-        </is>
-      </c>
-      <c r="N78" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/2026-09-01-0901-v2/RC-HARD-260901-0075.txt</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>Week_7_05_09/RC-HARD-260901-0075.docx</t>
+        </is>
+      </c>
       <c r="O78" s="2" t="inlineStr"/>
+      <c r="P78" s="2" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -5848,7 +6221,7 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260901-0052</t>
+          <t>RC-MEDIUM-260824-0044</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
@@ -5856,7 +6229,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260901-0052</t>
+          <t>RC-MEDIUM-260824-0044</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -5866,7 +6239,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Anthropology &amp; Archaeology</t>
+          <t>Politics, Law &amp; Policy</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -5874,13 +6247,13 @@
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="I79" s="3" t="inlineStr">
-        <is>
-          <t>approved</t>
+      <c r="I79" s="4" t="inlineStr">
+        <is>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
@@ -5889,31 +6262,36 @@
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/2026-09-01-0901b-v2/RC-MEDIUM-260901-0052.txt</t>
+          <t>emailed</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>Week_7_05_09/RC-MEDIUM-260901-0052.docx</t>
-        </is>
-      </c>
-      <c r="N79" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/2026-08-29-post-0823-v2/RC-MEDIUM-260824-0044.txt</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>Week_7_05_09/RC-MEDIUM-260824-0044.docx</t>
+        </is>
+      </c>
       <c r="O79" s="2" t="inlineStr"/>
+      <c r="P79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Week_8_12_09</t>
+          <t>Week_7_05_09</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>RC_ELITE_260912_01</t>
+          <t>RC-MEDIUM-260901-0050</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
@@ -5921,17 +6299,17 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260711-0025</t>
+          <t>RC-MEDIUM-260901-0050</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>elite</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Life Sciences &amp; Environment</t>
+          <t>History</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -5939,50 +6317,53 @@
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="I80" s="4" t="inlineStr">
-        <is>
-          <t>needs_review</t>
-        </is>
-      </c>
-      <c r="J80" s="2" t="n">
-        <v>8.6</v>
+      <c r="I80" s="5" t="inlineStr">
+        <is>
+          <t>solver_dispute</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>passage fuzzy 0.89</t>
+          <t>passage exact</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260711-0025.txt</t>
+          <t>emailed</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>Week_8_12_09/RC_ELITE_260912_01.docx</t>
-        </is>
-      </c>
-      <c r="N80" s="2" t="inlineStr"/>
-      <c r="O80" s="2" t="inlineStr">
-        <is>
-          <t>passage edited after export</t>
-        </is>
-      </c>
+          <t>exported_rc_sets/2026-09-01-0901-v2/RC-MEDIUM-260901-0050.txt</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>Week_7_05_09/RC-MEDIUM-260901-0050.docx</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr"/>
+      <c r="P80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Week_8_12_09</t>
+          <t>Week_7_05_09</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>RC_ELITE_260912_02</t>
+          <t>RC-MEDIUM-260901-0051</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
@@ -5990,17 +6371,17 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260726-0032</t>
+          <t>RC-MEDIUM-260901-0051</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>elite</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Sociology &amp; Culture</t>
+          <t>Life Sciences &amp; Environment</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -6008,9 +6389,9 @@
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="I81" s="3" t="inlineStr">
-        <is>
-          <t>approved</t>
+      <c r="I81" s="4" t="inlineStr">
+        <is>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
@@ -6023,35 +6404,36 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260726-0032.txt</t>
+          <t>emailed</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>Week_8_12_09/RC_ELITE_260912_02.docx</t>
-        </is>
-      </c>
-      <c r="N81" s="2" t="inlineStr"/>
-      <c r="O81" s="2" t="inlineStr">
-        <is>
-          <t>Pipeline approved (score 8.6); passed duplicate check, word count 527 (elite band), length-bias clean (0/6 longest); placed into Week_5</t>
-        </is>
-      </c>
+          <t>exported_rc_sets/2026-09-01-0901-v2/RC-MEDIUM-260901-0051.txt</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>Week_7_05_09/RC-MEDIUM-260901-0051.docx</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr"/>
+      <c r="P81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Week_8_12_09</t>
+          <t>Week_7_05_09</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>RC_ELITE_260912_03</t>
+          <t>RC-MEDIUM-260901-0052</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
@@ -6059,17 +6441,17 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260904-0073</t>
+          <t>RC-MEDIUM-260901-0052</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>elite</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>History</t>
+          <t>Anthropology &amp; Archaeology</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -6077,13 +6459,13 @@
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="I82" s="4" t="inlineStr">
-        <is>
-          <t>needs_review</t>
+      <c r="I82" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
@@ -6092,16 +6474,21 @@
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260904-0073.txt</t>
+          <t>emailed</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>Week_8_12_09/RC_ELITE_260912_03.docx</t>
-        </is>
-      </c>
-      <c r="N82" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/2026-09-01-0901b-v2/RC-MEDIUM-260901-0052.txt</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>Week_7_05_09/RC-MEDIUM-260901-0052.docx</t>
+        </is>
+      </c>
       <c r="O82" s="2" t="inlineStr"/>
+      <c r="P82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -6116,7 +6503,7 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>RC_HARD_260912_01</t>
+          <t>RC_ELITE_260912_01</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
@@ -6124,17 +6511,17 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260726-0021</t>
+          <t>RC-ELITE-260711-0025</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>hard</t>
+          <t>elite</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Language &amp; Linguistics</t>
+          <t>Life Sciences &amp; Environment</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6142,9 +6529,9 @@
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="I83" s="3" t="inlineStr">
-        <is>
-          <t>approved</t>
+      <c r="I83" s="4" t="inlineStr">
+        <is>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
@@ -6152,21 +6539,26 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>passage fuzzy 0.99</t>
+          <t>passage fuzzy 0.89</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260726-0021.txt</t>
+          <t>emailed</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>Week_8_12_09/RC_HARD_260912_01.docx</t>
-        </is>
-      </c>
-      <c r="N83" s="2" t="inlineStr"/>
-      <c r="O83" s="2" t="inlineStr">
+          <t>exported_rc_sets/RC-ELITE-260711-0025.txt</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>Week_8_12_09/RC_ELITE_260912_01.docx</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr"/>
+      <c r="P83" s="2" t="inlineStr">
         <is>
           <t>passage edited after export</t>
         </is>
@@ -6185,7 +6577,7 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>RC_HARD_260912_02</t>
+          <t>RC_ELITE_260912_02</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
@@ -6193,17 +6585,17 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260726-0025</t>
+          <t>RC-ELITE-260726-0032</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>hard</t>
+          <t>elite</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Arts, Music &amp; Film</t>
+          <t>Sociology &amp; Culture</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -6217,7 +6609,7 @@
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
@@ -6226,18 +6618,23 @@
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260726-0025.txt</t>
+          <t>emailed</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>Week_8_12_09/RC_HARD_260912_02.docx</t>
-        </is>
-      </c>
-      <c r="N84" s="2" t="inlineStr"/>
-      <c r="O84" s="2" t="inlineStr">
-        <is>
-          <t>Was needs_review; manually judged 2026-07-26 (family_realization 9, ending_behavior 9, voice_consistency 8, distractor_efficiency 8, explanation_quality 8, avg 8.4) -- approve; db updated to approved/</t>
+          <t>exported_rc_sets/RC-ELITE-260726-0032.txt</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>Week_8_12_09/RC_ELITE_260912_02.docx</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr"/>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>Pipeline approved (score 8.6); passed duplicate check, word count 527 (elite band), length-bias clean (0/6 longest); placed into Week_5</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6651,7 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>RC_HARD_260912_03</t>
+          <t>RC_ELITE_260912_03</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
@@ -6262,17 +6659,17 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260822-0060</t>
+          <t>RC-ELITE-260904-0073</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>hard</t>
+          <t>elite</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Politics, Law &amp; Policy</t>
+          <t>History</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -6286,7 +6683,7 @@
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
@@ -6295,16 +6692,21 @@
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260822-0060.txt</t>
+          <t>emailed</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>Week_8_12_09/RC_HARD_260912_03.docx</t>
-        </is>
-      </c>
-      <c r="N85" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/RC-ELITE-260904-0073.txt</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>Week_8_12_09/RC_ELITE_260912_03.docx</t>
+        </is>
+      </c>
       <c r="O85" s="2" t="inlineStr"/>
+      <c r="P85" s="2" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -6319,7 +6721,7 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>RC_MEDIUM_260912_01</t>
+          <t>RC_HARD_260912_01</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
@@ -6327,17 +6729,17 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260905-0061</t>
+          <t>RC-HARD-260726-0021</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Medicine &amp; Health</t>
+          <t>Language &amp; Linguistics</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -6351,25 +6753,34 @@
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>passage exact</t>
+          <t>passage fuzzy 0.99</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260905-0061.txt</t>
+          <t>emailed</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>Week_8_12_09/RC_MEDIUM_260912_01.docx</t>
-        </is>
-      </c>
-      <c r="N86" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/RC-HARD-260726-0021.txt</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>Week_8_12_09/RC_HARD_260912_01.docx</t>
+        </is>
+      </c>
       <c r="O86" s="2" t="inlineStr"/>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>passage edited after export</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -6384,7 +6795,7 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>RC_MEDIUM_260912_02</t>
+          <t>RC_HARD_260912_02</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
@@ -6392,17 +6803,17 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260811-0027</t>
+          <t>RC-HARD-260726-0025</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Economics &amp; Business</t>
+          <t>Arts, Music &amp; Film</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -6410,13 +6821,13 @@
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="I87" s="4" t="inlineStr">
-        <is>
-          <t>needs_review</t>
+      <c r="I87" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
@@ -6425,16 +6836,25 @@
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-MEDIUM-260811-0027.txt</t>
+          <t>emailed</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>Week_8_12_09/RC_MEDIUM_260912_02.docx</t>
-        </is>
-      </c>
-      <c r="N87" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/RC-HARD-260726-0025.txt</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>Week_8_12_09/RC_HARD_260912_02.docx</t>
+        </is>
+      </c>
       <c r="O87" s="2" t="inlineStr"/>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>Was needs_review; manually judged 2026-07-26 (family_realization 9, ending_behavior 9, voice_consistency 8, distractor_efficiency 8, explanation_quality 8, avg 8.4) -- approve; db updated to approved/</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -6449,7 +6869,7 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>RC_MEDIUM_260912_03</t>
+          <t>RC_HARD_260912_03</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
@@ -6457,17 +6877,17 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260819-0030</t>
+          <t>RC-HARD-260822-0060</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Philosophy &amp; Ethics</t>
+          <t>Politics, Law &amp; Policy</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -6481,7 +6901,7 @@
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
@@ -6490,16 +6910,21 @@
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-MEDIUM-260819-0030.txt</t>
+          <t>emailed</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>Week_8_12_09/RC_MEDIUM_260912_03.docx</t>
-        </is>
-      </c>
-      <c r="N88" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/RC-HARD-260822-0060.txt</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>Week_8_12_09/RC_HARD_260912_03.docx</t>
+        </is>
+      </c>
       <c r="O88" s="2" t="inlineStr"/>
+      <c r="P88" s="2" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -6514,7 +6939,7 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>RC_MEDIUM_260912_04</t>
+          <t>RC_MEDIUM_260912_01</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
@@ -6522,52 +6947,267 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
+          <t>RC-MEDIUM-260905-0061</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>Medicine &amp; Health</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="I89" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>passage exact</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>emailed</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260905-0061.txt</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>Week_8_12_09/RC_MEDIUM_260912_01.docx</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr"/>
+      <c r="P89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Week_8_12_09</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>RC_MEDIUM_260912_02</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>RC-MEDIUM-260811-0027</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>Economics &amp; Business</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="I90" s="4" t="inlineStr">
+        <is>
+          <t>needs_review</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>passage exact</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>emailed</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>exported_rc_sets/RC-MEDIUM-260811-0027.txt</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>Week_8_12_09/RC_MEDIUM_260912_02.docx</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr"/>
+      <c r="P90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>Week_8_12_09</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>RC_MEDIUM_260912_03</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>RC-MEDIUM-260819-0030</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>Philosophy &amp; Ethics</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="I91" s="4" t="inlineStr">
+        <is>
+          <t>needs_review</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>passage exact</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>emailed</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>exported_rc_sets/RC-MEDIUM-260819-0030.txt</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>Week_8_12_09/RC_MEDIUM_260912_03.docx</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr"/>
+      <c r="P91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Week_8_12_09</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>RC_MEDIUM_260912_04</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
           <t>RC-MEDIUM-260907-0065</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
       </c>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="I89" s="4" t="inlineStr">
+      <c r="I92" s="4" t="inlineStr">
         <is>
           <t>needs_review</t>
         </is>
       </c>
-      <c r="J89" s="2" t="n">
+      <c r="J92" s="2" t="n">
         <v>7.6</v>
       </c>
-      <c r="K89" s="2" t="inlineStr">
+      <c r="K92" s="2" t="inlineStr">
         <is>
           <t>passage exact</t>
         </is>
       </c>
-      <c r="L89" s="2" t="inlineStr">
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>emailed</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
         <is>
           <t>exported_rc_sets/RC-MEDIUM-260907-0065.txt</t>
         </is>
       </c>
-      <c r="M89" s="2" t="inlineStr">
+      <c r="N92" s="2" t="inlineStr">
         <is>
           <t>Week_8_12_09/RC_MEDIUM_260912_04.docx</t>
         </is>
       </c>
-      <c r="N89" s="2" t="inlineStr"/>
-      <c r="O89" s="2" t="inlineStr"/>
+      <c r="O92" s="2" t="inlineStr"/>
+      <c r="P92" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O89"/>
+  <autoFilter ref="A1:P92"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6578,7 +7218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P71"/>
+  <dimension ref="A1:P70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -9948,7 +10588,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260811-0025</t>
+          <t>RC-MEDIUM-260901-0055</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -9958,7 +10598,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Philosophy &amp; Ethics</t>
+          <t>Literature &amp; Criticism</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -9979,44 +10619,44 @@
         <v>8.6</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>1</v>
+        <v>0.871</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.544</v>
+        <v>0.523</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>506</v>
+        <v>551</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-MEDIUM-260811-0025.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260901-0055.txt</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-MEDIUM-260811-0025.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-MEDIUM-260901-0055.txt</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-MEDIUM-260811-0025.txt | exported_rc_sets/2026-08-14-exports-260810-260811/260811/RC-MEDIUM-260811-0025.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260901-0055.txt</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>2 exported variants; preferred one listed first</t>
+          <t>only ever exported into flagged_similar (novelty-flagged)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260901-0055</t>
+          <t>RC-MEDIUM-260905-0063</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -10026,7 +10666,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Literature &amp; Criticism</t>
+          <t>Politics, Law &amp; Policy</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -10044,35 +10684,35 @@
       </c>
       <c r="G51" s="2" t="inlineStr"/>
       <c r="H51" s="2" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>0.871</v>
+        <v>0.875</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.523</v>
+        <v>0.508</v>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
-        <v>551</v>
+        <v>474</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260901-0055.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260905-0063.txt</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-MEDIUM-260901-0055.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-MEDIUM-260905-0063.txt</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260901-0055.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260905-0063.txt</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -10084,7 +10724,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260905-0063</t>
+          <t>RC-MEDIUM-260822-0040</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -10094,7 +10734,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Politics, Law &amp; Policy</t>
+          <t>Philosophy &amp; Ethics</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -10112,35 +10752,35 @@
       </c>
       <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="2" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>0.875</v>
+        <v>0.845</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.508</v>
+        <v>0.593</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>474</v>
+        <v>401</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260905-0063.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260822-0040.txt</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-MEDIUM-260905-0063.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-MEDIUM-260822-0040.txt</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260905-0063.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260822-0040.txt</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -10152,7 +10792,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260822-0040</t>
+          <t>RC-MEDIUM-260822-0038</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -10162,7 +10802,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Philosophy &amp; Ethics</t>
+          <t>Politics, Law &amp; Policy</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -10180,13 +10820,13 @@
       </c>
       <c r="G53" s="2" t="inlineStr"/>
       <c r="H53" s="2" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>0.845</v>
+        <v>0.95</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.593</v>
+        <v>0.633</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
@@ -10194,33 +10834,33 @@
         </is>
       </c>
       <c r="L53" s="2" t="n">
-        <v>401</v>
+        <v>479</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260822-0040.txt</t>
+          <t>exported_rc_sets/post_housevoice_fix/RC-MEDIUM-260822-0038.txt</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-MEDIUM-260822-0040.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\post_housevoice_fix\RC-MEDIUM-260822-0038.txt</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260822-0040.txt</t>
+          <t>exported_rc_sets/post_housevoice_fix/RC-MEDIUM-260822-0038.txt | exported_rc_sets/review_shippable/02_likely_length_only/RC-MEDIUM-260822-0038.txt | exported_rc_sets/flagged_similar/RC-MEDIUM-260822-0038.txt | exported_rc_sets/try_2/flagged_similar/RC-MEDIUM-260822-0038.txt</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>only ever exported into flagged_similar (novelty-flagged)</t>
+          <t>4 exported variants; preferred one listed first</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260822-0038</t>
+          <t>RC-MEDIUM-260901-0054</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -10230,7 +10870,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Politics, Law &amp; Policy</t>
+          <t>Arts, Music &amp; Film</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -10251,44 +10891,40 @@
         <v>7.8</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>0.95</v>
+        <v>0.884</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.633</v>
+        <v>0.45</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>479</v>
+        <v>525</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/post_housevoice_fix/RC-MEDIUM-260822-0038.txt</t>
+          <t>exported_rc_sets/RC-MEDIUM-260901-0054.txt</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\post_housevoice_fix\RC-MEDIUM-260822-0038.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-MEDIUM-260901-0054.txt</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/post_housevoice_fix/RC-MEDIUM-260822-0038.txt | exported_rc_sets/review_shippable/02_likely_length_only/RC-MEDIUM-260822-0038.txt | exported_rc_sets/flagged_similar/RC-MEDIUM-260822-0038.txt | exported_rc_sets/try_2/flagged_similar/RC-MEDIUM-260822-0038.txt</t>
-        </is>
-      </c>
-      <c r="P54" s="2" t="inlineStr">
-        <is>
-          <t>4 exported variants; preferred one listed first</t>
-        </is>
-      </c>
+          <t>exported_rc_sets/RC-MEDIUM-260901-0054.txt</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260901-0054</t>
+          <t>RC-MEDIUM-260904-0060</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -10298,7 +10934,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Arts, Music &amp; Film</t>
+          <t>History</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -10319,55 +10955,59 @@
         <v>7.8</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>0.884</v>
+        <v>0.847</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.45</v>
+        <v>0.536</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
-        <v>525</v>
+        <v>557</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-MEDIUM-260901-0054.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260904-0060.txt</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-MEDIUM-260901-0054.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-MEDIUM-260904-0060.txt</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-MEDIUM-260901-0054.txt</t>
-        </is>
-      </c>
-      <c r="P55" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260904-0060.txt</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>only ever exported into flagged_similar (novelty-flagged)</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260904-0060</t>
+          <t>RC-ELITE-260822-0056</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>elite</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="D56" s="4" t="inlineStr">
-        <is>
-          <t>needs_review</t>
+          <t>Anthropology &amp; Archaeology</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>solver_dispute</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -10379,48 +11019,50 @@
         <v>8</v>
       </c>
       <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="n">
-        <v>7.8</v>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>0.847</v>
+        <v>0.9</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.536</v>
+        <v>0.531</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>557</v>
+        <v>548</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260904-0060.txt</t>
+          <t>exported_rc_sets/RC-ELITE-260822-0056.txt</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-MEDIUM-260904-0060.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260822-0056.txt</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260904-0060.txt</t>
+          <t>exported_rc_sets/RC-ELITE-260822-0056.txt | exported_rc_sets/post_housevoice_fix/RC-ELITE-260822-0056.txt | exported_rc_sets/try_2/RC-ELITE-260822-0056.txt</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>only ever exported into flagged_similar (novelty-flagged)</t>
+          <t>3 exported variants; preferred one listed first</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260822-0056</t>
+          <t>RC-ELITE-260905-0080</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -10430,7 +11072,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Anthropology &amp; Archaeology</t>
+          <t>Literature &amp; Criticism</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
@@ -10453,49 +11095,45 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>0.9</v>
+        <v>0.804</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.531</v>
+        <v>0.542</v>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
-        <v>548</v>
+        <v>519</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260822-0056.txt</t>
+          <t>exported_rc_sets/RC-ELITE-260905-0080.txt</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260822-0056.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260905-0080.txt</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260822-0056.txt | exported_rc_sets/post_housevoice_fix/RC-ELITE-260822-0056.txt | exported_rc_sets/try_2/RC-ELITE-260822-0056.txt</t>
-        </is>
-      </c>
-      <c r="P57" s="2" t="inlineStr">
-        <is>
-          <t>3 exported variants; preferred one listed first</t>
-        </is>
-      </c>
+          <t>exported_rc_sets/RC-ELITE-260905-0080.txt</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260905-0080</t>
+          <t>RC-HARD-260901-0076</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>elite</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -10523,32 +11161,32 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0.804</v>
+        <v>0.8</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.542</v>
+        <v>0.549</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>519</v>
+        <v>539</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260905-0080.txt</t>
+          <t>exported_rc_sets/RC-HARD-260901-0076.txt</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260905-0080.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260901-0076.txt</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260905-0080.txt</t>
+          <t>exported_rc_sets/RC-HARD-260901-0076.txt</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr"/>
@@ -10556,7 +11194,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260901-0076</t>
+          <t>RC-HARD-260904-0078</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -10566,7 +11204,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Literature &amp; Criticism</t>
+          <t>Psychology</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
@@ -10589,50 +11227,54 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.549</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260901-0076.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-HARD-260904-0078.txt</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260901-0076.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-HARD-260904-0078.txt</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260901-0076.txt</t>
-        </is>
-      </c>
-      <c r="P59" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/flagged_similar/RC-HARD-260904-0078.txt</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>only ever exported into flagged_similar (novelty-flagged)</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260904-0078</t>
+          <t>RC-MEDIUM-260810-0022</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>hard</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Psychology</t>
+          <t>Medicine &amp; Health</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
@@ -10655,44 +11297,44 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>1</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.647</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>544</v>
+        <v>553</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-HARD-260904-0078.txt</t>
+          <t>exported_rc_sets/2026-08-14-exports-260810-260811/260810/RC-MEDIUM-260810-0022.txt</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-HARD-260904-0078.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\2026-08-14-exports-260810-260811\260810\RC-MEDIUM-260810-0022.txt</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-HARD-260904-0078.txt</t>
+          <t>exported_rc_sets/2026-08-14-exports-260810-260811/260810/RC-MEDIUM-260810-0022.txt | exported_rc_sets/2026-08-14-medium-8q/RC-MEDIUM-260810-0022.txt | exported_rc_sets/RC-MEDIUM-260810-0022.txt</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>only ever exported into flagged_similar (novelty-flagged)</t>
+          <t>3 exported variants; preferred one listed first</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260810-0022</t>
+          <t>RC-MEDIUM-260822-0035</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -10702,7 +11344,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Medicine &amp; Health</t>
+          <t>Politics, Law &amp; Policy</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
@@ -10725,44 +11367,44 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.647</v>
+        <v>0.59</v>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>553</v>
+        <v>540</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/2026-08-14-exports-260810-260811/260810/RC-MEDIUM-260810-0022.txt</t>
+          <t>exported_rc_sets/RC-MEDIUM-260822-0035.txt</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\2026-08-14-exports-260810-260811\260810\RC-MEDIUM-260810-0022.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-MEDIUM-260822-0035.txt</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/2026-08-14-exports-260810-260811/260810/RC-MEDIUM-260810-0022.txt | exported_rc_sets/2026-08-14-medium-8q/RC-MEDIUM-260810-0022.txt | exported_rc_sets/RC-MEDIUM-260810-0022.txt</t>
+          <t>exported_rc_sets/RC-MEDIUM-260822-0035.txt | exported_rc_sets/post_housevoice_fix/RC-MEDIUM-260822-0035.txt</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>3 exported variants; preferred one listed first</t>
+          <t>2 exported variants; preferred one listed first</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260822-0035</t>
+          <t>RC-MEDIUM-260905-0062</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -10772,7 +11414,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Politics, Law &amp; Policy</t>
+          <t>Economics &amp; Business</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
@@ -10795,44 +11437,44 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>0.9</v>
+        <v>0.79</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.59</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>540</v>
+        <v>566</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-MEDIUM-260822-0035.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260905-0062.txt</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-MEDIUM-260822-0035.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-MEDIUM-260905-0062.txt</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-MEDIUM-260822-0035.txt | exported_rc_sets/post_housevoice_fix/RC-MEDIUM-260822-0035.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260905-0062.txt</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>2 exported variants; preferred one listed first</t>
+          <t>only ever exported into flagged_similar (novelty-flagged)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260905-0062</t>
+          <t>RC-MEDIUM-260907-0066</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -10842,7 +11484,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Economics &amp; Business</t>
+          <t>Politics, Law &amp; Policy</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
@@ -10865,59 +11507,55 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>0.79</v>
+        <v>0.785</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.528</v>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>566</v>
+        <v>543</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260905-0062.txt</t>
+          <t>exported_rc_sets/RC-MEDIUM-260907-0066.txt</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-MEDIUM-260905-0062.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-MEDIUM-260907-0066.txt</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260905-0062.txt</t>
-        </is>
-      </c>
-      <c r="P63" s="2" t="inlineStr">
-        <is>
-          <t>only ever exported into flagged_similar (novelty-flagged)</t>
-        </is>
-      </c>
+          <t>exported_rc_sets/RC-MEDIUM-260907-0066.txt</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260907-0066</t>
+          <t>RC-ELITE-260726-0030</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>elite</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Politics, Law &amp; Policy</t>
-        </is>
-      </c>
-      <c r="D64" s="5" t="inlineStr">
-        <is>
-          <t>solver_dispute</t>
+          <t>Anthropology &amp; Archaeology</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>rejected_novelty</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -10926,41 +11564,45 @@
         </is>
       </c>
       <c r="F64" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G64" s="2" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>+2 questions</t>
+        </is>
+      </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>0.785</v>
+        <v>1</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.528</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>543</v>
+        <v>500</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-MEDIUM-260907-0066.txt</t>
+          <t>exported_rc_sets/RC-ELITE-260726-0030.txt</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-MEDIUM-260907-0066.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260726-0030.txt</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-MEDIUM-260907-0066.txt</t>
+          <t>exported_rc_sets/RC-ELITE-260726-0030.txt</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr"/>
@@ -10968,17 +11610,17 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260726-0030</t>
+          <t>RC-MEDIUM-260904-0059</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>elite</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Anthropology &amp; Archaeology</t>
+          <t>Science &amp; Technology</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
@@ -10992,53 +11634,53 @@
         </is>
       </c>
       <c r="F65" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t>+2 questions</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="G65" s="2" t="inlineStr"/>
       <c r="H65" s="2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>1</v>
+        <v>0.84</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.525</v>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>500</v>
+        <v>568</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260726-0030.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260904-0059.txt</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260726-0030.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-MEDIUM-260904-0059.txt</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260726-0030.txt</t>
-        </is>
-      </c>
-      <c r="P65" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260904-0059.txt</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>only ever exported into flagged_similar (novelty-flagged)</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260904-0059</t>
+          <t>RC-MANUAL-260708-10</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -11053,7 +11695,7 @@
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>rejected_novelty</t>
+          <t>unrated</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -11062,68 +11704,60 @@
         </is>
       </c>
       <c r="F66" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="J66" s="2" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="K66" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>+2 questions</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr"/>
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="n">
-        <v>568</v>
+        <v>384</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260904-0059.txt</t>
+          <t>exported_rc_sets/RC-MANUAL-260708-10_medium.txt</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-MEDIUM-260904-0059.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-MANUAL-260708-10_medium.txt</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260904-0059.txt</t>
+          <t>exported_rc_sets/RC-MANUAL-260708-10_medium.txt</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>only ever exported into flagged_similar (novelty-flagged)</t>
+          <t xml:space="preserve">legacy/manual export, not in the engine DB; Source: manual generator (evolutionary metaphors for technology); word count 384 (medium band); tier assigned via word count + complexity read 2026-07-12; user-vetted before shipping; placed into new </t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>RC-MANUAL-260708-10</t>
+          <t>RC_E_0705_2</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>elite</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Science &amp; Technology</t>
-        </is>
-      </c>
-      <c r="D67" s="6" t="inlineStr">
-        <is>
-          <t>unrated</t>
+          <t>Sociology &amp; Culture</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>blocked</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -11139,38 +11773,46 @@
           <t>+2 questions</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>8.8</t>
+        </is>
+      </c>
       <c r="I67" s="2" t="inlineStr"/>
       <c r="J67" s="2" t="inlineStr"/>
-      <c r="K67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="L67" s="2" t="n">
-        <v>384</v>
+        <v>580</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-MANUAL-260708-10_medium.txt</t>
+          <t>exported_rc_sets/RC_E_0705_2.txt</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-MANUAL-260708-10_medium.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC_E_0705_2.txt</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-MANUAL-260708-10_medium.txt</t>
+          <t>exported_rc_sets/RC_E_0705_2.txt</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">legacy/manual export, not in the engine DB; Source: manual generator (evolutionary metaphors for technology); word count 384 (medium band); tier assigned via word count + complexity read 2026-07-12; user-vetted before shipping; placed into new </t>
+          <t>BLOCKED - you marked this not-sent: length-bias FAILED: correct answer longest in 4/6 questions, incl. thesis Q1 -- needs content fix before shipping; legacy/manual export, not in the engine DB</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>RC_E_0705_2</t>
+          <t>RC_E_0705_5</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -11180,7 +11822,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Sociology &amp; Culture</t>
+          <t>Language &amp; Linguistics</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
@@ -11214,43 +11856,43 @@
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>580</v>
+        <v>589</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC_E_0705_2.txt</t>
+          <t>exported_rc_sets/RC_E_0705_5.txt</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC_E_0705_2.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC_E_0705_5.txt</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC_E_0705_2.txt</t>
+          <t>exported_rc_sets/RC_E_0705_5.txt</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED - you marked this not-sent: length-bias FAILED: correct answer longest in 4/6 questions, incl. thesis Q1 -- needs content fix before shipping; legacy/manual export, not in the engine DB</t>
+          <t>BLOCKED - you marked this not-sent: length-bias FAILED: correct answer longest in 5/6 questions, incl. thesis Q1 -- needs content fix before shipping; legacy/manual export, not in the engine DB</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>RC_E_0705_5</t>
+          <t>rc_hard_0004</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>elite</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Language &amp; Linguistics</t>
+          <t>Anthropology &amp; Archaeology</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
@@ -11273,44 +11915,44 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr"/>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>589</v>
+        <v>485</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC_E_0705_5.txt</t>
+          <t>exported_rc_sets/rc_hard_0004.txt</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC_E_0705_5.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\rc_hard_0004.txt</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC_E_0705_5.txt</t>
+          <t>exported_rc_sets/rc_hard_0004.txt</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED - you marked this not-sent: length-bias FAILED: correct answer longest in 5/6 questions, incl. thesis Q1 -- needs content fix before shipping; legacy/manual export, not in the engine DB</t>
+          <t>BLOCKED - you marked this not-sent: length-bias FAILED: correct answer longest in 6/6 questions (all), incl. thesis Q1 -- needs content fix before shipping; legacy/manual export, not in the engine DB</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>rc_hard_0004</t>
+          <t>RC_H_0705_3</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -11320,7 +11962,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Anthropology &amp; Archaeology</t>
+          <t>Medicine &amp; Health</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
@@ -11343,112 +11985,42 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr"/>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>485</v>
+        <v>515</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/rc_hard_0004.txt</t>
+          <t>exported_rc_sets/RC_H_0705_3.txt</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\rc_hard_0004.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC_H_0705_3.txt</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/rc_hard_0004.txt</t>
+          <t>exported_rc_sets/RC_H_0705_3.txt</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED - you marked this not-sent: length-bias FAILED: correct answer longest in 6/6 questions (all), incl. thesis Q1 -- needs content fix before shipping; legacy/manual export, not in the engine DB</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>RC_H_0705_3</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>Medicine &amp; Health</t>
-        </is>
-      </c>
-      <c r="D71" s="5" t="inlineStr">
-        <is>
-          <t>blocked</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t>+2 questions</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>8.2</t>
-        </is>
-      </c>
-      <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr"/>
-      <c r="K71" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="n">
-        <v>515</v>
-      </c>
-      <c r="M71" s="2" t="inlineStr">
-        <is>
-          <t>exported_rc_sets/RC_H_0705_3.txt</t>
-        </is>
-      </c>
-      <c r="N71" s="2" t="inlineStr">
-        <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC_H_0705_3.txt</t>
-        </is>
-      </c>
-      <c r="O71" s="2" t="inlineStr">
-        <is>
-          <t>exported_rc_sets/RC_H_0705_3.txt</t>
-        </is>
-      </c>
-      <c r="P71" s="2" t="inlineStr">
-        <is>
           <t>BLOCKED - you marked this not-sent: length-bias FAILED: correct answer longest in 5/6 questions, incl. thesis Q1 -- needs content fix before shipping; legacy/manual export, not in the engine DB</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P71"/>
+  <autoFilter ref="A1:P70"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11652,7 +12224,7 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>5</v>
@@ -11661,10 +12233,10 @@
         <v>5</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>4</v>
@@ -11904,10 +12476,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>3</v>
@@ -11919,10 +12491,10 @@
         <v>2</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>18.2</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="3">
@@ -11950,7 +12522,7 @@
         <v>6</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>9.1</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -11978,7 +12550,7 @@
         <v>3</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>9.1</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -12006,7 +12578,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>8</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="6">
@@ -12034,7 +12606,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>8</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="7">
@@ -12062,26 +12634,26 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>8</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>History</t>
+          <t>Economics &amp; Business</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>2</v>
@@ -12090,23 +12662,23 @@
         <v>1</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Sociology &amp; Culture</t>
+          <t>History</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>2</v>
@@ -12115,20 +12687,20 @@
         <v>2</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Economics &amp; Business</t>
+          <t>Sociology &amp; Culture</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>4</v>
@@ -12137,16 +12709,16 @@
         <v>2</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="11">
@@ -12174,7 +12746,7 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="12">
@@ -12202,7 +12774,7 @@
         <v>2</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="13">
@@ -12230,7 +12802,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="14">
@@ -12258,7 +12830,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="15">
@@ -12296,10 +12868,10 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>15</v>
@@ -12311,7 +12883,7 @@
         <v>28</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
     </row>
@@ -12322,6 +12894,251 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Issue</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Sent_as</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>RC_ID</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Week_4_15_08</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>emailed, not in the folder</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>RC_MEDIUM_260811_0025</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>RC-MEDIUM-260811-0025</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>closest folder file RC_ELITE_260815_01 at 0.07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Week_4_15_08</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>emailed, not in the folder</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>RC_MEDIUM_260811_0027</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>RC-MEDIUM-260811-0027</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>closest folder file RC_HARD_260815_03 at 0.08</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Week_4_15_08</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>emailed, not in the folder</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>RC_MEDIUM_260815_02</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>(unresolved)</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>closest folder file RC_HARD_260815_01 at 0.09</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Week_4_15_08</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>in the folder, never emailed</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>RC_ELITE_260815_01</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>counted as spoken for; reuse only deliberately</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Week_4_15_08</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>in the folder, never emailed</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>RC_ELITE_260815_02</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>counted as spoken for; reuse only deliberately</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Week_4_15_08</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>in the folder, never emailed</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>RC_HARD_260815_02</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>counted as spoken for; reuse only deliberately</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Week_4_15_08</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>in the folder, never emailed</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>RC_HARD_260815_05</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>counted as spoken for; reuse only deliberately</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Week_4_15_08</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>in the folder, never emailed</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>RC_MEDIUM_260815_02</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr"/>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>counted as spoken for; reuse only deliberately</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E9"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13079,13 +13896,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -13123,7 +13940,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6">
@@ -13143,7 +13960,7 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -13153,7 +13970,7 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -13166,7 +13983,7 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11">
@@ -13206,7 +14023,7 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -13259,7 +14076,7 @@
         </is>
       </c>
       <c r="B20" s="9" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21">
@@ -13312,7 +14129,7 @@
         </is>
       </c>
       <c r="B26" s="9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27">
@@ -13335,7 +14152,7 @@
         </is>
       </c>
       <c r="B29" s="9" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="30">
@@ -13349,6 +14166,56 @@
       </c>
       <c r="B31" s="9" t="n">
         <v>21</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Folder-vs-mail discrepancies</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  emailed</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  emailed, never filed</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  staged, never emailed</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  staged, not yet emailed</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/RC_Shipping_Tracker.xlsx
+++ b/RC_Shipping_Tracker.xlsx
@@ -16,9 +16,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Shipped'!$A$1:$P$92</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Available'!$A$1:$P$70</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Week'!$A$1:$J$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Shipped'!$A$1:$P$102</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Available'!$A$1:$P$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Week'!$A$1:$J$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Genre Mix'!$A$1:$H$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Folder vs Sent'!$A$1:$E$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Reconciliation'!$A$1:$G$22</definedName>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P92"/>
+  <dimension ref="A1:P102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -7206,8 +7206,716 @@
       <c r="O92" s="2" t="inlineStr"/>
       <c r="P92" s="2" t="inlineStr"/>
     </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>Week_9_19_09</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>RC_ELITE_260919_01</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>RC-ELITE-260711-0024</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>elite</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>Philosophy &amp; Ethics</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="I93" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>passage exact</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>staged, not yet emailed</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>exported_rc_sets/2026-09-14-week9-v2/RC-ELITE-260711-0024.txt</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>Week_9_19_09/RC_ELITE_260919_01.docx</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr"/>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>Was needs_review; manually judged 2026-07-26 (avg 8.4, corroborates pipeline judge) -- approve. Original had length-bias FAIL (3/6 longest: Q4,Q5,Q6) AND word count 414 (86 under elite band); manually</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Week_9_19_09</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>RC_ELITE_260919_02</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>RC-ELITE-260811-0039</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>elite</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>Literature &amp; Criticism</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="I94" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>passage exact</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>staged, not yet emailed</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>exported_rc_sets/2026-09-14-week9-v2/RC-ELITE-260811-0039.txt</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>Week_9_19_09/RC_ELITE_260919_02.docx</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr"/>
+      <c r="P94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>Week_9_19_09</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>RC_ELITE_260919_03</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>RC-ELITE-260914-0087</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>elite</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>Literature &amp; Criticism</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="I95" s="4" t="inlineStr">
+        <is>
+          <t>needs_review</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>passage exact</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>staged, not yet emailed</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>exported_rc_sets/2026-09-14-week9-v2/RC-ELITE-260914-0087.txt</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>Week_9_19_09/RC_ELITE_260919_03.docx</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr"/>
+      <c r="P95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>Week_9_19_09</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>RC_HARD_260919_01</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>RC-HARD-260811-0037</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>Philosophy &amp; Ethics</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="I96" s="4" t="inlineStr">
+        <is>
+          <t>needs_review</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>passage exact</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>staged, not yet emailed</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>exported_rc_sets/2026-09-14-week9-v2/RC-HARD-260811-0037.txt</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>Week_9_19_09/RC_HARD_260919_01.docx</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr"/>
+      <c r="P96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>Week_9_19_09</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>RC_HARD_260919_02</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>RC-HARD-260811-0047</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>Literature &amp; Criticism</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="I97" s="4" t="inlineStr">
+        <is>
+          <t>needs_review</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>passage exact</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>staged, not yet emailed</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>exported_rc_sets/2026-09-14-week9-v2/RC-HARD-260811-0047.txt</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>Week_9_19_09/RC_HARD_260919_02.docx</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr"/>
+      <c r="P97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Week_9_19_09</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>RC_HARD_260919_03</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>RC-HARD-260914-0099</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>Philosophy &amp; Ethics</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="I98" s="4" t="inlineStr">
+        <is>
+          <t>needs_review</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>passage exact</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>staged, not yet emailed</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>exported_rc_sets/2026-09-14-week9-v2/RC-HARD-260914-0099.txt</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>Week_9_19_09/RC_HARD_260919_03.docx</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr"/>
+      <c r="P98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>Week_9_19_09</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>RC_MEDIUM_260919_01</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>RC-MEDIUM-260726-0021</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>Philosophy &amp; Ethics</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="I99" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>passage exact</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>staged, not yet emailed</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>exported_rc_sets/2026-09-14-week9-v2/RC-MEDIUM-260726-0021.txt</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>Week_9_19_09/RC_MEDIUM_260919_01.docx</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr"/>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pipeline approved (score 8.8, verdict approve, verified via judge_json before shipping); passed duplicate check, word count 503 (53 over medium band 400-450, flagged), length-bias clean (0/6 longest, </t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Week_9_19_09</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>RC_MEDIUM_260919_02</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>RC-MEDIUM-260901-0054</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>Arts, Music &amp; Film</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="I100" s="4" t="inlineStr">
+        <is>
+          <t>needs_review</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>passage exact</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>staged, not yet emailed</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>exported_rc_sets/2026-09-14-week9-v2/RC-MEDIUM-260901-0054.txt</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>Week_9_19_09/RC_MEDIUM_260919_02.docx</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr"/>
+      <c r="P100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Week_9_19_09</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>RC_MEDIUM_260919_03</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>RC-MEDIUM-260904-0056</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>Politics, Law &amp; Policy</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="I101" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>passage exact</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>staged, not yet emailed</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>exported_rc_sets/2026-09-14-week9-v2/RC-MEDIUM-260904-0056.txt</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>Week_9_19_09/RC_MEDIUM_260919_03.docx</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr"/>
+      <c r="P101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Week_9_19_09</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>RC_MEDIUM_260919_04</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>RC-MEDIUM-260914-0074</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>Philosophy &amp; Ethics</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="I102" s="4" t="inlineStr">
+        <is>
+          <t>needs_review</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>passage exact</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>staged, not yet emailed</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>exported_rc_sets/2026-09-14-week9-v2/RC-MEDIUM-260914-0074.txt</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>Week_9_19_09/RC_MEDIUM_260919_04.docx</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr"/>
+      <c r="P102" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P92"/>
+  <autoFilter ref="A1:P102"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7218,7 +7926,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P70"/>
+  <dimension ref="A1:P78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -7396,7 +8104,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260811-0039</t>
+          <t>RC-ELITE-260904-0074</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -7406,7 +8114,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Literature &amp; Criticism</t>
+          <t>Arts, Music &amp; Film</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -7424,47 +8132,43 @@
       </c>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1</v>
+        <v>0.862</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.678</v>
+        <v>0.505</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>518</v>
+        <v>545</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260811-0039.txt</t>
+          <t>exported_rc_sets/RC-ELITE-260904-0074.txt</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260811-0039.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260904-0074.txt</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260811-0039.txt | exported_rc_sets/2026-08-14-exports-260810-260811/260811/RC-ELITE-260811-0039.txt</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>2 exported variants; preferred one listed first</t>
-        </is>
-      </c>
+          <t>exported_rc_sets/RC-ELITE-260904-0074.txt</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260711-0024</t>
+          <t>RC-ELITE-260822-0057</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -7474,7 +8178,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Philosophy &amp; Ethics</t>
+          <t>Sociology &amp; Culture</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -7488,55 +8192,51 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>+2 questions</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.707</v>
+        <v>0.588</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>414</v>
+        <v>535</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260711-0024.txt</t>
+          <t>exported_rc_sets/RC-ELITE-260822-0057.txt</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260711-0024.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260822-0057.txt</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260711-0024.txt</t>
+          <t>exported_rc_sets/RC-ELITE-260822-0057.txt | exported_rc_sets/post_housevoice_fix/RC-ELITE-260822-0057.txt</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Was needs_review; manually judged 2026-07-26 (avg 8.4, corroborates pipeline judge) -- approve. Original had length-bias FAIL (3/6 longest: Q4,Q5,Q6) AND word count 414 (86 under elite band); manually</t>
+          <t>2 exported variants; preferred one listed first</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260904-0074</t>
+          <t>RC_E_0705_7</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -7546,7 +8246,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Arts, Music &amp; Film</t>
+          <t>Philosophy &amp; Ethics</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -7560,47 +8260,53 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>0.862</v>
-      </c>
-      <c r="J5" s="2" t="n">
-        <v>0.505</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>+2 questions</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>545</v>
+        <v>573</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260904-0074.txt</t>
+          <t>exported_rc_sets/RC_E_0705_7.txt</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260904-0074.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC_E_0705_7.txt</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260904-0074.txt</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/RC_E_0705_7.txt</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>legacy/manual export, not in the engine DB</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260822-0057</t>
+          <t>RC-ELITE-260711-0023</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -7610,7 +8316,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Sociology &amp; Culture</t>
+          <t>Economics &amp; Business</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -7624,63 +8330,65 @@
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="n">
-        <v>8.199999999999999</v>
+        <v>6</v>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>+2 questions</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.9330000000000001</v>
+        <v>1</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.588</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260822-0057.txt</t>
+          <t>exported_rc_sets/RC-ELITE-260711-0023.txt</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260822-0057.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260711-0023.txt</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260822-0057.txt | exported_rc_sets/post_housevoice_fix/RC-ELITE-260822-0057.txt</t>
+          <t>exported_rc_sets/RC-ELITE-260711-0023.txt</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2 exported variants; preferred one listed first</t>
+          <t>Was rejected_novelty (verdict not_run_novelty, flagged nearest to RC-ELITE-260706-0005 and RC_E_0706_1); manually judged 2026-07-26 (avg 7.8) -- approve. Manually compared against both flagged neighbo</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>RC_E_0705_7</t>
+          <t>RC-HARD-260912-0094</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>elite</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Philosophy &amp; Ethics</t>
-        </is>
-      </c>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr">
         <is>
           <t>approved</t>
@@ -7692,63 +8400,57 @@
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>+2 questions</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>8.2</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>0.921</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>0.492</v>
+      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>573</v>
+        <v>538</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC_E_0705_7.txt</t>
+          <t>exported_rc_sets/RC-HARD-260912-0094.txt</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC_E_0705_7.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260912-0094.txt</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC_E_0705_7.txt</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>legacy/manual export, not in the engine DB</t>
-        </is>
-      </c>
+          <t>exported_rc_sets/RC-HARD-260912-0094.txt</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260711-0023</t>
+          <t>RC-HARD-260726-0022</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>elite</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Economics &amp; Business</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -7769,50 +8471,48 @@
           <t>+2 questions</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="H8" s="2" t="n">
+        <v>8.6</v>
       </c>
       <c r="I8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.621</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>532</v>
+        <v>518</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260711-0023.txt</t>
+          <t>exported_rc_sets/RC-HARD-260726-0022.txt</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260711-0023.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260726-0022.txt</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260711-0023.txt</t>
+          <t>exported_rc_sets/RC-HARD-260726-0022.txt</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Was rejected_novelty (verdict not_run_novelty, flagged nearest to RC-ELITE-260706-0005 and RC_E_0706_1); manually judged 2026-07-26 (avg 7.8) -- approve. Manually compared against both flagged neighbo</t>
+          <t>Pipeline approved (score 8.6); passed duplicate check, word count 518 (18 over hard band, within tolerance), length-bias clean (0/6 longest); placed into Week_5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260726-0022</t>
+          <t>RC-HARD-260726-0024</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -7822,7 +8522,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Psychology</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -7850,7 +8550,7 @@
         <v>1</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.621</v>
+        <v>0.623</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
@@ -7858,33 +8558,33 @@
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260726-0022.txt</t>
+          <t>exported_rc_sets/RC-HARD-260726-0024.txt</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260726-0022.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260726-0024.txt</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260726-0022.txt</t>
+          <t>exported_rc_sets/RC-HARD-260726-0024.txt</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>Pipeline approved (score 8.6); passed duplicate check, word count 518 (18 over hard band, within tolerance), length-bias clean (0/6 longest); placed into Week_5</t>
+          <t>Pipeline approved (score 8.6); passed duplicate check, word count 524 (24 over hard band, flagged), length-bias clean (1/6, Q4, thesis not longest); placed into Week_5 (completed to 5/5)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260726-0024</t>
+          <t>RC-HARD-260811-0046</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -7894,7 +8594,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Psychology</t>
+          <t>Economics &amp; Business</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -7908,13 +8608,9 @@
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>+2 questions</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="n">
         <v>8.6</v>
       </c>
@@ -7922,41 +8618,41 @@
         <v>1</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.623</v>
+        <v>0.486</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>524</v>
+        <v>512</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260726-0024.txt</t>
+          <t>exported_rc_sets/RC-HARD-260811-0046.txt</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260726-0024.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260811-0046.txt</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260726-0024.txt</t>
+          <t>exported_rc_sets/RC-HARD-260811-0046.txt | exported_rc_sets/2026-08-14-exports-260810-260811/260811/RC-HARD-260811-0046.txt</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Pipeline approved (score 8.6); passed duplicate check, word count 524 (24 over hard band, flagged), length-bias clean (1/6, Q4, thesis not longest); placed into Week_5 (completed to 5/5)</t>
+          <t>2 exported variants; preferred one listed first</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260811-0046</t>
+          <t>RC-HARD-260912-0091</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -7964,11 +8660,7 @@
           <t>hard</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Economics &amp; Business</t>
-        </is>
-      </c>
+      <c r="C11" s="2" t="inlineStr"/>
       <c r="D11" s="3" t="inlineStr">
         <is>
           <t>approved</t>
@@ -7987,39 +8679,35 @@
         <v>8.6</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1</v>
+        <v>0.831</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.486</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>512</v>
+        <v>548</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260811-0046.txt</t>
+          <t>exported_rc_sets/RC-HARD-260912-0091.txt</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260811-0046.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260912-0091.txt</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260811-0046.txt | exported_rc_sets/2026-08-14-exports-260810-260811/260811/RC-HARD-260811-0046.txt</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>2 exported variants; preferred one listed first</t>
-        </is>
-      </c>
+          <t>exported_rc_sets/RC-HARD-260912-0091.txt</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -8152,14 +8840,10 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260822-0063.txt | exported_rc_sets/flagged_similar/RC-HARD-260822-0063.txt</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2 exported variants; preferred one listed first</t>
-        </is>
-      </c>
+          <t>exported_rc_sets/RC-HARD-260822-0063.txt</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -8236,12 +8920,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260904-0056</t>
+          <t>RC-ELITE-260905-0075</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>elite</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -8254,9 +8938,9 @@
           <t>approved</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
       <c r="F15" s="2" t="n">
@@ -8264,115 +8948,111 @@
       </c>
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0.794</v>
+        <v>0.871</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.451</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>533</v>
+        <v>549</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-MEDIUM-260904-0056.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-ELITE-260905-0075.txt</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-MEDIUM-260904-0056.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-ELITE-260905-0075.txt</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-MEDIUM-260904-0056.txt</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/flagged_similar/RC-ELITE-260905-0075.txt</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>only ever exported into flagged_similar (novelty-flagged)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260726-0021</t>
+          <t>RC-ELITE-260914-0086</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Philosophy &amp; Ethics</t>
-        </is>
-      </c>
+          <t>elite</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr"/>
       <c r="D16" s="3" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>+2 questions</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1</v>
+        <v>0.844</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.541</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>503</v>
+        <v>538</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-MEDIUM-260726-0021.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-ELITE-260914-0086.txt</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-MEDIUM-260726-0021.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-ELITE-260914-0086.txt</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-MEDIUM-260726-0021.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-ELITE-260914-0086.txt</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pipeline approved (score 8.8, verdict approve, verified via judge_json before shipping); passed duplicate check, word count 503 (53 over medium band 400-450, flagged), length-bias clean (0/6 longest, </t>
+          <t>only ever exported into flagged_similar (novelty-flagged)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260905-0075</t>
+          <t>RC-ELITE-260905-0077</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -8382,7 +9062,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Politics, Law &amp; Policy</t>
+          <t>Science &amp; Technology</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -8400,13 +9080,13 @@
       </c>
       <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0.871</v>
+        <v>0.784</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.451</v>
+        <v>0.545</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
@@ -8414,21 +9094,21 @@
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>549</v>
+        <v>528</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-ELITE-260905-0075.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-ELITE-260905-0077.txt</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-ELITE-260905-0075.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-ELITE-260905-0077.txt</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-ELITE-260905-0075.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-ELITE-260905-0077.txt</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8440,19 +9120,15 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260905-0077</t>
+          <t>RC-MEDIUM-260912-0068</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>elite</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Science &amp; Technology</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr"/>
       <c r="D18" s="3" t="inlineStr">
         <is>
           <t>approved</t>
@@ -8468,35 +9144,35 @@
       </c>
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0.784</v>
+        <v>0.765</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.545</v>
+        <v>0.523</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>528</v>
+        <v>543</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-ELITE-260905-0077.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260912-0068.txt</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-ELITE-260905-0077.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-MEDIUM-260912-0068.txt</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-ELITE-260905-0077.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260912-0068.txt</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -8576,7 +9252,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260810-0035</t>
+          <t>RC-ELITE-260914-0089</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -8584,11 +9260,7 @@
           <t>elite</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Life Sciences &amp; Environment</t>
-        </is>
-      </c>
+      <c r="C20" s="2" t="inlineStr"/>
       <c r="D20" s="4" t="inlineStr">
         <is>
           <t>needs_review</t>
@@ -8604,47 +9276,47 @@
       </c>
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1</v>
+        <v>0.862</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.652</v>
+        <v>0.542</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260810-0035.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-ELITE-260914-0089.txt</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260810-0035.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-ELITE-260914-0089.txt</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260810-0035.txt | exported_rc_sets/2026-08-14-exports-260810-260811/260810/RC-ELITE-260810-0035.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-ELITE-260914-0089.txt</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2 exported variants; preferred one listed first</t>
+          <t>only ever exported into flagged_similar (novelty-flagged)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260821-0050</t>
+          <t>RC-ELITE-260810-0035</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -8654,7 +9326,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Psychology</t>
+          <t>Life Sciences &amp; Environment</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -8675,44 +9347,44 @@
         <v>8.6</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>0.74</v>
+        <v>1</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.517</v>
+        <v>0.652</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>533</v>
+        <v>564</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260821-0050.txt</t>
+          <t>exported_rc_sets/RC-ELITE-260810-0035.txt</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260821-0050.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260810-0035.txt</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260821-0050.txt | exported_rc_sets/post_housevoice_fix/RC-ELITE-260821-0050.txt | exported_rc_sets/try_2/RC-ELITE-260821-0050.txt</t>
+          <t>exported_rc_sets/RC-ELITE-260810-0035.txt | exported_rc_sets/2026-08-14-exports-260810-260811/260810/RC-ELITE-260810-0035.txt</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3 exported variants; preferred one listed first</t>
+          <t>2 exported variants; preferred one listed first</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260822-0060</t>
+          <t>RC-ELITE-260821-0050</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -8722,7 +9394,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Arts, Music &amp; Film</t>
+          <t>Psychology</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -8743,44 +9415,44 @@
         <v>8.6</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0.895</v>
+        <v>0.74</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.509</v>
+        <v>0.517</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>564</v>
+        <v>533</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/post_housevoice_fix/RC-ELITE-260822-0060.txt</t>
+          <t>exported_rc_sets/RC-ELITE-260821-0050.txt</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\post_housevoice_fix\RC-ELITE-260822-0060.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260821-0050.txt</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/post_housevoice_fix/RC-ELITE-260822-0060.txt | exported_rc_sets/review_shippable/02_likely_length_only/RC-ELITE-260822-0060.txt | exported_rc_sets/flagged_similar/RC-ELITE-260822-0060.txt | exported_rc_sets/try_2/flagged_similar/RC-ELITE-260822-0060.txt</t>
+          <t>exported_rc_sets/RC-ELITE-260821-0050.txt | exported_rc_sets/post_housevoice_fix/RC-ELITE-260821-0050.txt | exported_rc_sets/try_2/RC-ELITE-260821-0050.txt</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4 exported variants; preferred one listed first</t>
+          <t>3 exported variants; preferred one listed first</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260811-0038</t>
+          <t>RC-ELITE-260822-0060</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -8790,7 +9462,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>History</t>
+          <t>Arts, Music &amp; Film</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -8808,47 +9480,47 @@
       </c>
       <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>1</v>
+        <v>0.895</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.529</v>
+        <v>0.509</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>519</v>
+        <v>564</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260811-0038.txt</t>
+          <t>exported_rc_sets/post_housevoice_fix/RC-ELITE-260822-0060.txt</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260811-0038.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\post_housevoice_fix\RC-ELITE-260822-0060.txt</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260811-0038.txt | exported_rc_sets/2026-08-14-exports-260810-260811/260811/RC-ELITE-260811-0038.txt</t>
+          <t>exported_rc_sets/post_housevoice_fix/RC-ELITE-260822-0060.txt | exported_rc_sets/review_shippable/02_likely_length_only/RC-ELITE-260822-0060.txt | exported_rc_sets/flagged_similar/RC-ELITE-260822-0060.txt | exported_rc_sets/try_2/flagged_similar/RC-ELITE-260822-0060.txt</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2 exported variants; preferred one listed first</t>
+          <t>4 exported variants; preferred one listed first</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260822-0062</t>
+          <t>RC-ELITE-260912-0084</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -8856,11 +9528,7 @@
           <t>elite</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Philosophy &amp; Ethics</t>
-        </is>
-      </c>
+      <c r="C24" s="2" t="inlineStr"/>
       <c r="D24" s="4" t="inlineStr">
         <is>
           <t>needs_review</t>
@@ -8876,47 +9544,47 @@
       </c>
       <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0.907</v>
+        <v>0.831</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.616</v>
+        <v>0.554</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>525</v>
+        <v>560</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260822-0062.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-ELITE-260912-0084.txt</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260822-0062.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-ELITE-260912-0084.txt</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260822-0062.txt | exported_rc_sets/flagged_similar/RC-ELITE-260822-0062.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-ELITE-260912-0084.txt</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2 exported variants; preferred one listed first</t>
+          <t>only ever exported into flagged_similar (novelty-flagged)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260907-0082</t>
+          <t>RC-ELITE-260811-0038</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -8926,7 +9594,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Politics, Law &amp; Policy</t>
+          <t>History</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -8947,40 +9615,44 @@
         <v>8.199999999999999</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>0.884</v>
+        <v>1</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.482</v>
+        <v>0.529</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>550</v>
+        <v>519</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260907-0082.txt</t>
+          <t>exported_rc_sets/RC-ELITE-260811-0038.txt</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260907-0082.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260811-0038.txt</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260907-0082.txt</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/RC-ELITE-260811-0038.txt | exported_rc_sets/2026-08-14-exports-260810-260811/260811/RC-ELITE-260811-0038.txt</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>2 exported variants; preferred one listed first</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260907-0083</t>
+          <t>RC-ELITE-260822-0062</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -8990,7 +9662,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Medicine &amp; Health</t>
+          <t>Philosophy &amp; Ethics</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -9008,35 +9680,35 @@
       </c>
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>0.862</v>
+        <v>0.907</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.44</v>
+        <v>0.616</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>578</v>
+        <v>525</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260907-0083.txt</t>
+          <t>exported_rc_sets/RC-ELITE-260822-0062.txt</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260907-0083.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260822-0062.txt</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260907-0083.txt</t>
+          <t>exported_rc_sets/RC-ELITE-260822-0062.txt</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr"/>
@@ -9044,7 +9716,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260905-0076</t>
+          <t>RC-ELITE-260907-0082</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -9054,7 +9726,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>History</t>
+          <t>Politics, Law &amp; Policy</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -9072,35 +9744,35 @@
       </c>
       <c r="G27" s="2" t="inlineStr"/>
       <c r="H27" s="2" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>0.862</v>
+        <v>0.884</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.457</v>
+        <v>0.482</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>536</v>
+        <v>550</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260905-0076.txt</t>
+          <t>exported_rc_sets/RC-ELITE-260907-0082.txt</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260905-0076.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260907-0082.txt</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260905-0076.txt</t>
+          <t>exported_rc_sets/RC-ELITE-260907-0082.txt</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr"/>
@@ -9108,7 +9780,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260822-0059</t>
+          <t>RC-ELITE-260912-0085</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -9116,11 +9788,7 @@
           <t>elite</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Politics, Law &amp; Policy</t>
-        </is>
-      </c>
+      <c r="C28" s="2" t="inlineStr"/>
       <c r="D28" s="4" t="inlineStr">
         <is>
           <t>needs_review</t>
@@ -9136,52 +9804,48 @@
       </c>
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>0.981</v>
+        <v>0.765</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.622</v>
+        <v>0.495</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>531</v>
+        <v>572</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/post_housevoice_fix/RC-ELITE-260822-0059.txt</t>
+          <t>exported_rc_sets/RC-ELITE-260912-0085.txt</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\post_housevoice_fix\RC-ELITE-260822-0059.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260912-0085.txt</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/post_housevoice_fix/RC-ELITE-260822-0059.txt | exported_rc_sets/flagged_similar/RC-ELITE-260822-0059.txt | exported_rc_sets/try_2/flagged_similar/RC-ELITE-260822-0059.txt</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>3 exported variants; preferred one listed first</t>
-        </is>
-      </c>
+          <t>exported_rc_sets/RC-ELITE-260912-0085.txt</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260811-0035</t>
+          <t>RC-ELITE-260907-0083</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>hard</t>
+          <t>elite</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -9204,57 +9868,53 @@
       </c>
       <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>1</v>
+        <v>0.862</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.493</v>
+        <v>0.44</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>516</v>
+        <v>578</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260811-0035.txt</t>
+          <t>exported_rc_sets/RC-ELITE-260907-0083.txt</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260811-0035.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260907-0083.txt</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260811-0035.txt | exported_rc_sets/2026-08-14-exports-260810-260811/260811/RC-HARD-260811-0035.txt</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>2 exported variants; preferred one listed first</t>
-        </is>
-      </c>
+          <t>exported_rc_sets/RC-ELITE-260907-0083.txt</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260901-0073</t>
+          <t>RC-ELITE-260905-0076</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>hard</t>
+          <t>elite</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Medicine &amp; Health</t>
+          <t>History</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -9272,59 +9932,51 @@
       </c>
       <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="n">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>0.85</v>
+        <v>0.862</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.499</v>
+        <v>0.457</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/2026-09-01-0901-v2/RC-HARD-260901-0073.txt</t>
+          <t>exported_rc_sets/RC-ELITE-260905-0076.txt</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\2026-09-01-0901-v2\RC-HARD-260901-0073.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260905-0076.txt</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/2026-09-01-0901-v2/RC-HARD-260901-0073.txt | exported_rc_sets/flagged_similar/RC-HARD-260901-0073.txt</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>2 exported variants; preferred one listed first</t>
-        </is>
-      </c>
+          <t>exported_rc_sets/RC-ELITE-260905-0076.txt</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260811-0037</t>
+          <t>RC-ELITE-260914-0091</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Philosophy &amp; Ethics</t>
-        </is>
-      </c>
+          <t>elite</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr"/>
       <c r="D31" s="4" t="inlineStr">
         <is>
           <t>needs_review</t>
@@ -9340,57 +9992,57 @@
       </c>
       <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="n">
-        <v>8.6</v>
+        <v>6.2</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>1</v>
+        <v>0.921</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.505</v>
+        <v>0.467</v>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>531</v>
+        <v>567</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260811-0037.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-ELITE-260914-0091.txt</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260811-0037.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-ELITE-260914-0091.txt</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260811-0037.txt | exported_rc_sets/2026-08-14-exports-260810-260811/260811/RC-HARD-260811-0037.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-ELITE-260914-0091.txt</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2 exported variants; preferred one listed first</t>
+          <t>only ever exported into flagged_similar (novelty-flagged)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260811-0047</t>
+          <t>RC-ELITE-260822-0059</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>hard</t>
+          <t>elite</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Literature &amp; Criticism</t>
+          <t>Politics, Law &amp; Policy</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -9408,47 +10060,47 @@
       </c>
       <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="n">
-        <v>8.6</v>
+        <v>6</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1</v>
+        <v>0.981</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.538</v>
+        <v>0.622</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>496</v>
+        <v>531</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260811-0047.txt</t>
+          <t>exported_rc_sets/post_housevoice_fix/RC-ELITE-260822-0059.txt</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260811-0047.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\post_housevoice_fix\RC-ELITE-260822-0059.txt</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260811-0047.txt | exported_rc_sets/2026-08-14-exports-260810-260811/260811/RC-HARD-260811-0047.txt</t>
+          <t>exported_rc_sets/post_housevoice_fix/RC-ELITE-260822-0059.txt | exported_rc_sets/flagged_similar/RC-ELITE-260822-0059.txt | exported_rc_sets/try_2/flagged_similar/RC-ELITE-260822-0059.txt</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2 exported variants; preferred one listed first</t>
+          <t>3 exported variants; preferred one listed first</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260819-0050</t>
+          <t>RC-HARD-260811-0035</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -9458,7 +10110,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Language &amp; Linguistics</t>
+          <t>Medicine &amp; Health</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -9476,35 +10128,35 @@
       </c>
       <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I33" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.493</v>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>533</v>
+        <v>516</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260819-0050.txt</t>
+          <t>exported_rc_sets/RC-HARD-260811-0035.txt</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260819-0050.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260811-0035.txt</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260819-0050.txt | exported_rc_sets/try_2/RC-HARD-260819-0050.txt</t>
+          <t>exported_rc_sets/RC-HARD-260811-0035.txt | exported_rc_sets/2026-08-14-exports-260810-260811/260811/RC-HARD-260811-0035.txt</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -9516,7 +10168,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260810-0034</t>
+          <t>RC-HARD-260901-0073</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -9526,7 +10178,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>History</t>
+          <t>Medicine &amp; Health</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -9544,35 +10196,35 @@
       </c>
       <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.543</v>
+        <v>0.499</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>548</v>
+        <v>540</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260810-0034.txt</t>
+          <t>exported_rc_sets/2026-09-01-0901-v2/RC-HARD-260901-0073.txt</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260810-0034.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\2026-09-01-0901-v2\RC-HARD-260901-0073.txt</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260810-0034.txt | exported_rc_sets/2026-08-14-exports-260810-260811/260810/RC-HARD-260810-0034.txt</t>
+          <t>exported_rc_sets/2026-09-01-0901-v2/RC-HARD-260901-0073.txt | exported_rc_sets/flagged_similar/RC-HARD-260901-0073.txt</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -9584,7 +10236,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260904-0080</t>
+          <t>RC-HARD-260819-0050</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -9594,7 +10246,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Literature &amp; Criticism</t>
+          <t>Language &amp; Linguistics</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -9612,47 +10264,47 @@
       </c>
       <c r="G35" s="2" t="inlineStr"/>
       <c r="H35" s="2" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>0.737</v>
+        <v>1</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.581</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>567</v>
+        <v>533</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-HARD-260904-0080.txt</t>
+          <t>exported_rc_sets/RC-HARD-260819-0050.txt</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-HARD-260904-0080.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260819-0050.txt</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-HARD-260904-0080.txt</t>
+          <t>exported_rc_sets/RC-HARD-260819-0050.txt | exported_rc_sets/try_2/RC-HARD-260819-0050.txt</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>only ever exported into flagged_similar (novelty-flagged)</t>
+          <t>2 exported variants; preferred one listed first</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260905-0082</t>
+          <t>RC-HARD-260912-0092</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -9660,11 +10312,7 @@
           <t>hard</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Anthropology &amp; Archaeology</t>
-        </is>
-      </c>
+      <c r="C36" s="2" t="inlineStr"/>
       <c r="D36" s="4" t="inlineStr">
         <is>
           <t>needs_review</t>
@@ -9680,43 +10328,47 @@
       </c>
       <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="2" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>0.85</v>
+        <v>0.869</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.533</v>
+        <v>0.58</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260905-0082.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-HARD-260912-0092.txt</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260905-0082.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-HARD-260912-0092.txt</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260905-0082.txt</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/flagged_similar/RC-HARD-260912-0092.txt</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>only ever exported into flagged_similar (novelty-flagged)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260907-0087</t>
+          <t>RC-HARD-260810-0034</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -9726,7 +10378,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Arts, Music &amp; Film</t>
+          <t>History</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -9744,47 +10396,47 @@
       </c>
       <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>0.831</v>
+        <v>1</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.534</v>
+        <v>0.543</v>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>561</v>
+        <v>548</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-HARD-260907-0087.txt</t>
+          <t>exported_rc_sets/RC-HARD-260810-0034.txt</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-HARD-260907-0087.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260810-0034.txt</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-HARD-260907-0087.txt</t>
+          <t>exported_rc_sets/RC-HARD-260810-0034.txt | exported_rc_sets/2026-08-14-exports-260810-260811/260810/RC-HARD-260810-0034.txt</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>only ever exported into flagged_similar (novelty-flagged)</t>
+          <t>2 exported variants; preferred one listed first</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260822-0061</t>
+          <t>RC-HARD-260904-0080</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -9794,7 +10446,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Politics, Law &amp; Policy</t>
+          <t>Literature &amp; Criticism</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -9812,47 +10464,47 @@
       </c>
       <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>0.857</v>
+        <v>0.737</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.524</v>
+        <v>0.581</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>503</v>
+        <v>567</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/post_housevoice_fix/RC-HARD-260822-0061.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-HARD-260904-0080.txt</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\post_housevoice_fix\RC-HARD-260822-0061.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-HARD-260904-0080.txt</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/post_housevoice_fix/RC-HARD-260822-0061.txt | exported_rc_sets/review_shippable/01_shippable_as_is/RC-HARD-260822-0061.txt | exported_rc_sets/flagged_similar/RC-HARD-260822-0061.txt | exported_rc_sets/try_2/flagged_similar/RC-HARD-260822-0061.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-HARD-260904-0080.txt</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>4 exported variants; preferred one listed first</t>
+          <t>only ever exported into flagged_similar (novelty-flagged)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260901-0077</t>
+          <t>RC-HARD-260905-0082</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -9862,7 +10514,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Sociology &amp; Culture</t>
+          <t>Anthropology &amp; Archaeology</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -9880,35 +10532,35 @@
       </c>
       <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="2" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.531</v>
+        <v>0.533</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260901-0077.txt</t>
+          <t>exported_rc_sets/RC-HARD-260905-0082.txt</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260901-0077.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260905-0082.txt</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260901-0077.txt</t>
+          <t>exported_rc_sets/RC-HARD-260905-0082.txt</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr"/>
@@ -9916,7 +10568,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260905-0081</t>
+          <t>RC-HARD-260914-0098</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -9924,11 +10576,7 @@
           <t>hard</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Politics, Law &amp; Policy</t>
-        </is>
-      </c>
+      <c r="C40" s="2" t="inlineStr"/>
       <c r="D40" s="4" t="inlineStr">
         <is>
           <t>needs_review</t>
@@ -9944,47 +10592,43 @@
       </c>
       <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>0.862</v>
+        <v>0.78</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.524</v>
+        <v>0.548</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>545</v>
+        <v>502</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-HARD-260905-0081.txt</t>
+          <t>exported_rc_sets/RC-HARD-260914-0098.txt</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-HARD-260905-0081.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260914-0098.txt</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-HARD-260905-0081.txt</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>only ever exported into flagged_similar (novelty-flagged)</t>
-        </is>
-      </c>
+          <t>exported_rc_sets/RC-HARD-260914-0098.txt</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260901-0074</t>
+          <t>RC-HARD-260907-0087</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -9994,7 +10638,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Medicine &amp; Health</t>
+          <t>Arts, Music &amp; Film</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -10012,47 +10656,47 @@
       </c>
       <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="2" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>0.86</v>
+        <v>0.831</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.529</v>
+        <v>0.534</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>545</v>
+        <v>561</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/2026-09-01-0901-v2/RC-HARD-260901-0074.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-HARD-260907-0087.txt</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\2026-09-01-0901-v2\RC-HARD-260901-0074.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-HARD-260907-0087.txt</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/2026-09-01-0901-v2/RC-HARD-260901-0074.txt | exported_rc_sets/RC-HARD-260901-0074.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-HARD-260907-0087.txt</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2 exported variants; preferred one listed first</t>
+          <t>only ever exported into flagged_similar (novelty-flagged)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260822-0062</t>
+          <t>RC-HARD-260914-0096</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -10060,11 +10704,7 @@
           <t>hard</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Philosophy &amp; Ethics</t>
-        </is>
-      </c>
+      <c r="C42" s="2" t="inlineStr"/>
       <c r="D42" s="4" t="inlineStr">
         <is>
           <t>needs_review</t>
@@ -10080,47 +10720,43 @@
       </c>
       <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>0.843</v>
+        <v>0.756</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.6</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>452</v>
+        <v>551</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-HARD-260822-0062.txt</t>
+          <t>exported_rc_sets/RC-HARD-260914-0096.txt</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-HARD-260822-0062.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260914-0096.txt</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-HARD-260822-0062.txt</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>only ever exported into flagged_similar (novelty-flagged)</t>
-        </is>
-      </c>
+          <t>exported_rc_sets/RC-HARD-260914-0096.txt</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260907-0086</t>
+          <t>RC-HARD-260822-0061</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -10130,7 +10766,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Science &amp; Technology</t>
+          <t>Politics, Law &amp; Policy</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -10148,43 +10784,47 @@
       </c>
       <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>0.847</v>
+        <v>0.857</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.578</v>
+        <v>0.524</v>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>550</v>
+        <v>503</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260907-0086.txt</t>
+          <t>exported_rc_sets/post_housevoice_fix/RC-HARD-260822-0061.txt</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260907-0086.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\post_housevoice_fix\RC-HARD-260822-0061.txt</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260907-0086.txt</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/post_housevoice_fix/RC-HARD-260822-0061.txt | exported_rc_sets/review_shippable/01_shippable_as_is/RC-HARD-260822-0061.txt | exported_rc_sets/flagged_similar/RC-HARD-260822-0061.txt | exported_rc_sets/try_2/flagged_similar/RC-HARD-260822-0061.txt</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>4 exported variants; preferred one listed first</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260905-0084</t>
+          <t>RC-HARD-260901-0077</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -10194,7 +10834,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Life Sciences &amp; Environment</t>
+          <t>Sociology &amp; Culture</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -10212,47 +10852,43 @@
       </c>
       <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="2" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>0.839</v>
+        <v>0.79</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.531</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>523</v>
+        <v>551</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-HARD-260905-0084.txt</t>
+          <t>exported_rc_sets/RC-HARD-260901-0077.txt</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-HARD-260905-0084.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260901-0077.txt</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-HARD-260905-0084.txt</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>only ever exported into flagged_similar (novelty-flagged)</t>
-        </is>
-      </c>
+          <t>exported_rc_sets/RC-HARD-260901-0077.txt</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260905-0085</t>
+          <t>RC-HARD-260905-0081</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -10262,7 +10898,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Economics &amp; Business</t>
+          <t>Politics, Law &amp; Policy</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -10280,13 +10916,13 @@
       </c>
       <c r="G45" s="2" t="inlineStr"/>
       <c r="H45" s="2" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>0.766</v>
+        <v>0.862</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.539</v>
+        <v>0.524</v>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
@@ -10294,29 +10930,33 @@
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>521</v>
+        <v>545</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260905-0085.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-HARD-260905-0081.txt</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260905-0085.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-HARD-260905-0081.txt</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260905-0085.txt</t>
-        </is>
-      </c>
-      <c r="P45" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/flagged_similar/RC-HARD-260905-0081.txt</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>only ever exported into flagged_similar (novelty-flagged)</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260904-0079</t>
+          <t>RC-HARD-260912-0089</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -10324,11 +10964,7 @@
           <t>hard</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
+      <c r="C46" s="2" t="inlineStr"/>
       <c r="D46" s="4" t="inlineStr">
         <is>
           <t>needs_review</t>
@@ -10344,35 +10980,35 @@
       </c>
       <c r="G46" s="2" t="inlineStr"/>
       <c r="H46" s="2" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>0.806</v>
+        <v>0.786</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.514</v>
+        <v>0.481</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>566</v>
+        <v>548</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-HARD-260904-0079.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-HARD-260912-0089.txt</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-HARD-260904-0079.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-HARD-260912-0089.txt</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-HARD-260904-0079.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-HARD-260912-0089.txt</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -10384,17 +11020,17 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260904-0057</t>
+          <t>RC-HARD-260901-0074</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Science &amp; Technology</t>
+          <t>Medicine &amp; Health</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -10412,57 +11048,57 @@
       </c>
       <c r="G47" s="2" t="inlineStr"/>
       <c r="H47" s="2" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>0.537</v>
+        <v>0.86</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.524</v>
+        <v>0.529</v>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260904-0057.txt</t>
+          <t>exported_rc_sets/2026-09-01-0901-v2/RC-HARD-260901-0074.txt</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-MEDIUM-260904-0057.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\2026-09-01-0901-v2\RC-HARD-260901-0074.txt</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260904-0057.txt</t>
+          <t>exported_rc_sets/2026-09-01-0901-v2/RC-HARD-260901-0074.txt | exported_rc_sets/RC-HARD-260901-0074.txt</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>only ever exported into flagged_similar (novelty-flagged)</t>
+          <t>2 exported variants; preferred one listed first</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260904-0058</t>
+          <t>RC-HARD-260822-0062</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Politics, Law &amp; Policy</t>
+          <t>Philosophy &amp; Ethics</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -10480,35 +11116,35 @@
       </c>
       <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="n">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>0.89</v>
+        <v>0.843</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.585</v>
+        <v>0.6</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>544</v>
+        <v>452</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260904-0058.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-HARD-260822-0062.txt</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-MEDIUM-260904-0058.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-HARD-260822-0062.txt</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260904-0058.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-HARD-260822-0062.txt</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -10520,19 +11156,15 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260810-0024</t>
+          <t>RC-HARD-260912-0093</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>Medicine &amp; Health</t>
-        </is>
-      </c>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr"/>
       <c r="D49" s="4" t="inlineStr">
         <is>
           <t>needs_review</t>
@@ -10548,57 +11180,57 @@
       </c>
       <c r="G49" s="2" t="inlineStr"/>
       <c r="H49" s="2" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>1</v>
+        <v>0.767</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.653</v>
+        <v>0.535</v>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="L49" s="2" t="n">
-        <v>535</v>
+        <v>552</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/2026-08-14-exports-260810-260811/260810/RC-MEDIUM-260810-0024.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-HARD-260912-0093.txt</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\2026-08-14-exports-260810-260811\260810\RC-MEDIUM-260810-0024.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-HARD-260912-0093.txt</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/2026-08-14-exports-260810-260811/260810/RC-MEDIUM-260810-0024.txt | exported_rc_sets/2026-08-14-medium-8q/RC-MEDIUM-260810-0024.txt | exported_rc_sets/RC-MEDIUM-260810-0024.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-HARD-260912-0093.txt</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>3 exported variants; preferred one listed first</t>
+          <t>only ever exported into flagged_similar (novelty-flagged)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260901-0055</t>
+          <t>RC-HARD-260907-0086</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Literature &amp; Criticism</t>
+          <t>Science &amp; Technology</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -10616,57 +11248,53 @@
       </c>
       <c r="G50" s="2" t="inlineStr"/>
       <c r="H50" s="2" t="n">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>0.871</v>
+        <v>0.847</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.523</v>
+        <v>0.578</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260901-0055.txt</t>
+          <t>exported_rc_sets/RC-HARD-260907-0086.txt</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-MEDIUM-260901-0055.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260907-0086.txt</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260901-0055.txt</t>
-        </is>
-      </c>
-      <c r="P50" s="2" t="inlineStr">
-        <is>
-          <t>only ever exported into flagged_similar (novelty-flagged)</t>
-        </is>
-      </c>
+          <t>exported_rc_sets/RC-HARD-260907-0086.txt</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260905-0063</t>
+          <t>RC-HARD-260905-0084</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Politics, Law &amp; Policy</t>
+          <t>Life Sciences &amp; Environment</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -10684,13 +11312,13 @@
       </c>
       <c r="G51" s="2" t="inlineStr"/>
       <c r="H51" s="2" t="n">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>0.875</v>
+        <v>0.839</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.508</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
@@ -10698,21 +11326,21 @@
         </is>
       </c>
       <c r="L51" s="2" t="n">
-        <v>474</v>
+        <v>523</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260905-0063.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-HARD-260905-0084.txt</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-MEDIUM-260905-0063.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-HARD-260905-0084.txt</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260905-0063.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-HARD-260905-0084.txt</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -10724,17 +11352,17 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260822-0040</t>
+          <t>RC-HARD-260905-0085</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Philosophy &amp; Ethics</t>
+          <t>Economics &amp; Business</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -10752,57 +11380,53 @@
       </c>
       <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="2" t="n">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>0.845</v>
+        <v>0.766</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.593</v>
+        <v>0.539</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>401</v>
+        <v>521</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260822-0040.txt</t>
+          <t>exported_rc_sets/RC-HARD-260905-0085.txt</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-MEDIUM-260822-0040.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260905-0085.txt</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260822-0040.txt</t>
-        </is>
-      </c>
-      <c r="P52" s="2" t="inlineStr">
-        <is>
-          <t>only ever exported into flagged_similar (novelty-flagged)</t>
-        </is>
-      </c>
+          <t>exported_rc_sets/RC-HARD-260905-0085.txt</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260822-0038</t>
+          <t>RC-HARD-260904-0079</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Politics, Law &amp; Policy</t>
+          <t>History</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -10820,47 +11444,47 @@
       </c>
       <c r="G53" s="2" t="inlineStr"/>
       <c r="H53" s="2" t="n">
-        <v>7.8</v>
+        <v>6</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>0.95</v>
+        <v>0.806</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.633</v>
+        <v>0.514</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
-        <v>479</v>
+        <v>566</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/post_housevoice_fix/RC-MEDIUM-260822-0038.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-HARD-260904-0079.txt</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\post_housevoice_fix\RC-MEDIUM-260822-0038.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-HARD-260904-0079.txt</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/post_housevoice_fix/RC-MEDIUM-260822-0038.txt | exported_rc_sets/review_shippable/02_likely_length_only/RC-MEDIUM-260822-0038.txt | exported_rc_sets/flagged_similar/RC-MEDIUM-260822-0038.txt | exported_rc_sets/try_2/flagged_similar/RC-MEDIUM-260822-0038.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-HARD-260904-0079.txt</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>4 exported variants; preferred one listed first</t>
+          <t>only ever exported into flagged_similar (novelty-flagged)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260901-0054</t>
+          <t>RC-MEDIUM-260904-0057</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -10870,7 +11494,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Arts, Music &amp; Film</t>
+          <t>Science &amp; Technology</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -10888,43 +11512,47 @@
       </c>
       <c r="G54" s="2" t="inlineStr"/>
       <c r="H54" s="2" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>0.884</v>
+        <v>0.537</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.45</v>
+        <v>0.524</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>525</v>
+        <v>550</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-MEDIUM-260901-0054.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260904-0057.txt</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-MEDIUM-260901-0054.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-MEDIUM-260904-0057.txt</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-MEDIUM-260901-0054.txt</t>
-        </is>
-      </c>
-      <c r="P54" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260904-0057.txt</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>only ever exported into flagged_similar (novelty-flagged)</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260904-0060</t>
+          <t>RC-MEDIUM-260904-0058</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -10934,7 +11562,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>History</t>
+          <t>Politics, Law &amp; Policy</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -10952,13 +11580,13 @@
       </c>
       <c r="G55" s="2" t="inlineStr"/>
       <c r="H55" s="2" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>0.847</v>
+        <v>0.89</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.536</v>
+        <v>0.585</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
@@ -10966,21 +11594,21 @@
         </is>
       </c>
       <c r="L55" s="2" t="n">
-        <v>557</v>
+        <v>544</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260904-0060.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260904-0058.txt</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-MEDIUM-260904-0060.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-MEDIUM-260904-0058.txt</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260904-0060.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260904-0058.txt</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -10992,22 +11620,22 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260822-0056</t>
+          <t>RC-MEDIUM-260810-0024</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>elite</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Anthropology &amp; Archaeology</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="inlineStr">
-        <is>
-          <t>solver_dispute</t>
+          <t>Medicine &amp; Health</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -11019,38 +11647,36 @@
         <v>8</v>
       </c>
       <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="H56" s="2" t="n">
+        <v>8.6</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.531</v>
+        <v>0.653</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>548</v>
+        <v>535</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260822-0056.txt</t>
+          <t>exported_rc_sets/2026-08-14-exports-260810-260811/260810/RC-MEDIUM-260810-0024.txt</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260822-0056.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\2026-08-14-exports-260810-260811\260810\RC-MEDIUM-260810-0024.txt</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260822-0056.txt | exported_rc_sets/post_housevoice_fix/RC-ELITE-260822-0056.txt | exported_rc_sets/try_2/RC-ELITE-260822-0056.txt</t>
+          <t>exported_rc_sets/2026-08-14-exports-260810-260811/260810/RC-MEDIUM-260810-0024.txt | exported_rc_sets/2026-08-14-medium-8q/RC-MEDIUM-260810-0024.txt | exported_rc_sets/RC-MEDIUM-260810-0024.txt</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -11062,12 +11688,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260905-0080</t>
+          <t>RC-MEDIUM-260901-0055</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>elite</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -11075,9 +11701,9 @@
           <t>Literature &amp; Criticism</t>
         </is>
       </c>
-      <c r="D57" s="5" t="inlineStr">
-        <is>
-          <t>solver_dispute</t>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -11089,61 +11715,63 @@
         <v>8</v>
       </c>
       <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="H57" s="2" t="n">
+        <v>8.6</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>0.804</v>
+        <v>0.871</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.542</v>
+        <v>0.523</v>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
-        <v>519</v>
+        <v>551</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260905-0080.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260901-0055.txt</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260905-0080.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-MEDIUM-260901-0055.txt</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260905-0080.txt</t>
-        </is>
-      </c>
-      <c r="P57" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260901-0055.txt</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>only ever exported into flagged_similar (novelty-flagged)</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260901-0076</t>
+          <t>RC-MEDIUM-260905-0063</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>hard</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Literature &amp; Criticism</t>
-        </is>
-      </c>
-      <c r="D58" s="5" t="inlineStr">
-        <is>
-          <t>solver_dispute</t>
+          <t>Politics, Law &amp; Policy</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -11155,61 +11783,63 @@
         <v>8</v>
       </c>
       <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="H58" s="2" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0.8</v>
+        <v>0.875</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.549</v>
+        <v>0.508</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>539</v>
+        <v>474</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260901-0076.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260905-0063.txt</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260901-0076.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-MEDIUM-260905-0063.txt</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-HARD-260901-0076.txt</t>
-        </is>
-      </c>
-      <c r="P58" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260905-0063.txt</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>only ever exported into flagged_similar (novelty-flagged)</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>RC-HARD-260904-0078</t>
+          <t>RC-MEDIUM-260822-0040</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>hard</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Psychology</t>
-        </is>
-      </c>
-      <c r="D59" s="5" t="inlineStr">
-        <is>
-          <t>solver_dispute</t>
+          <t>Philosophy &amp; Ethics</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -11221,38 +11851,36 @@
         <v>8</v>
       </c>
       <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="H59" s="2" t="n">
+        <v>8</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.845</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.593</v>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>544</v>
+        <v>401</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-HARD-260904-0078.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260822-0040.txt</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-HARD-260904-0078.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-MEDIUM-260822-0040.txt</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-HARD-260904-0078.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260822-0040.txt</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -11264,7 +11892,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260810-0022</t>
+          <t>RC-MEDIUM-260822-0038</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -11274,12 +11902,12 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Medicine &amp; Health</t>
-        </is>
-      </c>
-      <c r="D60" s="5" t="inlineStr">
-        <is>
-          <t>solver_dispute</t>
+          <t>Politics, Law &amp; Policy</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -11291,50 +11919,48 @@
         <v>8</v>
       </c>
       <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="H60" s="2" t="n">
+        <v>7.8</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.647</v>
+        <v>0.633</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>553</v>
+        <v>479</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/2026-08-14-exports-260810-260811/260810/RC-MEDIUM-260810-0022.txt</t>
+          <t>exported_rc_sets/post_housevoice_fix/RC-MEDIUM-260822-0038.txt</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\2026-08-14-exports-260810-260811\260810\RC-MEDIUM-260810-0022.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\post_housevoice_fix\RC-MEDIUM-260822-0038.txt</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/2026-08-14-exports-260810-260811/260810/RC-MEDIUM-260810-0022.txt | exported_rc_sets/2026-08-14-medium-8q/RC-MEDIUM-260810-0022.txt | exported_rc_sets/RC-MEDIUM-260810-0022.txt</t>
+          <t>exported_rc_sets/post_housevoice_fix/RC-MEDIUM-260822-0038.txt | exported_rc_sets/review_shippable/02_likely_length_only/RC-MEDIUM-260822-0038.txt | exported_rc_sets/flagged_similar/RC-MEDIUM-260822-0038.txt | exported_rc_sets/try_2/flagged_similar/RC-MEDIUM-260822-0038.txt</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>3 exported variants; preferred one listed first</t>
+          <t>4 exported variants; preferred one listed first</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260822-0035</t>
+          <t>RC-MEDIUM-260904-0060</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -11344,12 +11970,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Politics, Law &amp; Policy</t>
-        </is>
-      </c>
-      <c r="D61" s="5" t="inlineStr">
-        <is>
-          <t>solver_dispute</t>
+          <t>History</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -11361,50 +11987,48 @@
         <v>8</v>
       </c>
       <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="H61" s="2" t="n">
+        <v>7.8</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>0.9</v>
+        <v>0.847</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.59</v>
+        <v>0.536</v>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>540</v>
+        <v>557</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-MEDIUM-260822-0035.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260904-0060.txt</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-MEDIUM-260822-0035.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-MEDIUM-260904-0060.txt</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-MEDIUM-260822-0035.txt | exported_rc_sets/post_housevoice_fix/RC-MEDIUM-260822-0035.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260904-0060.txt</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>2 exported variants; preferred one listed first</t>
+          <t>only ever exported into flagged_similar (novelty-flagged)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260905-0062</t>
+          <t>RC-MEDIUM-260912-0067</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -11412,14 +12036,10 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>Economics &amp; Business</t>
-        </is>
-      </c>
-      <c r="D62" s="5" t="inlineStr">
-        <is>
-          <t>solver_dispute</t>
+      <c r="C62" s="2" t="inlineStr"/>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -11431,38 +12051,36 @@
         <v>8</v>
       </c>
       <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="H62" s="2" t="n">
+        <v>7.8</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>0.79</v>
+        <v>0.829</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.471</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>566</v>
+        <v>553</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260905-0062.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260912-0067.txt</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-MEDIUM-260905-0062.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-MEDIUM-260912-0067.txt</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260905-0062.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260912-0067.txt</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -11474,7 +12092,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260907-0066</t>
+          <t>RC-MEDIUM-260914-0070</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -11482,14 +12100,10 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>Politics, Law &amp; Policy</t>
-        </is>
-      </c>
-      <c r="D63" s="5" t="inlineStr">
-        <is>
-          <t>solver_dispute</t>
+      <c r="C63" s="2" t="inlineStr"/>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -11501,61 +12115,59 @@
         <v>8</v>
       </c>
       <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="H63" s="2" t="n">
+        <v>7.8</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>0.785</v>
+        <v>0.739</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.528</v>
+        <v>0.55</v>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>543</v>
+        <v>557</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-MEDIUM-260907-0066.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260914-0070.txt</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-MEDIUM-260907-0066.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-MEDIUM-260914-0070.txt</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-MEDIUM-260907-0066.txt</t>
-        </is>
-      </c>
-      <c r="P63" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260914-0070.txt</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>only ever exported into flagged_similar (novelty-flagged)</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>RC-ELITE-260726-0030</t>
+          <t>RC-MEDIUM-260914-0076</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>elite</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>Anthropology &amp; Archaeology</t>
-        </is>
-      </c>
-      <c r="D64" s="6" t="inlineStr">
-        <is>
-          <t>rejected_novelty</t>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr"/>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -11564,68 +12176,66 @@
         </is>
       </c>
       <c r="F64" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>+2 questions</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+        <v>8</v>
+      </c>
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="n">
+        <v>7.8</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>1</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.476</v>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>500</v>
+        <v>556</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260726-0030.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260914-0076.txt</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260726-0030.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-MEDIUM-260914-0076.txt</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-ELITE-260726-0030.txt</t>
-        </is>
-      </c>
-      <c r="P64" s="2" t="inlineStr"/>
+          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260914-0076.txt</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>only ever exported into flagged_similar (novelty-flagged)</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>RC-MEDIUM-260904-0059</t>
+          <t>RC-ELITE-260822-0056</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>elite</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Science &amp; Technology</t>
-        </is>
-      </c>
-      <c r="D65" s="6" t="inlineStr">
-        <is>
-          <t>rejected_novelty</t>
+          <t>Anthropology &amp; Archaeology</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>solver_dispute</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -11643,59 +12253,59 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>0.84</v>
+        <v>0.9</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.525</v>
+        <v>0.531</v>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>568</v>
+        <v>548</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260904-0059.txt</t>
+          <t>exported_rc_sets/RC-ELITE-260822-0056.txt</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-MEDIUM-260904-0059.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260822-0056.txt</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260904-0059.txt</t>
+          <t>exported_rc_sets/RC-ELITE-260822-0056.txt | exported_rc_sets/post_housevoice_fix/RC-ELITE-260822-0056.txt | exported_rc_sets/try_2/RC-ELITE-260822-0056.txt</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>only ever exported into flagged_similar (novelty-flagged)</t>
+          <t>3 exported variants; preferred one listed first</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>RC-MANUAL-260708-10</t>
+          <t>RC-ELITE-260905-0080</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>elite</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Science &amp; Technology</t>
-        </is>
-      </c>
-      <c r="D66" s="6" t="inlineStr">
-        <is>
-          <t>unrated</t>
+          <t>Literature &amp; Criticism</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>solver_dispute</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -11704,60 +12314,64 @@
         </is>
       </c>
       <c r="F66" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>+2 questions</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr"/>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr"/>
-      <c r="K66" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>0.804</v>
+      </c>
+      <c r="J66" s="2" t="n">
+        <v>0.542</v>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
       <c r="L66" s="2" t="n">
-        <v>384</v>
+        <v>519</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-MANUAL-260708-10_medium.txt</t>
+          <t>exported_rc_sets/RC-ELITE-260905-0080.txt</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-MANUAL-260708-10_medium.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-ELITE-260905-0080.txt</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC-MANUAL-260708-10_medium.txt</t>
-        </is>
-      </c>
-      <c r="P66" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">legacy/manual export, not in the engine DB; Source: manual generator (evolutionary metaphors for technology); word count 384 (medium band); tier assigned via word count + complexity read 2026-07-12; user-vetted before shipping; placed into new </t>
-        </is>
-      </c>
+          <t>exported_rc_sets/RC-ELITE-260905-0080.txt</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>RC_E_0705_2</t>
+          <t>RC-HARD-260901-0076</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>elite</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Sociology &amp; Culture</t>
+          <t>Literature &amp; Criticism</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>solver_dispute</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -11766,68 +12380,64 @@
         </is>
       </c>
       <c r="F67" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t>+2 questions</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="G67" s="2" t="inlineStr"/>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>8.8</t>
-        </is>
-      </c>
-      <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr"/>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J67" s="2" t="n">
+        <v>0.549</v>
+      </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
-        <v>580</v>
+        <v>539</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC_E_0705_2.txt</t>
+          <t>exported_rc_sets/RC-HARD-260901-0076.txt</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC_E_0705_2.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-HARD-260901-0076.txt</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC_E_0705_2.txt</t>
-        </is>
-      </c>
-      <c r="P67" s="2" t="inlineStr">
-        <is>
-          <t>BLOCKED - you marked this not-sent: length-bias FAILED: correct answer longest in 4/6 questions, incl. thesis Q1 -- needs content fix before shipping; legacy/manual export, not in the engine DB</t>
-        </is>
-      </c>
+          <t>exported_rc_sets/RC-HARD-260901-0076.txt</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>RC_E_0705_5</t>
+          <t>RC-HARD-260904-0078</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>elite</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Language &amp; Linguistics</t>
+          <t>Psychology</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>solver_dispute</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -11836,68 +12446,68 @@
         </is>
       </c>
       <c r="F68" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>+2 questions</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="G68" s="2" t="inlineStr"/>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>8.8</t>
-        </is>
-      </c>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr"/>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="J68" s="2" t="n">
+        <v>0.5629999999999999</v>
+      </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>589</v>
+        <v>544</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC_E_0705_5.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-HARD-260904-0078.txt</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC_E_0705_5.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-HARD-260904-0078.txt</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/RC_E_0705_5.txt</t>
+          <t>exported_rc_sets/flagged_similar/RC-HARD-260904-0078.txt</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED - you marked this not-sent: length-bias FAILED: correct answer longest in 5/6 questions, incl. thesis Q1 -- needs content fix before shipping; legacy/manual export, not in the engine DB</t>
+          <t>only ever exported into flagged_similar (novelty-flagged)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>rc_hard_0004</t>
+          <t>RC-MEDIUM-260810-0022</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>hard</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Anthropology &amp; Archaeology</t>
+          <t>Medicine &amp; Health</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>solver_dispute</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -11906,121 +12516,661 @@
         </is>
       </c>
       <c r="F69" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>+2 questions</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="G69" s="2" t="inlineStr"/>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>8.4</t>
-        </is>
-      </c>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr"/>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J69" s="2" t="n">
+        <v>0.647</v>
+      </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>485</v>
+        <v>553</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/rc_hard_0004.txt</t>
+          <t>exported_rc_sets/2026-08-14-exports-260810-260811/260810/RC-MEDIUM-260810-0022.txt</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\rc_hard_0004.txt</t>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\2026-08-14-exports-260810-260811\260810\RC-MEDIUM-260810-0022.txt</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>exported_rc_sets/rc_hard_0004.txt</t>
+          <t>exported_rc_sets/2026-08-14-exports-260810-260811/260810/RC-MEDIUM-260810-0022.txt | exported_rc_sets/2026-08-14-medium-8q/RC-MEDIUM-260810-0022.txt | exported_rc_sets/RC-MEDIUM-260810-0022.txt</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED - you marked this not-sent: length-bias FAILED: correct answer longest in 6/6 questions (all), incl. thesis Q1 -- needs content fix before shipping; legacy/manual export, not in the engine DB</t>
+          <t>3 exported variants; preferred one listed first</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>RC-MEDIUM-260822-0035</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Politics, Law &amp; Policy</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>solver_dispute</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J70" s="2" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="n">
+        <v>540</v>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>exported_rc_sets/RC-MEDIUM-260822-0035.txt</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-MEDIUM-260822-0035.txt</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>exported_rc_sets/RC-MEDIUM-260822-0035.txt | exported_rc_sets/post_housevoice_fix/RC-MEDIUM-260822-0035.txt</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>2 exported variants; preferred one listed first</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>RC-MEDIUM-260905-0062</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Economics &amp; Business</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>solver_dispute</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="J71" s="2" t="n">
+        <v>0.5610000000000001</v>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="n">
+        <v>566</v>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260905-0062.txt</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\flagged_similar\RC-MEDIUM-260905-0062.txt</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>exported_rc_sets/flagged_similar/RC-MEDIUM-260905-0062.txt</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>only ever exported into flagged_similar (novelty-flagged)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>RC-MEDIUM-260907-0066</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Politics, Law &amp; Policy</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>solver_dispute</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="J72" s="2" t="n">
+        <v>0.528</v>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="n">
+        <v>543</v>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>exported_rc_sets/RC-MEDIUM-260907-0066.txt</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-MEDIUM-260907-0066.txt</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>exported_rc_sets/RC-MEDIUM-260907-0066.txt</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>RC-MEDIUM-260914-0071</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr"/>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>solver_dispute</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="J73" s="2" t="n">
+        <v>0.539</v>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="n">
+        <v>570</v>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>exported_rc_sets/RC-MEDIUM-260914-0071.txt</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-MEDIUM-260914-0071.txt</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>exported_rc_sets/RC-MEDIUM-260914-0071.txt</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>RC-MANUAL-260708-10</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Science &amp; Technology</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>unrated</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>+2 questions</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr"/>
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="n">
+        <v>384</v>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>exported_rc_sets/RC-MANUAL-260708-10_medium.txt</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC-MANUAL-260708-10_medium.txt</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>exported_rc_sets/RC-MANUAL-260708-10_medium.txt</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">legacy/manual export, not in the engine DB; Source: manual generator (evolutionary metaphors for technology); word count 384 (medium band); tier assigned via word count + complexity read 2026-07-12; user-vetted before shipping; placed into new </t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>RC_E_0705_2</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>elite</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Sociology &amp; Culture</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>+2 questions</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>8.8</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="n">
+        <v>580</v>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>exported_rc_sets/RC_E_0705_2.txt</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC_E_0705_2.txt</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>exported_rc_sets/RC_E_0705_2.txt</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>BLOCKED - you marked this not-sent: length-bias FAILED: correct answer longest in 4/6 questions, incl. thesis Q1 -- needs content fix before shipping; legacy/manual export, not in the engine DB</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>RC_E_0705_5</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>elite</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Language &amp; Linguistics</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>+2 questions</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>8.8</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="n">
+        <v>589</v>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>exported_rc_sets/RC_E_0705_5.txt</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC_E_0705_5.txt</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>exported_rc_sets/RC_E_0705_5.txt</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>BLOCKED - you marked this not-sent: length-bias FAILED: correct answer longest in 5/6 questions, incl. thesis Q1 -- needs content fix before shipping; legacy/manual export, not in the engine DB</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>rc_hard_0004</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Anthropology &amp; Archaeology</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>+2 questions</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>485</v>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>exported_rc_sets/rc_hard_0004.txt</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\rc_hard_0004.txt</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>exported_rc_sets/rc_hard_0004.txt</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>BLOCKED - you marked this not-sent: length-bias FAILED: correct answer longest in 6/6 questions (all), incl. thesis Q1 -- needs content fix before shipping; legacy/manual export, not in the engine DB</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
           <t>RC_H_0705_3</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
         <is>
           <t>Medicine &amp; Health</t>
         </is>
       </c>
-      <c r="D70" s="5" t="inlineStr">
+      <c r="D78" s="5" t="inlineStr">
         <is>
           <t>blocked</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="F70" s="2" t="n">
+      <c r="F78" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t>+2 questions</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>8.2</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr"/>
-      <c r="K70" s="2" t="inlineStr">
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr">
         <is>
           <t>2026-07-05</t>
         </is>
       </c>
-      <c r="L70" s="2" t="n">
+      <c r="L78" s="2" t="n">
         <v>515</v>
       </c>
-      <c r="M70" s="2" t="inlineStr">
+      <c r="M78" s="2" t="inlineStr">
         <is>
           <t>exported_rc_sets/RC_H_0705_3.txt</t>
         </is>
       </c>
-      <c r="N70" s="2" t="inlineStr">
+      <c r="N78" s="2" t="inlineStr">
         <is>
           <t>C:\Users\anshu\OneDrive - eLitmus\RC Gen Project\exported_rc_sets\RC_H_0705_3.txt</t>
         </is>
       </c>
-      <c r="O70" s="2" t="inlineStr">
+      <c r="O78" s="2" t="inlineStr">
         <is>
           <t>exported_rc_sets/RC_H_0705_3.txt</t>
         </is>
       </c>
-      <c r="P70" s="2" t="inlineStr">
+      <c r="P78" s="2" t="inlineStr">
         <is>
           <t>BLOCKED - you marked this not-sent: length-bias FAILED: correct answer longest in 5/6 questions, incl. thesis Q1 -- needs content fix before shipping; legacy/manual export, not in the engine DB</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P70"/>
+  <autoFilter ref="A1:P78"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12031,7 +13181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -12402,8 +13552,46 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Week_9_19_09</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>renamed (RC_TIER_YYMMDD_NN)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J9"/>
+  <autoFilter ref="A1:J10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12476,25 +13664,25 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>19.8</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="3">
@@ -12504,13 +13692,13 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>3</v>
@@ -12519,48 +13707,48 @@
         <v>2</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Science &amp; Technology</t>
+          <t>Arts, Music &amp; Film</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>3</v>
-      </c>
       <c r="H4" s="2" t="n">
-        <v>8.800000000000001</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Anthropology &amp; Archaeology</t>
+          <t>Science &amp; Technology</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>4</v>
@@ -12569,44 +13757,44 @@
         <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F5" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="H5" s="2" t="n">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Arts, Music &amp; Film</t>
+          <t>Anthropology &amp; Archaeology</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>7.7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="7">
@@ -12634,7 +13822,7 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>7.7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="8">
@@ -12662,7 +13850,7 @@
         <v>1</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="9">
@@ -12690,7 +13878,7 @@
         <v>1</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="10">
@@ -12718,7 +13906,7 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="11">
@@ -12746,7 +13934,7 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -12774,7 +13962,7 @@
         <v>2</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -12802,63 +13990,63 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Literature &amp; Criticism</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C14" s="2" t="n">
+      <c r="G14" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="H14" s="2" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Literature &amp; Criticism</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>6</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="2" t="n">
         <v>2</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>1.1</v>
       </c>
     </row>
     <row r="16">
@@ -12868,22 +14056,22 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
     </row>
@@ -13696,7 +14884,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>no file in the live week folder; returned to the available bench</t>
+          <t>no file in the live week folder; the set itself shipped under another id</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13881,7 +15069,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>no file in the live week folder; returned to the available bench</t>
+          <t>no file in the live week folder; the set itself shipped under another id</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13930,7 +15118,7 @@
         </is>
       </c>
       <c r="B4" s="9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -13940,7 +15128,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>91</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6">
@@ -13950,7 +15138,7 @@
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>83</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7">
@@ -13983,7 +15171,7 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>69</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11">
@@ -14003,7 +15191,7 @@
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
@@ -14013,7 +15201,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -14023,7 +15211,7 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -14033,7 +15221,7 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
@@ -14043,7 +15231,7 @@
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -14076,7 +15264,7 @@
         </is>
       </c>
       <c r="B20" s="9" t="n">
-        <v>54</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21">
@@ -14086,7 +15274,7 @@
         </is>
       </c>
       <c r="B21" s="9" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22">
@@ -14096,7 +15284,7 @@
         </is>
       </c>
       <c r="B22" s="9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
@@ -14109,7 +15297,7 @@
         </is>
       </c>
       <c r="B24" s="9" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25">
@@ -14119,7 +15307,7 @@
         </is>
       </c>
       <c r="B25" s="9" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26">
@@ -14129,7 +15317,7 @@
         </is>
       </c>
       <c r="B26" s="9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27">
@@ -14142,7 +15330,7 @@
         </is>
       </c>
       <c r="B28" s="9" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="29">
@@ -14152,7 +15340,7 @@
         </is>
       </c>
       <c r="B29" s="9" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="30">
@@ -14215,7 +15403,7 @@
         </is>
       </c>
       <c r="B36" s="9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
